--- a/dados/user/IA.xlsx
+++ b/dados/user/IA.xlsx
@@ -499,8 +499,6 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>13435.65</v>
       </c>
@@ -534,8 +532,6 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>12753.98</v>
       </c>
@@ -569,8 +565,6 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>12378.6</v>
       </c>
@@ -604,8 +598,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>11604.72</v>
       </c>
@@ -639,8 +631,6 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>9976.16</v>
       </c>
@@ -674,8 +664,6 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>10086.56</v>
       </c>
@@ -709,8 +697,6 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>11779.59</v>
       </c>
@@ -744,8 +730,6 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>9645.459999999999</v>
       </c>
@@ -779,8 +763,6 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>8616.889999999999</v>
       </c>
@@ -814,8 +796,6 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>22091.55</v>
       </c>
@@ -849,8 +829,6 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>22278.87</v>
       </c>
@@ -884,8 +862,6 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>12466.76</v>
       </c>
@@ -919,8 +895,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>17934.17</v>
       </c>
@@ -954,8 +928,6 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>10521.94</v>
       </c>
@@ -989,8 +961,6 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>12430.27</v>
       </c>
@@ -1024,8 +994,6 @@
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>26273.75</v>
       </c>
@@ -1059,8 +1027,6 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>8465.42</v>
       </c>
@@ -1094,8 +1060,6 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>11314.22</v>
       </c>
@@ -1129,8 +1093,6 @@
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>30939.88</v>
       </c>
@@ -1164,8 +1126,6 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>11636.7</v>
       </c>
@@ -1199,8 +1159,6 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>15445.82</v>
       </c>
@@ -1234,8 +1192,6 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>9409.01</v>
       </c>
@@ -1269,8 +1225,6 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>7278.31</v>
       </c>
@@ -1304,8 +1258,6 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>18193.17</v>
       </c>
@@ -1339,8 +1291,6 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>9201.799999999999</v>
       </c>
@@ -1374,8 +1324,6 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>12297.49</v>
       </c>
@@ -1409,8 +1357,6 @@
       <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>18070.41</v>
       </c>
@@ -1444,8 +1390,6 @@
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -1479,8 +1423,6 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>9601.33</v>
       </c>
@@ -1514,8 +1456,6 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>8856.540000000001</v>
       </c>
@@ -1549,8 +1489,6 @@
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>10921.35</v>
       </c>
@@ -1584,8 +1522,6 @@
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>7510.16</v>
       </c>
@@ -1619,8 +1555,6 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>10330.84</v>
       </c>
@@ -1654,8 +1588,6 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>12013.54</v>
       </c>
@@ -1689,8 +1621,6 @@
       <c r="F36" t="n">
         <v>0</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>18098.91</v>
       </c>
@@ -1724,8 +1654,6 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>10922.34</v>
       </c>
@@ -1759,8 +1687,6 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>7448.98</v>
       </c>
@@ -1794,8 +1720,6 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>11989.52</v>
       </c>
@@ -1829,8 +1753,6 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>19069.96</v>
       </c>
@@ -1864,8 +1786,6 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>24383.1</v>
       </c>
@@ -1899,8 +1819,6 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>12351.49</v>
       </c>
@@ -1934,8 +1852,6 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>9984.24</v>
       </c>
@@ -1969,8 +1885,6 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>9614.09</v>
       </c>
@@ -2004,8 +1918,6 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>8253.35</v>
       </c>
@@ -2039,8 +1951,6 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>22949.5</v>
       </c>
@@ -2074,8 +1984,6 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>7544.78</v>
       </c>
@@ -2109,8 +2017,6 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>9655.34</v>
       </c>
@@ -2144,8 +2050,6 @@
       <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>7720.47</v>
       </c>
@@ -2179,8 +2083,6 @@
       <c r="F50" t="n">
         <v>0</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>16333.85</v>
       </c>
@@ -2214,8 +2116,6 @@
       <c r="F51" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>9610.440000000001</v>
       </c>
@@ -2249,8 +2149,6 @@
       <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>9211.68</v>
       </c>
@@ -2284,8 +2182,6 @@
       <c r="F53" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>10162.15</v>
       </c>
@@ -2319,8 +2215,6 @@
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>9700.25</v>
       </c>
@@ -2354,8 +2248,6 @@
       <c r="F55" t="n">
         <v>0</v>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>11155.81</v>
       </c>
@@ -2389,8 +2281,6 @@
       <c r="F56" t="n">
         <v>0</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>15878.43</v>
       </c>
@@ -2424,8 +2314,6 @@
       <c r="F57" t="n">
         <v>0</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>12579.68</v>
       </c>
@@ -2459,8 +2347,6 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>12780.46</v>
       </c>
@@ -2494,8 +2380,6 @@
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>11963.12</v>
       </c>
@@ -2529,8 +2413,6 @@
       <c r="F60" t="n">
         <v>0</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>8053.93</v>
       </c>
@@ -2564,8 +2446,6 @@
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>6047.86</v>
       </c>
@@ -2599,8 +2479,6 @@
       <c r="F62" t="n">
         <v>0</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>6599.23</v>
       </c>
@@ -2634,8 +2512,6 @@
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>6506.6</v>
       </c>
@@ -2669,8 +2545,6 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>6584.72</v>
       </c>
@@ -2704,8 +2578,6 @@
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>5919.97</v>
       </c>
@@ -2739,8 +2611,6 @@
       <c r="F66" t="n">
         <v>0</v>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>6059.07</v>
       </c>
@@ -2774,8 +2644,6 @@
       <c r="F67" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>5843.9</v>
       </c>
@@ -2809,8 +2677,6 @@
       <c r="F68" t="n">
         <v>0</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>6084.07</v>
       </c>
@@ -2844,8 +2710,6 @@
       <c r="F69" t="n">
         <v>0</v>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>6084.43</v>
       </c>
@@ -2879,8 +2743,6 @@
       <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>5902.83</v>
       </c>
@@ -2914,8 +2776,6 @@
       <c r="F71" t="n">
         <v>0</v>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>12742.29</v>
       </c>
@@ -2949,8 +2809,6 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>5843.45</v>
       </c>
@@ -2984,8 +2842,6 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>6078.81</v>
       </c>
@@ -3019,8 +2875,6 @@
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>6024.02</v>
       </c>
@@ -3054,8 +2908,6 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>5841.98</v>
       </c>
@@ -3089,8 +2941,6 @@
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>14429.12</v>
       </c>
@@ -3124,8 +2974,6 @@
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>6824.25</v>
       </c>
@@ -3159,8 +3007,6 @@
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
         <v>12957.63</v>
       </c>
@@ -3194,8 +3040,6 @@
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>6327.62</v>
       </c>
@@ -3229,8 +3073,6 @@
       <c r="F80" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>5844.06</v>
       </c>
@@ -3264,8 +3106,6 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>6161.04</v>
       </c>
@@ -3299,8 +3139,6 @@
       <c r="F82" t="n">
         <v>0</v>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>6097.46</v>
       </c>
@@ -3334,8 +3172,6 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>5877.09</v>
       </c>
@@ -3369,8 +3205,6 @@
       <c r="F84" t="n">
         <v>0</v>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>5830.14</v>
       </c>
@@ -3404,8 +3238,6 @@
       <c r="F85" t="n">
         <v>0</v>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>5830.14</v>
       </c>
@@ -3439,8 +3271,6 @@
       <c r="F86" t="n">
         <v>0</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
         <v>6141.95</v>
       </c>
@@ -3474,8 +3304,6 @@
       <c r="F87" t="n">
         <v>0</v>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>11674.79</v>
       </c>
@@ -3509,8 +3337,6 @@
       <c r="F88" t="n">
         <v>0</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>5989.8</v>
       </c>
@@ -3544,8 +3370,6 @@
       <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>5865.27</v>
       </c>
@@ -6761,8 +6585,6 @@
       <c r="F164" t="n">
         <v>0</v>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>6066.43</v>
       </c>
@@ -6796,8 +6618,6 @@
       <c r="F165" t="n">
         <v>0</v>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>6659.08</v>
       </c>
@@ -6831,8 +6651,6 @@
       <c r="F166" t="n">
         <v>0</v>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>0</v>
       </c>
@@ -6909,8 +6727,6 @@
       <c r="F168" t="n">
         <v>0</v>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>7370.93</v>
       </c>
@@ -7030,8 +6846,6 @@
       <c r="F171" t="n">
         <v>0</v>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>8659.139999999999</v>
       </c>
@@ -7065,8 +6879,6 @@
       <c r="F172" t="n">
         <v>0</v>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>6272.26</v>
       </c>
@@ -7100,8 +6912,6 @@
       <c r="F173" t="n">
         <v>0</v>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>5998.92</v>
       </c>
@@ -7135,8 +6945,6 @@
       <c r="F174" t="n">
         <v>0</v>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>6632.31</v>
       </c>
@@ -7256,8 +7064,6 @@
       <c r="F177" t="n">
         <v>0</v>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>6429.41</v>
       </c>
@@ -7291,8 +7097,6 @@
       <c r="F178" t="n">
         <v>0</v>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>6317.39</v>
       </c>
@@ -7326,8 +7130,6 @@
       <c r="F179" t="n">
         <v>0</v>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>6235.65</v>
       </c>
@@ -7361,8 +7163,6 @@
       <c r="F180" t="n">
         <v>0</v>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>7470.12</v>
       </c>
@@ -7482,8 +7282,6 @@
       <c r="F183" t="n">
         <v>0</v>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>7637.84</v>
       </c>
@@ -7517,8 +7315,6 @@
       <c r="F184" t="n">
         <v>0</v>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>6203.62</v>
       </c>
@@ -7552,8 +7348,6 @@
       <c r="F185" t="n">
         <v>0</v>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>7325.57</v>
       </c>
@@ -7587,8 +7381,6 @@
       <c r="F186" t="n">
         <v>0</v>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
         <v>0</v>
       </c>
@@ -7622,8 +7414,6 @@
       <c r="F187" t="n">
         <v>0</v>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
         <v>6242.2</v>
       </c>
@@ -7657,8 +7447,6 @@
       <c r="F188" t="n">
         <v>0</v>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
         <v>6400.27</v>
       </c>
@@ -7692,8 +7480,6 @@
       <c r="F189" t="n">
         <v>0</v>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
         <v>9467.209999999999</v>
       </c>
@@ -7727,8 +7513,6 @@
       <c r="F190" t="n">
         <v>0</v>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
         <v>6125.87</v>
       </c>
@@ -7848,8 +7632,6 @@
       <c r="F193" t="n">
         <v>0</v>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
         <v>13790.7</v>
       </c>
@@ -8227,8 +8009,6 @@
       <c r="F202" t="n">
         <v>0</v>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
         <v>8374.92</v>
       </c>
@@ -8262,8 +8042,6 @@
       <c r="F203" t="n">
         <v>0</v>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
         <v>7970.58</v>
       </c>
@@ -8297,8 +8075,6 @@
       <c r="F204" t="n">
         <v>0</v>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
         <v>7813.5</v>
       </c>
@@ -8375,8 +8151,6 @@
       <c r="F206" t="n">
         <v>0</v>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
         <v>8353.780000000001</v>
       </c>
@@ -8797,8 +8571,6 @@
       <c r="F216" t="n">
         <v>0</v>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
         <v>9145.4</v>
       </c>
@@ -8875,8 +8647,6 @@
       <c r="F218" t="n">
         <v>0</v>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
         <v>6467.3</v>
       </c>
@@ -8996,8 +8766,6 @@
       <c r="F221" t="n">
         <v>0</v>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
         <v>11435.25</v>
       </c>
@@ -9074,8 +8842,6 @@
       <c r="F223" t="n">
         <v>0</v>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
         <v>6012.33</v>
       </c>
@@ -9109,8 +8875,6 @@
       <c r="F224" t="n">
         <v>0</v>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
         <v>6287.72</v>
       </c>
@@ -9144,8 +8908,6 @@
       <c r="F225" t="n">
         <v>0</v>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
         <v>6284.61</v>
       </c>
@@ -9179,8 +8941,6 @@
       <c r="F226" t="n">
         <v>0</v>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
         <v>6074.31</v>
       </c>
@@ -9214,8 +8974,6 @@
       <c r="F227" t="n">
         <v>0</v>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
         <v>6279.32</v>
       </c>
@@ -9249,8 +9007,6 @@
       <c r="F228" t="n">
         <v>0</v>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
         <v>5949.08</v>
       </c>
@@ -9284,8 +9040,6 @@
       <c r="F229" t="n">
         <v>0</v>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
         <v>5938</v>
       </c>
@@ -9319,8 +9073,6 @@
       <c r="F230" t="n">
         <v>0</v>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
         <v>6082</v>
       </c>
@@ -9354,8 +9106,6 @@
       <c r="F231" t="n">
         <v>0</v>
       </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
         <v>5835.67</v>
       </c>
@@ -9389,8 +9139,6 @@
       <c r="F232" t="n">
         <v>0</v>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
         <v>8666.75</v>
       </c>
@@ -9424,8 +9172,6 @@
       <c r="F233" t="n">
         <v>0</v>
       </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
         <v>6774.58</v>
       </c>
@@ -9459,8 +9205,6 @@
       <c r="F234" t="n">
         <v>0</v>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
         <v>6287.94</v>
       </c>
@@ -9494,8 +9238,6 @@
       <c r="F235" t="n">
         <v>0</v>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
         <v>6006.29</v>
       </c>
@@ -9529,8 +9271,6 @@
       <c r="F236" t="n">
         <v>0</v>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
         <v>8249.68</v>
       </c>
@@ -9564,8 +9304,6 @@
       <c r="F237" t="n">
         <v>0</v>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
         <v>7929.34</v>
       </c>
@@ -9599,8 +9337,6 @@
       <c r="F238" t="n">
         <v>0</v>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
         <v>11235.11</v>
       </c>
@@ -9634,8 +9370,6 @@
       <c r="F239" t="n">
         <v>0</v>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
         <v>12773.91</v>
       </c>
@@ -9669,8 +9403,6 @@
       <c r="F240" t="n">
         <v>0</v>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
         <v>7721.42</v>
       </c>
@@ -9704,8 +9436,6 @@
       <c r="F241" t="n">
         <v>0</v>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
         <v>7877.94</v>
       </c>
@@ -9739,8 +9469,6 @@
       <c r="F242" t="n">
         <v>0</v>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
         <v>28300.86</v>
       </c>
@@ -9774,8 +9502,6 @@
       <c r="F243" t="n">
         <v>0</v>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
         <v>7230.96</v>
       </c>
@@ -9809,8 +9535,6 @@
       <c r="F244" t="n">
         <v>0</v>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
         <v>8021.04</v>
       </c>
@@ -9844,8 +9568,6 @@
       <c r="F245" t="n">
         <v>0</v>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
         <v>22986.12</v>
       </c>
@@ -9922,8 +9644,6 @@
       <c r="F247" t="n">
         <v>0</v>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
         <v>19761.84</v>
       </c>
@@ -9957,8 +9677,6 @@
       <c r="F248" t="n">
         <v>0</v>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
         <v>9031.51</v>
       </c>
@@ -9992,8 +9710,6 @@
       <c r="F249" t="n">
         <v>0</v>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
         <v>8217.23</v>
       </c>
@@ -10027,8 +9743,6 @@
       <c r="F250" t="n">
         <v>0</v>
       </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
         <v>21716.75</v>
       </c>
@@ -10062,8 +9776,6 @@
       <c r="F251" t="n">
         <v>0</v>
       </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
         <v>7762.9</v>
       </c>
@@ -10097,8 +9809,6 @@
       <c r="F252" t="n">
         <v>0</v>
       </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
         <v>9885.129999999999</v>
       </c>
@@ -10132,8 +9842,6 @@
       <c r="F253" t="n">
         <v>0</v>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
         <v>6484.12</v>
       </c>
@@ -10167,8 +9875,6 @@
       <c r="F254" t="n">
         <v>0</v>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
         <v>19286.26</v>
       </c>
@@ -10202,8 +9908,6 @@
       <c r="F255" t="n">
         <v>0</v>
       </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
         <v>18529.96</v>
       </c>
@@ -10237,8 +9941,6 @@
       <c r="F256" t="n">
         <v>0</v>
       </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
         <v>0</v>
       </c>
@@ -10272,8 +9974,6 @@
       <c r="F257" t="n">
         <v>0</v>
       </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
         <v>8332.469999999999</v>
       </c>
@@ -10307,8 +10007,6 @@
       <c r="F258" t="n">
         <v>0</v>
       </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
         <v>6238.78</v>
       </c>
@@ -10342,8 +10040,6 @@
       <c r="F259" t="n">
         <v>0</v>
       </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
         <v>14426.78</v>
       </c>
@@ -10420,8 +10116,6 @@
       <c r="F261" t="n">
         <v>0</v>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
         <v>19480.38</v>
       </c>
@@ -10455,8 +10149,6 @@
       <c r="F262" t="n">
         <v>0</v>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
         <v>20982.04</v>
       </c>
@@ -10490,8 +10182,6 @@
       <c r="F263" t="n">
         <v>0</v>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
         <v>24034.98</v>
       </c>
@@ -10525,8 +10215,6 @@
       <c r="F264" t="n">
         <v>0</v>
       </c>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
         <v>12361.3</v>
       </c>
@@ -10560,8 +10248,6 @@
       <c r="F265" t="n">
         <v>0</v>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
         <v>10594</v>
       </c>
@@ -10595,8 +10281,6 @@
       <c r="F266" t="n">
         <v>0</v>
       </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
         <v>6598.14</v>
       </c>
@@ -10630,8 +10314,6 @@
       <c r="F267" t="n">
         <v>0</v>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
         <v>15048.82</v>
       </c>
@@ -10665,8 +10347,6 @@
       <c r="F268" t="n">
         <v>0</v>
       </c>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
         <v>6237.08</v>
       </c>
@@ -10700,8 +10380,6 @@
       <c r="F269" t="n">
         <v>0</v>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
         <v>0</v>
       </c>
@@ -10735,8 +10413,6 @@
       <c r="F270" t="n">
         <v>0</v>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
         <v>7949.94</v>
       </c>
@@ -10770,8 +10446,6 @@
       <c r="F271" t="n">
         <v>0</v>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
         <v>12787.65</v>
       </c>
@@ -10805,8 +10479,6 @@
       <c r="F272" t="n">
         <v>0</v>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
         <v>17942.98</v>
       </c>
@@ -10840,8 +10512,6 @@
       <c r="F273" t="n">
         <v>0</v>
       </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
         <v>6387.65</v>
       </c>
@@ -10875,8 +10545,6 @@
       <c r="F274" t="n">
         <v>0</v>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
         <v>8088.5</v>
       </c>
@@ -10910,8 +10578,6 @@
       <c r="F275" t="n">
         <v>0</v>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
         <v>12364.96</v>
       </c>
@@ -10945,8 +10611,6 @@
       <c r="F276" t="n">
         <v>0</v>
       </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
         <v>10649.88</v>
       </c>
@@ -10980,8 +10644,6 @@
       <c r="F277" t="n">
         <v>0</v>
       </c>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
         <v>16200.71</v>
       </c>
@@ -11015,8 +10677,6 @@
       <c r="F278" t="n">
         <v>0</v>
       </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
         <v>0</v>
       </c>
@@ -11050,8 +10710,6 @@
       <c r="F279" t="n">
         <v>0</v>
       </c>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
         <v>6782.78</v>
       </c>
@@ -11128,8 +10786,6 @@
       <c r="F281" t="n">
         <v>0</v>
       </c>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
         <v>13292.33</v>
       </c>
@@ -11163,8 +10819,6 @@
       <c r="F282" t="n">
         <v>0</v>
       </c>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
         <v>6205.68</v>
       </c>
@@ -11198,8 +10852,6 @@
       <c r="F283" t="n">
         <v>0</v>
       </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
         <v>6858.7</v>
       </c>
@@ -11233,8 +10885,6 @@
       <c r="F284" t="n">
         <v>0</v>
       </c>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="n">
         <v>6290.26</v>
       </c>
@@ -11268,8 +10918,6 @@
       <c r="F285" t="n">
         <v>0</v>
       </c>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="n">
         <v>15149.01</v>
       </c>
@@ -11303,8 +10951,6 @@
       <c r="F286" t="n">
         <v>0</v>
       </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="n">
         <v>13798.45</v>
       </c>
@@ -11338,8 +10984,6 @@
       <c r="F287" t="n">
         <v>0</v>
       </c>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="n">
         <v>6678.15</v>
       </c>
@@ -11416,8 +11060,6 @@
       <c r="F289" t="n">
         <v>0</v>
       </c>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="n">
         <v>15931.64</v>
       </c>
@@ -11451,8 +11093,6 @@
       <c r="F290" t="n">
         <v>0</v>
       </c>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="n">
         <v>8204.700000000001</v>
       </c>
@@ -11486,8 +11126,6 @@
       <c r="F291" t="n">
         <v>0</v>
       </c>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="n">
         <v>12624.24</v>
       </c>
@@ -11521,8 +11159,6 @@
       <c r="F292" t="n">
         <v>0</v>
       </c>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="n">
         <v>7594.65</v>
       </c>
@@ -11556,8 +11192,6 @@
       <c r="F293" t="n">
         <v>0</v>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="n">
         <v>14869.44</v>
       </c>
@@ -11591,8 +11225,6 @@
       <c r="F294" t="n">
         <v>0</v>
       </c>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="n">
         <v>9780.530000000001</v>
       </c>
@@ -11626,8 +11258,6 @@
       <c r="F295" t="n">
         <v>0</v>
       </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="n">
         <v>27053.33</v>
       </c>
@@ -11661,8 +11291,6 @@
       <c r="F296" t="n">
         <v>0</v>
       </c>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="n">
         <v>37587.98</v>
       </c>
@@ -11696,8 +11324,6 @@
       <c r="F297" t="n">
         <v>0</v>
       </c>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="n">
         <v>32325.28</v>
       </c>
@@ -11731,8 +11357,6 @@
       <c r="F298" t="n">
         <v>0</v>
       </c>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="n">
         <v>20527.21</v>
       </c>
@@ -11766,8 +11390,6 @@
       <c r="F299" t="n">
         <v>0</v>
       </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
         <v>27235.03</v>
       </c>
@@ -11801,8 +11423,6 @@
       <c r="F300" t="n">
         <v>0</v>
       </c>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="n">
         <v>39122.08</v>
       </c>
@@ -11836,8 +11456,6 @@
       <c r="F301" t="n">
         <v>0</v>
       </c>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="n">
         <v>24012.88</v>
       </c>
@@ -11871,8 +11489,6 @@
       <c r="F302" t="n">
         <v>0</v>
       </c>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="n">
         <v>27457.62</v>
       </c>
@@ -11906,8 +11522,6 @@
       <c r="F303" t="n">
         <v>0</v>
       </c>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="n">
         <v>29663.93</v>
       </c>
@@ -11941,8 +11555,6 @@
       <c r="F304" t="n">
         <v>0</v>
       </c>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="n">
         <v>34663.95</v>
       </c>
@@ -11976,8 +11588,6 @@
       <c r="F305" t="n">
         <v>0</v>
       </c>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="n">
         <v>42621.36</v>
       </c>
@@ -12011,8 +11621,6 @@
       <c r="F306" t="n">
         <v>0</v>
       </c>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="n">
         <v>30514.51</v>
       </c>
@@ -12046,8 +11654,6 @@
       <c r="F307" t="n">
         <v>0</v>
       </c>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="n">
         <v>17139.39</v>
       </c>
@@ -12081,8 +11687,6 @@
       <c r="F308" t="n">
         <v>0</v>
       </c>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="n">
         <v>30210.49</v>
       </c>
@@ -12116,8 +11720,6 @@
       <c r="F309" t="n">
         <v>0</v>
       </c>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="n">
         <v>25956.08</v>
       </c>
@@ -12151,8 +11753,6 @@
       <c r="F310" t="n">
         <v>0</v>
       </c>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="n">
         <v>34053.65</v>
       </c>
@@ -12186,8 +11786,6 @@
       <c r="F311" t="n">
         <v>0</v>
       </c>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="n">
         <v>20684.1</v>
       </c>
@@ -12221,8 +11819,6 @@
       <c r="F312" t="n">
         <v>0</v>
       </c>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="n">
         <v>30135.73</v>
       </c>
@@ -12256,8 +11852,6 @@
       <c r="F313" t="n">
         <v>0</v>
       </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="n">
         <v>46259.91</v>
       </c>
@@ -12291,8 +11885,6 @@
       <c r="F314" t="n">
         <v>0</v>
       </c>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="n">
         <v>22270.7</v>
       </c>
@@ -12369,8 +11961,6 @@
       <c r="F316" t="n">
         <v>0</v>
       </c>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="n">
         <v>30646.69</v>
       </c>
@@ -12404,8 +11994,6 @@
       <c r="F317" t="n">
         <v>0</v>
       </c>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
         <v>25937.64</v>
       </c>
@@ -12439,8 +12027,6 @@
       <c r="F318" t="n">
         <v>0</v>
       </c>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="n">
         <v>39543.71</v>
       </c>
@@ -12474,8 +12060,6 @@
       <c r="F319" t="n">
         <v>0</v>
       </c>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="n">
         <v>28416.81</v>
       </c>
@@ -12509,8 +12093,6 @@
       <c r="F320" t="n">
         <v>0</v>
       </c>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="n">
         <v>34878.55</v>
       </c>
@@ -12544,8 +12126,6 @@
       <c r="F321" t="n">
         <v>0</v>
       </c>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
         <v>30855.42</v>
       </c>
@@ -12579,8 +12159,6 @@
       <c r="F322" t="n">
         <v>0</v>
       </c>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="n">
         <v>25284.95</v>
       </c>
@@ -12614,8 +12192,6 @@
       <c r="F323" t="n">
         <v>0</v>
       </c>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="n">
         <v>29656.42</v>
       </c>
@@ -12649,8 +12225,6 @@
       <c r="F324" t="n">
         <v>0</v>
       </c>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="n">
         <v>21124.58</v>
       </c>
@@ -12684,8 +12258,6 @@
       <c r="F325" t="n">
         <v>0</v>
       </c>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="n">
         <v>31842.47</v>
       </c>
@@ -12719,8 +12291,6 @@
       <c r="F326" t="n">
         <v>0</v>
       </c>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="n">
         <v>19455.83</v>
       </c>
@@ -12754,8 +12324,6 @@
       <c r="F327" t="n">
         <v>0</v>
       </c>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="n">
         <v>23631.16</v>
       </c>
@@ -12789,8 +12357,6 @@
       <c r="F328" t="n">
         <v>0</v>
       </c>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="n">
         <v>16419.67</v>
       </c>
@@ -12824,8 +12390,6 @@
       <c r="F329" t="n">
         <v>0</v>
       </c>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="n">
         <v>36762.49</v>
       </c>
@@ -12859,8 +12423,6 @@
       <c r="F330" t="n">
         <v>0</v>
       </c>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="n">
         <v>43009.94</v>
       </c>
@@ -12894,8 +12456,6 @@
       <c r="F331" t="n">
         <v>0</v>
       </c>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="n">
         <v>20223.75</v>
       </c>
@@ -13020,7 +12580,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
         <v>31473.66</v>
       </c>
@@ -13059,7 +12618,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
         <v>38531.21</v>
       </c>
@@ -13098,7 +12656,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
         <v>23610.1</v>
       </c>
@@ -13137,7 +12694,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
         <v>21608.99</v>
       </c>
@@ -13176,7 +12732,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">
         <v>35244.59</v>
       </c>
@@ -13215,7 +12770,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="n">
         <v>47206.69</v>
       </c>
@@ -13254,7 +12808,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="n">
         <v>19263.37</v>
       </c>
@@ -13293,7 +12846,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="n">
         <v>1280.2</v>
       </c>
@@ -13332,7 +12884,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="n">
         <v>19688.37</v>
       </c>
@@ -13371,7 +12922,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="n">
         <v>31806.08</v>
       </c>
@@ -13410,7 +12960,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="n">
         <v>24826.64</v>
       </c>
@@ -13449,7 +12998,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="n">
         <v>21266.32</v>
       </c>
@@ -13488,7 +13036,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="n">
         <v>33364.9</v>
       </c>
@@ -13527,7 +13074,6 @@
           <t>8108</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="n">
         <v>32937.07</v>
       </c>
@@ -13561,8 +13107,6 @@
       <c r="F348" t="n">
         <v>0</v>
       </c>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="n">
         <v>28572.99</v>
       </c>
@@ -13596,8 +13140,6 @@
       <c r="F349" t="n">
         <v>0</v>
       </c>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="n">
         <v>42663.29</v>
       </c>
@@ -13631,8 +13173,6 @@
       <c r="F350" t="n">
         <v>0</v>
       </c>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="n">
         <v>25484.93</v>
       </c>
@@ -13666,8 +13206,6 @@
       <c r="F351" t="n">
         <v>0</v>
       </c>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="n">
         <v>35309.11</v>
       </c>
@@ -13744,8 +13282,6 @@
       <c r="F353" t="n">
         <v>0</v>
       </c>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="n">
         <v>9273.6</v>
       </c>
@@ -13779,8 +13315,6 @@
       <c r="F354" t="n">
         <v>0</v>
       </c>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="n">
         <v>21215.61</v>
       </c>
@@ -13814,8 +13348,6 @@
       <c r="F355" t="n">
         <v>0</v>
       </c>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="n">
         <v>17171.33</v>
       </c>
@@ -13849,8 +13381,6 @@
       <c r="F356" t="n">
         <v>0</v>
       </c>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="n">
         <v>8595.190000000001</v>
       </c>
@@ -13884,8 +13414,6 @@
       <c r="F357" t="n">
         <v>0</v>
       </c>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="n">
         <v>9228.67</v>
       </c>
@@ -13919,8 +13447,6 @@
       <c r="F358" t="n">
         <v>0</v>
       </c>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="n">
         <v>20452.77</v>
       </c>
@@ -13954,8 +13480,6 @@
       <c r="F359" t="n">
         <v>0</v>
       </c>
-      <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="n">
         <v>6707.27</v>
       </c>
@@ -13989,8 +13513,6 @@
       <c r="F360" t="n">
         <v>0</v>
       </c>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="n">
         <v>8364.549999999999</v>
       </c>
@@ -14024,8 +13546,6 @@
       <c r="F361" t="n">
         <v>0</v>
       </c>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="n">
         <v>15521.04</v>
       </c>
@@ -14059,8 +13579,6 @@
       <c r="F362" t="n">
         <v>0</v>
       </c>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="n">
         <v>16625.03</v>
       </c>
@@ -14094,8 +13612,6 @@
       <c r="F363" t="n">
         <v>0</v>
       </c>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="n">
         <v>15316.99</v>
       </c>
@@ -14129,8 +13645,6 @@
       <c r="F364" t="n">
         <v>0</v>
       </c>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="n">
         <v>13353.53</v>
       </c>
@@ -14164,8 +13678,6 @@
       <c r="F365" t="n">
         <v>0</v>
       </c>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="n">
         <v>9065.379999999999</v>
       </c>
@@ -14199,8 +13711,6 @@
       <c r="F366" t="n">
         <v>0</v>
       </c>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="n">
         <v>12573.08</v>
       </c>
@@ -14234,8 +13744,6 @@
       <c r="F367" t="n">
         <v>0</v>
       </c>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="n">
         <v>10089.17</v>
       </c>
@@ -14269,8 +13777,6 @@
       <c r="F368" t="n">
         <v>0</v>
       </c>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="n">
         <v>14821.14</v>
       </c>
@@ -14304,8 +13810,6 @@
       <c r="F369" t="n">
         <v>0</v>
       </c>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="n">
         <v>0</v>
       </c>
@@ -14339,8 +13843,6 @@
       <c r="F370" t="n">
         <v>0</v>
       </c>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="n">
         <v>5905.6</v>
       </c>
@@ -14374,8 +13876,6 @@
       <c r="F371" t="n">
         <v>0</v>
       </c>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="n">
         <v>23991.11</v>
       </c>
@@ -14409,8 +13909,6 @@
       <c r="F372" t="n">
         <v>0</v>
       </c>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="n">
         <v>8628.530000000001</v>
       </c>
@@ -14444,8 +13942,6 @@
       <c r="F373" t="n">
         <v>0</v>
       </c>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="n">
         <v>10756.83</v>
       </c>
@@ -14479,8 +13975,6 @@
       <c r="F374" t="n">
         <v>0</v>
       </c>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="n">
         <v>12234.38</v>
       </c>
@@ -14514,8 +14008,6 @@
       <c r="F375" t="n">
         <v>0</v>
       </c>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="n">
         <v>5846.65</v>
       </c>
@@ -14549,8 +14041,6 @@
       <c r="F376" t="n">
         <v>0</v>
       </c>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="n">
         <v>6608.69</v>
       </c>
@@ -14584,8 +14074,6 @@
       <c r="F377" t="n">
         <v>0</v>
       </c>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="n">
         <v>11855.56</v>
       </c>
@@ -14619,8 +14107,6 @@
       <c r="F378" t="n">
         <v>0</v>
       </c>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="n">
         <v>16368.94</v>
       </c>
@@ -14654,8 +14140,6 @@
       <c r="F379" t="n">
         <v>0</v>
       </c>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="n">
         <v>12715.4</v>
       </c>
@@ -14689,8 +14173,6 @@
       <c r="F380" t="n">
         <v>0</v>
       </c>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="n">
         <v>12044.43</v>
       </c>
@@ -14724,8 +14206,6 @@
       <c r="F381" t="n">
         <v>0</v>
       </c>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="n">
         <v>6514.78</v>
       </c>
@@ -14759,8 +14239,6 @@
       <c r="F382" t="n">
         <v>0</v>
       </c>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr"/>
       <c r="I382" t="n">
         <v>15905.28</v>
       </c>
@@ -14794,8 +14272,6 @@
       <c r="F383" t="n">
         <v>0</v>
       </c>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="n">
         <v>6024.8</v>
       </c>
@@ -14829,8 +14305,6 @@
       <c r="F384" t="n">
         <v>0</v>
       </c>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="n">
         <v>7471.64</v>
       </c>
@@ -14864,8 +14338,6 @@
       <c r="F385" t="n">
         <v>0</v>
       </c>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="n">
         <v>8434.57</v>
       </c>
@@ -14899,8 +14371,6 @@
       <c r="F386" t="n">
         <v>0</v>
       </c>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="n">
         <v>16140.26</v>
       </c>
@@ -14934,8 +14404,6 @@
       <c r="F387" t="n">
         <v>0</v>
       </c>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="n">
         <v>24127.75</v>
       </c>
@@ -14969,8 +14437,6 @@
       <c r="F388" t="n">
         <v>0</v>
       </c>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="n">
         <v>6706.59</v>
       </c>
@@ -15004,8 +14470,6 @@
       <c r="F389" t="n">
         <v>0</v>
       </c>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="n">
         <v>9118.1</v>
       </c>
@@ -15039,8 +14503,6 @@
       <c r="F390" t="n">
         <v>0</v>
       </c>
-      <c r="G390" t="inlineStr"/>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="n">
         <v>17471.89</v>
       </c>
@@ -15074,8 +14536,6 @@
       <c r="F391" t="n">
         <v>0</v>
       </c>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="n">
         <v>15882.59</v>
       </c>
@@ -15109,8 +14569,6 @@
       <c r="F392" t="n">
         <v>0</v>
       </c>
-      <c r="G392" t="inlineStr"/>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="n">
         <v>15097.76</v>
       </c>
@@ -15144,8 +14602,6 @@
       <c r="F393" t="n">
         <v>0</v>
       </c>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="n">
         <v>0</v>
       </c>
@@ -15179,8 +14635,6 @@
       <c r="F394" t="n">
         <v>0</v>
       </c>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="n">
         <v>7870.71</v>
       </c>
@@ -15214,8 +14668,6 @@
       <c r="F395" t="n">
         <v>0</v>
       </c>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="n">
         <v>12859.6</v>
       </c>
@@ -15249,8 +14701,6 @@
       <c r="F396" t="n">
         <v>0</v>
       </c>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="n">
         <v>12590</v>
       </c>
@@ -15284,8 +14734,6 @@
       <c r="F397" t="n">
         <v>0</v>
       </c>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="n">
         <v>5841.33</v>
       </c>
@@ -15319,8 +14767,6 @@
       <c r="F398" t="n">
         <v>0</v>
       </c>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="n">
         <v>6223.85</v>
       </c>
@@ -15354,8 +14800,6 @@
       <c r="F399" t="n">
         <v>0</v>
       </c>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="n">
         <v>11749.98</v>
       </c>
@@ -15389,8 +14833,6 @@
       <c r="F400" t="n">
         <v>0</v>
       </c>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="n">
         <v>6550.61</v>
       </c>
@@ -15424,8 +14866,6 @@
       <c r="F401" t="n">
         <v>0</v>
       </c>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="n">
         <v>7667.46</v>
       </c>
@@ -15459,8 +14899,6 @@
       <c r="F402" t="n">
         <v>0</v>
       </c>
-      <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="n">
         <v>5808.44</v>
       </c>
@@ -15494,8 +14932,6 @@
       <c r="F403" t="n">
         <v>0</v>
       </c>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="n">
         <v>18408.01</v>
       </c>
@@ -15529,8 +14965,6 @@
       <c r="F404" t="n">
         <v>0</v>
       </c>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="n">
         <v>9460.280000000001</v>
       </c>
@@ -15564,8 +14998,6 @@
       <c r="F405" t="n">
         <v>0</v>
       </c>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="n">
         <v>12555.56</v>
       </c>
@@ -15599,8 +15031,6 @@
       <c r="F406" t="n">
         <v>0</v>
       </c>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="n">
         <v>5913.83</v>
       </c>
@@ -15634,8 +15064,6 @@
       <c r="F407" t="n">
         <v>0</v>
       </c>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="n">
         <v>16573.96</v>
       </c>
@@ -15669,8 +15097,6 @@
       <c r="F408" t="n">
         <v>0</v>
       </c>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="n">
         <v>16070.14</v>
       </c>
@@ -15704,8 +15130,6 @@
       <c r="F409" t="n">
         <v>0</v>
       </c>
-      <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="n">
         <v>25632.07</v>
       </c>
@@ -15739,8 +15163,6 @@
       <c r="F410" t="n">
         <v>0</v>
       </c>
-      <c r="G410" t="inlineStr"/>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="n">
         <v>23162.54</v>
       </c>
@@ -15774,8 +15196,6 @@
       <c r="F411" t="n">
         <v>0</v>
       </c>
-      <c r="G411" t="inlineStr"/>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="n">
         <v>15602.42</v>
       </c>
@@ -15809,8 +15229,6 @@
       <c r="F412" t="n">
         <v>0</v>
       </c>
-      <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="n">
         <v>16284.26</v>
       </c>
@@ -15887,8 +15305,6 @@
       <c r="F414" t="n">
         <v>0</v>
       </c>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="n">
         <v>3835.24</v>
       </c>
@@ -15922,8 +15338,6 @@
       <c r="F415" t="n">
         <v>0</v>
       </c>
-      <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="n">
         <v>12780.34</v>
       </c>
@@ -16215,8 +15629,6 @@
       <c r="F422" t="n">
         <v>0</v>
       </c>
-      <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr"/>
       <c r="I422" t="n">
         <v>9485.469999999999</v>
       </c>
@@ -16293,8 +15705,6 @@
       <c r="F424" t="n">
         <v>0</v>
       </c>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
       <c r="I424" t="n">
         <v>13258.88</v>
       </c>
@@ -16414,8 +15824,6 @@
       <c r="F427" t="n">
         <v>0</v>
       </c>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
       <c r="I427" t="n">
         <v>10310.79</v>
       </c>
@@ -16449,8 +15857,6 @@
       <c r="F428" t="n">
         <v>0</v>
       </c>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="n">
         <v>16915.45</v>
       </c>
@@ -16828,8 +16234,6 @@
       <c r="F437" t="n">
         <v>0</v>
       </c>
-      <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr"/>
       <c r="I437" t="n">
         <v>9697.190000000001</v>
       </c>
@@ -16906,8 +16310,6 @@
       <c r="F439" t="n">
         <v>0</v>
       </c>
-      <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr"/>
       <c r="I439" t="n">
         <v>12524.22</v>
       </c>
@@ -16941,8 +16343,6 @@
       <c r="F440" t="n">
         <v>0</v>
       </c>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr"/>
       <c r="I440" t="n">
         <v>14257.24</v>
       </c>
@@ -16976,8 +16376,6 @@
       <c r="F441" t="n">
         <v>0</v>
       </c>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
       <c r="I441" t="n">
         <v>15863.3</v>
       </c>
@@ -17097,8 +16495,6 @@
       <c r="F444" t="n">
         <v>0</v>
       </c>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
       <c r="I444" t="n">
         <v>8524.959999999999</v>
       </c>
@@ -17132,8 +16528,6 @@
       <c r="F445" t="n">
         <v>0</v>
       </c>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
       <c r="I445" t="n">
         <v>12440.47</v>
       </c>
@@ -17210,8 +16604,6 @@
       <c r="F447" t="n">
         <v>0</v>
       </c>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
       <c r="I447" t="n">
         <v>22684.53</v>
       </c>
@@ -17288,8 +16680,6 @@
       <c r="F449" t="n">
         <v>0</v>
       </c>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr"/>
       <c r="I449" t="n">
         <v>15059.72</v>
       </c>
@@ -17323,8 +16713,6 @@
       <c r="F450" t="n">
         <v>0</v>
       </c>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
       <c r="I450" t="n">
         <v>13474.28</v>
       </c>
@@ -17444,8 +16832,6 @@
       <c r="F453" t="n">
         <v>0</v>
       </c>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
       <c r="I453" t="n">
         <v>12619.65</v>
       </c>
@@ -17479,8 +16865,6 @@
       <c r="F454" t="n">
         <v>0</v>
       </c>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
       <c r="I454" t="n">
         <v>12020.29</v>
       </c>
@@ -17514,8 +16898,6 @@
       <c r="F455" t="n">
         <v>0</v>
       </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
       <c r="I455" t="n">
         <v>12644.15</v>
       </c>
@@ -17635,8 +17017,6 @@
       <c r="F458" t="n">
         <v>0</v>
       </c>
-      <c r="G458" t="inlineStr"/>
-      <c r="H458" t="inlineStr"/>
       <c r="I458" t="n">
         <v>10002.86</v>
       </c>
@@ -17756,8 +17136,6 @@
       <c r="F461" t="n">
         <v>0</v>
       </c>
-      <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
       <c r="I461" t="n">
         <v>16991.66</v>
       </c>
@@ -17834,8 +17212,6 @@
       <c r="F463" t="n">
         <v>0</v>
       </c>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
       <c r="I463" t="n">
         <v>12365.59</v>
       </c>
@@ -17912,8 +17288,6 @@
       <c r="F465" t="n">
         <v>0</v>
       </c>
-      <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
       <c r="I465" t="n">
         <v>8296.26</v>
       </c>
@@ -17947,8 +17321,6 @@
       <c r="F466" t="n">
         <v>0</v>
       </c>
-      <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
       <c r="I466" t="n">
         <v>11991.97</v>
       </c>
@@ -17982,8 +17354,6 @@
       <c r="F467" t="n">
         <v>0</v>
       </c>
-      <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr"/>
       <c r="I467" t="n">
         <v>10205.27</v>
       </c>
@@ -18017,8 +17387,6 @@
       <c r="F468" t="n">
         <v>0</v>
       </c>
-      <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
       <c r="I468" t="n">
         <v>8553.440000000001</v>
       </c>
@@ -18052,8 +17420,6 @@
       <c r="F469" t="n">
         <v>0</v>
       </c>
-      <c r="G469" t="inlineStr"/>
-      <c r="H469" t="inlineStr"/>
       <c r="I469" t="n">
         <v>8904.4</v>
       </c>
@@ -18087,8 +17453,6 @@
       <c r="F470" t="n">
         <v>0</v>
       </c>
-      <c r="G470" t="inlineStr"/>
-      <c r="H470" t="inlineStr"/>
       <c r="I470" t="n">
         <v>10242.5</v>
       </c>
@@ -18122,8 +17486,6 @@
       <c r="F471" t="n">
         <v>0</v>
       </c>
-      <c r="G471" t="inlineStr"/>
-      <c r="H471" t="inlineStr"/>
       <c r="I471" t="n">
         <v>7779.33</v>
       </c>
@@ -18157,8 +17519,6 @@
       <c r="F472" t="n">
         <v>0</v>
       </c>
-      <c r="G472" t="inlineStr"/>
-      <c r="H472" t="inlineStr"/>
       <c r="I472" t="n">
         <v>8953.42</v>
       </c>
@@ -18192,8 +17552,6 @@
       <c r="F473" t="n">
         <v>0</v>
       </c>
-      <c r="G473" t="inlineStr"/>
-      <c r="H473" t="inlineStr"/>
       <c r="I473" t="n">
         <v>7630.42</v>
       </c>
@@ -18270,8 +17628,6 @@
       <c r="F475" t="n">
         <v>0</v>
       </c>
-      <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr"/>
       <c r="I475" t="n">
         <v>11687.51</v>
       </c>
@@ -18305,8 +17661,6 @@
       <c r="F476" t="n">
         <v>0</v>
       </c>
-      <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
       <c r="I476" t="n">
         <v>10342.44</v>
       </c>
@@ -18340,8 +17694,6 @@
       <c r="F477" t="n">
         <v>0</v>
       </c>
-      <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
       <c r="I477" t="n">
         <v>9199.040000000001</v>
       </c>
@@ -18375,8 +17727,6 @@
       <c r="F478" t="n">
         <v>0</v>
       </c>
-      <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
       <c r="I478" t="n">
         <v>7661.75</v>
       </c>
@@ -18410,8 +17760,6 @@
       <c r="F479" t="n">
         <v>0</v>
       </c>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
       <c r="I479" t="n">
         <v>8561.110000000001</v>
       </c>
@@ -18445,8 +17793,6 @@
       <c r="F480" t="n">
         <v>0</v>
       </c>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
       <c r="I480" t="n">
         <v>11541.08</v>
       </c>
@@ -18480,8 +17826,6 @@
       <c r="F481" t="n">
         <v>0</v>
       </c>
-      <c r="G481" t="inlineStr"/>
-      <c r="H481" t="inlineStr"/>
       <c r="I481" t="n">
         <v>6784.28</v>
       </c>
@@ -18515,8 +17859,6 @@
       <c r="F482" t="n">
         <v>0</v>
       </c>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
       <c r="I482" t="n">
         <v>7931.52</v>
       </c>
@@ -18550,8 +17892,6 @@
       <c r="F483" t="n">
         <v>0</v>
       </c>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
       <c r="I483" t="n">
         <v>11239.82</v>
       </c>
@@ -18585,8 +17925,6 @@
       <c r="F484" t="n">
         <v>0</v>
       </c>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
       <c r="I484" t="n">
         <v>7430.51</v>
       </c>
@@ -18620,8 +17958,6 @@
       <c r="F485" t="n">
         <v>0</v>
       </c>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
       <c r="I485" t="n">
         <v>9380.09</v>
       </c>
@@ -18655,8 +17991,6 @@
       <c r="F486" t="n">
         <v>0</v>
       </c>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
       <c r="I486" t="n">
         <v>7692.52</v>
       </c>
@@ -18690,8 +18024,6 @@
       <c r="F487" t="n">
         <v>0</v>
       </c>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
       <c r="I487" t="n">
         <v>6540.08</v>
       </c>
@@ -18725,8 +18057,6 @@
       <c r="F488" t="n">
         <v>0</v>
       </c>
-      <c r="G488" t="inlineStr"/>
-      <c r="H488" t="inlineStr"/>
       <c r="I488" t="n">
         <v>10136.02</v>
       </c>
@@ -18760,8 +18090,6 @@
       <c r="F489" t="n">
         <v>0</v>
       </c>
-      <c r="G489" t="inlineStr"/>
-      <c r="H489" t="inlineStr"/>
       <c r="I489" t="n">
         <v>7240.02</v>
       </c>
@@ -18795,8 +18123,6 @@
       <c r="F490" t="n">
         <v>0</v>
       </c>
-      <c r="G490" t="inlineStr"/>
-      <c r="H490" t="inlineStr"/>
       <c r="I490" t="n">
         <v>9338.18</v>
       </c>
@@ -18830,8 +18156,6 @@
       <c r="F491" t="n">
         <v>0</v>
       </c>
-      <c r="G491" t="inlineStr"/>
-      <c r="H491" t="inlineStr"/>
       <c r="I491" t="n">
         <v>10358.86</v>
       </c>
@@ -18865,8 +18189,6 @@
       <c r="F492" t="n">
         <v>0</v>
       </c>
-      <c r="G492" t="inlineStr"/>
-      <c r="H492" t="inlineStr"/>
       <c r="I492" t="n">
         <v>6308.95</v>
       </c>
@@ -18900,8 +18222,6 @@
       <c r="F493" t="n">
         <v>0</v>
       </c>
-      <c r="G493" t="inlineStr"/>
-      <c r="H493" t="inlineStr"/>
       <c r="I493" t="n">
         <v>7388.26</v>
       </c>
@@ -18935,8 +18255,6 @@
       <c r="F494" t="n">
         <v>0</v>
       </c>
-      <c r="G494" t="inlineStr"/>
-      <c r="H494" t="inlineStr"/>
       <c r="I494" t="n">
         <v>6931.36</v>
       </c>
@@ -18970,8 +18288,6 @@
       <c r="F495" t="n">
         <v>0</v>
       </c>
-      <c r="G495" t="inlineStr"/>
-      <c r="H495" t="inlineStr"/>
       <c r="I495" t="n">
         <v>8333.67</v>
       </c>
@@ -19005,8 +18321,6 @@
       <c r="F496" t="n">
         <v>0</v>
       </c>
-      <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
       <c r="I496" t="n">
         <v>6428.97</v>
       </c>
@@ -19040,8 +18354,6 @@
       <c r="F497" t="n">
         <v>0</v>
       </c>
-      <c r="G497" t="inlineStr"/>
-      <c r="H497" t="inlineStr"/>
       <c r="I497" t="n">
         <v>7494.9</v>
       </c>
@@ -19075,8 +18387,6 @@
       <c r="F498" t="n">
         <v>0</v>
       </c>
-      <c r="G498" t="inlineStr"/>
-      <c r="H498" t="inlineStr"/>
       <c r="I498" t="n">
         <v>8237.690000000001</v>
       </c>
@@ -19110,8 +18420,6 @@
       <c r="F499" t="n">
         <v>0</v>
       </c>
-      <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
       <c r="I499" t="n">
         <v>10863.03</v>
       </c>
@@ -19145,8 +18453,6 @@
       <c r="F500" t="n">
         <v>0</v>
       </c>
-      <c r="G500" t="inlineStr"/>
-      <c r="H500" t="inlineStr"/>
       <c r="I500" t="n">
         <v>12016.67</v>
       </c>
@@ -19180,8 +18486,6 @@
       <c r="F501" t="n">
         <v>0</v>
       </c>
-      <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
         <v>6426.3</v>
       </c>
@@ -19215,8 +18519,6 @@
       <c r="F502" t="n">
         <v>0</v>
       </c>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
         <v>8933.389999999999</v>
       </c>
@@ -19250,8 +18552,6 @@
       <c r="F503" t="n">
         <v>0</v>
       </c>
-      <c r="G503" t="inlineStr"/>
-      <c r="H503" t="inlineStr"/>
       <c r="I503" t="n">
         <v>10716.15</v>
       </c>
@@ -19285,8 +18585,6 @@
       <c r="F504" t="n">
         <v>0</v>
       </c>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
       <c r="I504" t="n">
         <v>12711.43</v>
       </c>
@@ -19320,8 +18618,6 @@
       <c r="F505" t="n">
         <v>0</v>
       </c>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
         <v>10086.59</v>
       </c>
@@ -19355,8 +18651,6 @@
       <c r="F506" t="n">
         <v>0</v>
       </c>
-      <c r="G506" t="inlineStr"/>
-      <c r="H506" t="inlineStr"/>
       <c r="I506" t="n">
         <v>7381.85</v>
       </c>
@@ -19390,8 +18684,6 @@
       <c r="F507" t="n">
         <v>0</v>
       </c>
-      <c r="G507" t="inlineStr"/>
-      <c r="H507" t="inlineStr"/>
       <c r="I507" t="n">
         <v>0</v>
       </c>
@@ -19511,8 +18803,6 @@
       <c r="F510" t="n">
         <v>0</v>
       </c>
-      <c r="G510" t="inlineStr"/>
-      <c r="H510" t="inlineStr"/>
       <c r="I510" t="n">
         <v>6441.89</v>
       </c>
@@ -19546,8 +18836,6 @@
       <c r="F511" t="n">
         <v>0</v>
       </c>
-      <c r="G511" t="inlineStr"/>
-      <c r="H511" t="inlineStr"/>
       <c r="I511" t="n">
         <v>7231.93</v>
       </c>
@@ -19581,8 +18869,6 @@
       <c r="F512" t="n">
         <v>0</v>
       </c>
-      <c r="G512" t="inlineStr"/>
-      <c r="H512" t="inlineStr"/>
       <c r="I512" t="n">
         <v>6506.63</v>
       </c>
@@ -19616,8 +18902,6 @@
       <c r="F513" t="n">
         <v>0</v>
       </c>
-      <c r="G513" t="inlineStr"/>
-      <c r="H513" t="inlineStr"/>
       <c r="I513" t="n">
         <v>9995.209999999999</v>
       </c>
@@ -19651,8 +18935,6 @@
       <c r="F514" t="n">
         <v>0</v>
       </c>
-      <c r="G514" t="inlineStr"/>
-      <c r="H514" t="inlineStr"/>
       <c r="I514" t="n">
         <v>7858.28</v>
       </c>
@@ -19686,8 +18968,6 @@
       <c r="F515" t="n">
         <v>0</v>
       </c>
-      <c r="G515" t="inlineStr"/>
-      <c r="H515" t="inlineStr"/>
       <c r="I515" t="n">
         <v>0</v>
       </c>
@@ -19764,8 +19044,6 @@
       <c r="F517" t="n">
         <v>0</v>
       </c>
-      <c r="G517" t="inlineStr"/>
-      <c r="H517" t="inlineStr"/>
       <c r="I517" t="n">
         <v>8672.059999999999</v>
       </c>
@@ -19842,8 +19120,6 @@
       <c r="F519" t="n">
         <v>0</v>
       </c>
-      <c r="G519" t="inlineStr"/>
-      <c r="H519" t="inlineStr"/>
       <c r="I519" t="n">
         <v>9945.98</v>
       </c>
@@ -19877,8 +19153,6 @@
       <c r="F520" t="n">
         <v>0</v>
       </c>
-      <c r="G520" t="inlineStr"/>
-      <c r="H520" t="inlineStr"/>
       <c r="I520" t="n">
         <v>8366.99</v>
       </c>
@@ -19912,8 +19186,6 @@
       <c r="F521" t="n">
         <v>0</v>
       </c>
-      <c r="G521" t="inlineStr"/>
-      <c r="H521" t="inlineStr"/>
       <c r="I521" t="n">
         <v>8556.110000000001</v>
       </c>
@@ -26397,8 +25669,6 @@
       <c r="F672" t="n">
         <v>0</v>
       </c>
-      <c r="G672" t="inlineStr"/>
-      <c r="H672" t="inlineStr"/>
       <c r="I672" t="n">
         <v>2913.63</v>
       </c>
@@ -26432,8 +25702,6 @@
       <c r="F673" t="n">
         <v>0</v>
       </c>
-      <c r="G673" t="inlineStr"/>
-      <c r="H673" t="inlineStr"/>
       <c r="I673" t="n">
         <v>300.01</v>
       </c>
@@ -26467,8 +25735,6 @@
       <c r="F674" t="n">
         <v>0</v>
       </c>
-      <c r="G674" t="inlineStr"/>
-      <c r="H674" t="inlineStr"/>
       <c r="I674" t="n">
         <v>354.21</v>
       </c>
@@ -26502,8 +25768,6 @@
       <c r="F675" t="n">
         <v>0</v>
       </c>
-      <c r="G675" t="inlineStr"/>
-      <c r="H675" t="inlineStr"/>
       <c r="I675" t="n">
         <v>594.66</v>
       </c>
@@ -26537,8 +25801,6 @@
       <c r="F676" t="n">
         <v>0</v>
       </c>
-      <c r="G676" t="inlineStr"/>
-      <c r="H676" t="inlineStr"/>
       <c r="I676" t="n">
         <v>1998.06</v>
       </c>
@@ -26572,8 +25834,6 @@
       <c r="F677" t="n">
         <v>0</v>
       </c>
-      <c r="G677" t="inlineStr"/>
-      <c r="H677" t="inlineStr"/>
       <c r="I677" t="n">
         <v>1288.26</v>
       </c>
@@ -26607,8 +25867,6 @@
       <c r="F678" t="n">
         <v>0</v>
       </c>
-      <c r="G678" t="inlineStr"/>
-      <c r="H678" t="inlineStr"/>
       <c r="I678" t="n">
         <v>972.9400000000001</v>
       </c>
@@ -26642,8 +25900,6 @@
       <c r="F679" t="n">
         <v>0</v>
       </c>
-      <c r="G679" t="inlineStr"/>
-      <c r="H679" t="inlineStr"/>
       <c r="I679" t="n">
         <v>431.53</v>
       </c>
@@ -26677,8 +25933,6 @@
       <c r="F680" t="n">
         <v>0</v>
       </c>
-      <c r="G680" t="inlineStr"/>
-      <c r="H680" t="inlineStr"/>
       <c r="I680" t="n">
         <v>466.79</v>
       </c>
@@ -26712,8 +25966,6 @@
       <c r="F681" t="n">
         <v>0</v>
       </c>
-      <c r="G681" t="inlineStr"/>
-      <c r="H681" t="inlineStr"/>
       <c r="I681" t="n">
         <v>341.13</v>
       </c>
@@ -26790,8 +26042,6 @@
       <c r="F683" t="n">
         <v>0</v>
       </c>
-      <c r="G683" t="inlineStr"/>
-      <c r="H683" t="inlineStr"/>
       <c r="I683" t="n">
         <v>8213.59</v>
       </c>
@@ -26825,8 +26075,6 @@
       <c r="F684" t="n">
         <v>0</v>
       </c>
-      <c r="G684" t="inlineStr"/>
-      <c r="H684" t="inlineStr"/>
       <c r="I684" t="n">
         <v>7301.33</v>
       </c>
@@ -45522,7 +44770,6 @@
       <c r="F1119" t="n">
         <v>16333.64</v>
       </c>
-      <c r="G1119" t="inlineStr"/>
       <c r="H1119" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45604,7 +44851,6 @@
       <c r="F1121" t="n">
         <v>16100.51</v>
       </c>
-      <c r="G1121" t="inlineStr"/>
       <c r="H1121" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45643,7 +44889,6 @@
       <c r="F1122" t="n">
         <v>15475.65</v>
       </c>
-      <c r="G1122" t="inlineStr"/>
       <c r="H1122" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45682,7 +44927,6 @@
       <c r="F1123" t="n">
         <v>13431.73</v>
       </c>
-      <c r="G1123" t="inlineStr"/>
       <c r="H1123" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45721,7 +44965,6 @@
       <c r="F1124" t="n">
         <v>15897.86</v>
       </c>
-      <c r="G1124" t="inlineStr"/>
       <c r="H1124" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45760,7 +45003,6 @@
       <c r="F1125" t="n">
         <v>15991</v>
       </c>
-      <c r="G1125" t="inlineStr"/>
       <c r="H1125" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -45842,7 +45084,6 @@
       <c r="F1127" t="n">
         <v>11881.85</v>
       </c>
-      <c r="G1127" t="inlineStr"/>
       <c r="H1127" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46053,7 +45294,6 @@
       <c r="F1132" t="n">
         <v>10775.55</v>
       </c>
-      <c r="G1132" t="inlineStr"/>
       <c r="H1132" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46178,7 +45418,6 @@
       <c r="F1135" t="n">
         <v>15096.98</v>
       </c>
-      <c r="G1135" t="inlineStr"/>
       <c r="H1135" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46389,7 +45628,6 @@
       <c r="F1140" t="n">
         <v>8779.970000000001</v>
       </c>
-      <c r="G1140" t="inlineStr"/>
       <c r="H1140" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46428,7 +45666,6 @@
       <c r="F1141" t="n">
         <v>13258.07</v>
       </c>
-      <c r="G1141" t="inlineStr"/>
       <c r="H1141" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46596,7 +45833,6 @@
       <c r="F1145" t="n">
         <v>14935.86</v>
       </c>
-      <c r="G1145" t="inlineStr"/>
       <c r="H1145" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46635,7 +45871,6 @@
       <c r="F1146" t="n">
         <v>15043.05</v>
       </c>
-      <c r="G1146" t="inlineStr"/>
       <c r="H1146" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46760,7 +45995,6 @@
       <c r="F1149" t="n">
         <v>10942.03</v>
       </c>
-      <c r="G1149" t="inlineStr"/>
       <c r="H1149" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46842,7 +46076,6 @@
       <c r="F1151" t="n">
         <v>13876.9</v>
       </c>
-      <c r="G1151" t="inlineStr"/>
       <c r="H1151" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -47182,7 +46415,6 @@
       <c r="F1159" t="n">
         <v>15275.3</v>
       </c>
-      <c r="G1159" t="inlineStr"/>
       <c r="H1159" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47307,7 +46539,6 @@
       <c r="F1162" t="n">
         <v>16226.51</v>
       </c>
-      <c r="G1162" t="inlineStr"/>
       <c r="H1162" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47346,7 +46577,6 @@
       <c r="F1163" t="n">
         <v>13321.35</v>
       </c>
-      <c r="G1163" t="inlineStr"/>
       <c r="H1163" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47686,7 +46916,6 @@
       <c r="F1171" t="n">
         <v>17069.44</v>
       </c>
-      <c r="G1171" t="inlineStr"/>
       <c r="H1171" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47725,7 +46954,6 @@
       <c r="F1172" t="n">
         <v>16499.25</v>
       </c>
-      <c r="G1172" t="inlineStr"/>
       <c r="H1172" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47893,7 +47121,6 @@
       <c r="F1176" t="n">
         <v>17056.44</v>
       </c>
-      <c r="G1176" t="inlineStr"/>
       <c r="H1176" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -47975,7 +47202,6 @@
       <c r="F1178" t="n">
         <v>16986.84</v>
       </c>
-      <c r="G1178" t="inlineStr"/>
       <c r="H1178" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48014,7 +47240,6 @@
       <c r="F1179" t="n">
         <v>16800.32</v>
       </c>
-      <c r="G1179" t="inlineStr"/>
       <c r="H1179" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48053,7 +47278,6 @@
       <c r="F1180" t="n">
         <v>16190.19</v>
       </c>
-      <c r="G1180" t="inlineStr"/>
       <c r="H1180" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48092,7 +47316,6 @@
       <c r="F1181" t="n">
         <v>16926.34</v>
       </c>
-      <c r="G1181" t="inlineStr"/>
       <c r="H1181" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48131,7 +47354,6 @@
       <c r="F1182" t="n">
         <v>16954.16</v>
       </c>
-      <c r="G1182" t="inlineStr"/>
       <c r="H1182" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48213,7 +47435,6 @@
       <c r="F1184" t="n">
         <v>15727.53</v>
       </c>
-      <c r="G1184" t="inlineStr"/>
       <c r="H1184" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48424,7 +47645,6 @@
       <c r="F1189" t="n">
         <v>15397.3</v>
       </c>
-      <c r="G1189" t="inlineStr"/>
       <c r="H1189" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48549,7 +47769,6 @@
       <c r="F1192" t="n">
         <v>16687.27</v>
       </c>
-      <c r="G1192" t="inlineStr"/>
       <c r="H1192" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48760,7 +47979,6 @@
       <c r="F1197" t="n">
         <v>14801.62</v>
       </c>
-      <c r="G1197" t="inlineStr"/>
       <c r="H1197" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48799,7 +48017,6 @@
       <c r="F1198" t="n">
         <v>16138.38</v>
       </c>
-      <c r="G1198" t="inlineStr"/>
       <c r="H1198" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48967,7 +48184,6 @@
       <c r="F1202" t="n">
         <v>16639.2</v>
       </c>
-      <c r="G1202" t="inlineStr"/>
       <c r="H1202" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -49006,7 +48222,6 @@
       <c r="F1203" t="n">
         <v>16671.19</v>
       </c>
-      <c r="G1203" t="inlineStr"/>
       <c r="H1203" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -49561,7 +48776,6 @@
       <c r="F1216" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1216" t="inlineStr"/>
       <c r="H1216" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49600,7 +48814,6 @@
       <c r="F1217" t="n">
         <v>5380.03</v>
       </c>
-      <c r="G1217" t="inlineStr"/>
       <c r="H1217" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49639,7 +48852,6 @@
       <c r="F1218" t="n">
         <v>4768.08</v>
       </c>
-      <c r="G1218" t="inlineStr"/>
       <c r="H1218" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49678,7 +48890,6 @@
       <c r="F1219" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1219" t="inlineStr"/>
       <c r="H1219" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49717,7 +48928,6 @@
       <c r="F1220" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1220" t="inlineStr"/>
       <c r="H1220" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49756,7 +48966,6 @@
       <c r="F1221" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1221" t="inlineStr"/>
       <c r="H1221" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49795,7 +49004,6 @@
       <c r="F1222" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1222" t="inlineStr"/>
       <c r="H1222" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49834,7 +49042,6 @@
       <c r="F1223" t="n">
         <v>4972.07</v>
       </c>
-      <c r="G1223" t="inlineStr"/>
       <c r="H1223" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49873,7 +49080,6 @@
       <c r="F1224" t="n">
         <v>5584.02</v>
       </c>
-      <c r="G1224" t="inlineStr"/>
       <c r="H1224" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49912,8 +49118,6 @@
       <c r="F1225" t="n">
         <v>0</v>
       </c>
-      <c r="G1225" t="inlineStr"/>
-      <c r="H1225" t="inlineStr"/>
       <c r="I1225" t="n">
         <v>380048.26</v>
       </c>
@@ -49947,7 +49151,6 @@
       <c r="F1226" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1226" t="inlineStr"/>
       <c r="H1226" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49986,7 +49189,6 @@
       <c r="F1227" t="n">
         <v>4768.08</v>
       </c>
-      <c r="G1227" t="inlineStr"/>
       <c r="H1227" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50025,7 +49227,6 @@
       <c r="F1228" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1228" t="inlineStr"/>
       <c r="H1228" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50064,7 +49265,6 @@
       <c r="F1229" t="n">
         <v>4972.07</v>
       </c>
-      <c r="G1229" t="inlineStr"/>
       <c r="H1229" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50103,7 +49303,6 @@
       <c r="F1230" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1230" t="inlineStr"/>
       <c r="H1230" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50142,7 +49341,6 @@
       <c r="F1231" t="n">
         <v>5380.03</v>
       </c>
-      <c r="G1231" t="inlineStr"/>
       <c r="H1231" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50181,7 +49379,6 @@
       <c r="F1232" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1232" t="inlineStr"/>
       <c r="H1232" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50220,7 +49417,6 @@
       <c r="F1233" t="n">
         <v>5584.02</v>
       </c>
-      <c r="G1233" t="inlineStr"/>
       <c r="H1233" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50259,7 +49455,6 @@
       <c r="F1234" t="n">
         <v>4972.07</v>
       </c>
-      <c r="G1234" t="inlineStr"/>
       <c r="H1234" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50298,7 +49493,6 @@
       <c r="F1235" t="n">
         <v>4768.08</v>
       </c>
-      <c r="G1235" t="inlineStr"/>
       <c r="H1235" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50337,7 +49531,6 @@
       <c r="F1236" t="n">
         <v>5584.02</v>
       </c>
-      <c r="G1236" t="inlineStr"/>
       <c r="H1236" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -50376,7 +49569,6 @@
       <c r="F1237" t="n">
         <v>5176.05</v>
       </c>
-      <c r="G1237" t="inlineStr"/>
       <c r="H1237" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -56134,7 +55326,6 @@
       <c r="F1371" t="n">
         <v>5759.53</v>
       </c>
-      <c r="G1371" t="inlineStr"/>
       <c r="H1371" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -56173,7 +55364,6 @@
       <c r="F1372" t="n">
         <v>5733.1</v>
       </c>
-      <c r="G1372" t="inlineStr"/>
       <c r="H1372" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -56556,7 +55746,6 @@
       <c r="F1381" t="n">
         <v>5621.27</v>
       </c>
-      <c r="G1381" t="inlineStr"/>
       <c r="H1381" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -56724,7 +55913,6 @@
       <c r="F1385" t="n">
         <v>5759.53</v>
       </c>
-      <c r="G1385" t="inlineStr"/>
       <c r="H1385" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -61541,7 +60729,6 @@
           <t>0532</t>
         </is>
       </c>
-      <c r="H1497" t="inlineStr"/>
       <c r="I1497" t="n">
         <v>6227.01</v>
       </c>
@@ -61575,8 +60762,6 @@
       <c r="F1498" t="n">
         <v>0</v>
       </c>
-      <c r="G1498" t="inlineStr"/>
-      <c r="H1498" t="inlineStr"/>
       <c r="I1498" t="n">
         <v>5917.13</v>
       </c>
@@ -61610,8 +60795,6 @@
       <c r="F1499" t="n">
         <v>0</v>
       </c>
-      <c r="G1499" t="inlineStr"/>
-      <c r="H1499" t="inlineStr"/>
       <c r="I1499" t="n">
         <v>5924.67</v>
       </c>
@@ -61645,8 +60828,6 @@
       <c r="F1500" t="n">
         <v>0</v>
       </c>
-      <c r="G1500" t="inlineStr"/>
-      <c r="H1500" t="inlineStr"/>
       <c r="I1500" t="n">
         <v>11938.39</v>
       </c>
@@ -61680,8 +60861,6 @@
       <c r="F1501" t="n">
         <v>0</v>
       </c>
-      <c r="G1501" t="inlineStr"/>
-      <c r="H1501" t="inlineStr"/>
       <c r="I1501" t="n">
         <v>7729.9</v>
       </c>
@@ -61715,8 +60894,6 @@
       <c r="F1502" t="n">
         <v>0</v>
       </c>
-      <c r="G1502" t="inlineStr"/>
-      <c r="H1502" t="inlineStr"/>
       <c r="I1502" t="n">
         <v>6021.26</v>
       </c>
@@ -61789,10 +60966,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>11801005</t>
-        </is>
+      <c r="A2" t="n">
+        <v>11801005</v>
       </c>
       <c r="B2" t="n">
         <v>723159.73</v>
@@ -61822,10 +60997,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>21110005</t>
-        </is>
+      <c r="A3" t="n">
+        <v>21110005</v>
       </c>
       <c r="B3" t="n">
         <v>224030.64</v>
@@ -61855,10 +61028,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>21410001</t>
-        </is>
+      <c r="A4" t="n">
+        <v>21410001</v>
       </c>
       <c r="B4" t="n">
         <v>3411242.91</v>
@@ -61888,10 +61059,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>21410002</t>
-        </is>
+      <c r="A5" t="n">
+        <v>21410002</v>
       </c>
       <c r="B5" t="n">
         <v>153358.85</v>
@@ -61921,10 +61090,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>21410003</t>
-        </is>
+      <c r="A6" t="n">
+        <v>21410003</v>
       </c>
       <c r="B6" t="n">
         <v>56965.79</v>
@@ -61954,10 +61121,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>21410004</t>
-        </is>
+      <c r="A7" t="n">
+        <v>21410004</v>
       </c>
       <c r="B7" t="n">
         <v>11963.42</v>
@@ -61987,10 +61152,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>21410005</t>
-        </is>
+      <c r="A8" t="n">
+        <v>21410005</v>
       </c>
       <c r="B8" t="n">
         <v>212377.63</v>
@@ -62020,10 +61183,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>21410006</t>
-        </is>
+      <c r="A9" t="n">
+        <v>21410006</v>
       </c>
       <c r="B9" t="n">
         <v>310135.48</v>
@@ -62053,10 +61214,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>21410009</t>
-        </is>
+      <c r="A10" t="n">
+        <v>21410009</v>
       </c>
       <c r="B10" t="n">
         <v>90728.28</v>
@@ -62086,10 +61245,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>21420002</t>
-        </is>
+      <c r="A11" t="n">
+        <v>21420002</v>
       </c>
       <c r="B11" t="n">
         <v>775796.26</v>
@@ -62119,10 +61276,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>21420003</t>
-        </is>
+      <c r="A12" t="n">
+        <v>21420003</v>
       </c>
       <c r="B12" t="n">
         <v>1668494.57</v>
@@ -62152,10 +61307,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>21420004</t>
-        </is>
+      <c r="A13" t="n">
+        <v>21420004</v>
       </c>
       <c r="B13" t="n">
         <v>634721.78</v>
@@ -62185,10 +61338,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>21510001</t>
-        </is>
+      <c r="A14" t="n">
+        <v>21510001</v>
       </c>
       <c r="B14" t="n">
         <v>906311.49</v>
@@ -62218,10 +61369,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>21510002</t>
-        </is>
+      <c r="A15" t="n">
+        <v>21510002</v>
       </c>
       <c r="B15" t="n">
         <v>510600.02</v>
@@ -62251,10 +61400,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>42110001</t>
-        </is>
+      <c r="A16" t="n">
+        <v>42110001</v>
       </c>
       <c r="B16" t="n">
         <v>279056.35</v>
@@ -62284,10 +61431,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>42110002</t>
-        </is>
+      <c r="A17" t="n">
+        <v>42110002</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -62317,10 +61462,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>42110003</t>
-        </is>
+      <c r="A18" t="n">
+        <v>42110003</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -62350,10 +61493,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>42110004</t>
-        </is>
+      <c r="A19" t="n">
+        <v>42110004</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -62383,10 +61524,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>42110005</t>
-        </is>
+      <c r="A20" t="n">
+        <v>42110005</v>
       </c>
       <c r="B20" t="n">
         <v>8853.299999999999</v>
@@ -62411,15 +61550,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t>2 -  Diferença somente na folha RH</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>42110006</t>
-        </is>
+      <c r="A21" t="n">
+        <v>42110006</v>
       </c>
       <c r="B21" t="n">
         <v>807.92</v>
@@ -62444,15 +61581,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t>2 -  Diferença somente na folha RH</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>42110007</t>
-        </is>
+      <c r="A22" t="n">
+        <v>42110007</v>
       </c>
       <c r="B22" t="n">
         <v>15514.92</v>
@@ -62482,10 +61617,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>42110008</t>
-        </is>
+      <c r="A23" t="n">
+        <v>42110008</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -62515,10 +61648,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>42110010</t>
-        </is>
+      <c r="A24" t="n">
+        <v>42110010</v>
       </c>
       <c r="B24" t="n">
         <v>47387.85</v>
@@ -62548,10 +61679,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>42110011</t>
-        </is>
+      <c r="A25" t="n">
+        <v>42110011</v>
       </c>
       <c r="B25" t="n">
         <v>698.01</v>
@@ -62581,10 +61710,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>42110012</t>
-        </is>
+      <c r="A26" t="n">
+        <v>42110012</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -62614,10 +61741,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>42110013</t>
-        </is>
+      <c r="A27" t="n">
+        <v>42110013</v>
       </c>
       <c r="B27" t="n">
         <v>95305.08</v>
@@ -62647,10 +61772,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>42110014</t>
-        </is>
+      <c r="A28" t="n">
+        <v>42110014</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -62680,10 +61803,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>42120001</t>
-        </is>
+      <c r="A29" t="n">
+        <v>42120001</v>
       </c>
       <c r="B29" t="n">
         <v>2446.71</v>
@@ -62713,10 +61834,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>42120002</t>
-        </is>
+      <c r="A30" t="n">
+        <v>42120002</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -62746,10 +61865,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>42120003</t>
-        </is>
+      <c r="A31" t="n">
+        <v>42120003</v>
       </c>
       <c r="B31" t="n">
         <v>20635</v>
@@ -62779,10 +61896,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>42120004</t>
-        </is>
+      <c r="A32" t="n">
+        <v>42120004</v>
       </c>
       <c r="B32" t="n">
         <v>18342.49</v>
@@ -62812,10 +61927,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>42120005</t>
-        </is>
+      <c r="A33" t="n">
+        <v>42120005</v>
       </c>
       <c r="B33" t="n">
         <v>237112.09</v>
@@ -62845,10 +61958,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>42120006</t>
-        </is>
+      <c r="A34" t="n">
+        <v>42120006</v>
       </c>
       <c r="B34" t="n">
         <v>171422.7</v>
@@ -62878,10 +61989,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>42120011</t>
-        </is>
+      <c r="A35" t="n">
+        <v>42120011</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -62911,10 +62020,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>42130003</t>
-        </is>
+      <c r="A36" t="n">
+        <v>42130003</v>
       </c>
       <c r="B36" t="n">
         <v>380048.26</v>
@@ -62944,10 +62051,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>42130008</t>
-        </is>
+      <c r="A37" t="n">
+        <v>42130008</v>
       </c>
       <c r="B37" t="n">
         <v>1499613.52</v>
@@ -62977,10 +62082,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>42130009</t>
-        </is>
+      <c r="A38" t="n">
+        <v>42130009</v>
       </c>
       <c r="B38" t="n">
         <v>721258.91</v>
@@ -63010,10 +62113,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>42130010</t>
-        </is>
+      <c r="A39" t="n">
+        <v>42130010</v>
       </c>
       <c r="B39" t="n">
         <v>418295.08</v>
@@ -63043,10 +62144,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>42130012</t>
-        </is>
+      <c r="A40" t="n">
+        <v>42130012</v>
       </c>
       <c r="B40" t="n">
         <v>289578</v>
@@ -63076,10 +62175,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>42130023</t>
-        </is>
+      <c r="A41" t="n">
+        <v>42130023</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -63109,10 +62206,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>42330004</t>
-        </is>
+      <c r="A42" t="n">
+        <v>42330004</v>
       </c>
       <c r="B42" t="n">
         <v>6886.99</v>
@@ -63142,10 +62237,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42420001</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42420001</v>
       </c>
       <c r="B43" t="n">
         <v>37531.35</v>
@@ -63236,10 +62329,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1100000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1100000</v>
       </c>
       <c r="B2" t="n">
         <v>32165.63</v>
@@ -63269,10 +62360,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1100001</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1100001</v>
       </c>
       <c r="B3" t="n">
         <v>167345.88</v>
@@ -63302,10 +62391,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1100005</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1100005</v>
       </c>
       <c r="B4" t="n">
         <v>240547.34</v>
@@ -63335,10 +62422,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1110000</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1110000</v>
       </c>
       <c r="B5" t="n">
         <v>221920.09</v>
@@ -63368,10 +62453,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1110001</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1110001</v>
       </c>
       <c r="B6" t="n">
         <v>157889.73</v>
@@ -63401,10 +62484,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1110002</t>
-        </is>
+      <c r="A7" t="n">
+        <v>1110002</v>
       </c>
       <c r="B7" t="n">
         <v>141614.66</v>
@@ -63434,10 +62515,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1110003</t>
-        </is>
+      <c r="A8" t="n">
+        <v>1110003</v>
       </c>
       <c r="B8" t="n">
         <v>252213.84</v>
@@ -63467,10 +62546,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1110100</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1110100</v>
       </c>
       <c r="B9" t="n">
         <v>154380.73</v>
@@ -63500,10 +62577,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1110101</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1110101</v>
       </c>
       <c r="B10" t="n">
         <v>149484.98</v>
@@ -63533,10 +62608,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1110300</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1110300</v>
       </c>
       <c r="B11" t="n">
         <v>207463.31</v>
@@ -63566,10 +62639,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1119900</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1119900</v>
       </c>
       <c r="B12" t="n">
         <v>1944771.42</v>
@@ -63599,10 +62670,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1120100</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1120100</v>
       </c>
       <c r="B13" t="n">
         <v>480946.81</v>
@@ -63632,10 +62701,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1120102</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1120102</v>
       </c>
       <c r="B14" t="n">
         <v>318667.51</v>
@@ -63665,10 +62732,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1120103</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1120103</v>
       </c>
       <c r="B15" t="n">
         <v>155931.8</v>
@@ -63698,10 +62763,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1120104</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1120104</v>
       </c>
       <c r="B16" t="n">
         <v>156462.13</v>
@@ -63731,10 +62794,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1120105</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1120105</v>
       </c>
       <c r="B17" t="n">
         <v>223756.69</v>
@@ -63764,10 +62825,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1120400</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1120400</v>
       </c>
       <c r="B18" t="n">
         <v>123945.8</v>
@@ -63797,10 +62856,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1120600</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1120600</v>
       </c>
       <c r="B19" t="n">
         <v>205524.62</v>
@@ -63830,10 +62887,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1121000</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1121000</v>
       </c>
       <c r="B20" t="n">
         <v>101309.22</v>
@@ -63863,10 +62918,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1121100</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1121100</v>
       </c>
       <c r="B21" t="n">
         <v>224802.05</v>
@@ -63896,10 +62949,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1121500</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1121500</v>
       </c>
       <c r="B22" t="n">
         <v>264427.36</v>
@@ -63929,10 +62980,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1121600</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1121600</v>
       </c>
       <c r="B23" t="n">
         <v>93009.11</v>
@@ -63962,10 +63011,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1130001</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1130001</v>
       </c>
       <c r="B24" t="n">
         <v>185805.86</v>
@@ -63995,10 +63042,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1130002</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1130002</v>
       </c>
       <c r="B25" t="n">
         <v>224081.93</v>
@@ -64028,10 +63073,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1130100</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1130100</v>
       </c>
       <c r="B26" t="n">
         <v>181659.45</v>
@@ -64061,10 +63104,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1130101</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1130101</v>
       </c>
       <c r="B27" t="n">
         <v>269905.8</v>
@@ -64094,10 +63135,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1130102</t>
-        </is>
+      <c r="A28" t="n">
+        <v>1130102</v>
       </c>
       <c r="B28" t="n">
         <v>207543.76</v>
@@ -64127,10 +63166,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1130103</t>
-        </is>
+      <c r="A29" t="n">
+        <v>1130103</v>
       </c>
       <c r="B29" t="n">
         <v>251756.38</v>
@@ -64160,10 +63197,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1140003</t>
-        </is>
+      <c r="A30" t="n">
+        <v>1140003</v>
       </c>
       <c r="B30" t="n">
         <v>275992.18</v>
@@ -64193,10 +63228,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1140004</t>
-        </is>
+      <c r="A31" t="n">
+        <v>1140004</v>
       </c>
       <c r="B31" t="n">
         <v>213078.61</v>
@@ -64226,10 +63259,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1140005</t>
-        </is>
+      <c r="A32" t="n">
+        <v>1140005</v>
       </c>
       <c r="B32" t="n">
         <v>201807.32</v>
@@ -64259,10 +63290,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1140006</t>
-        </is>
+      <c r="A33" t="n">
+        <v>1140006</v>
       </c>
       <c r="B33" t="n">
         <v>118634.19</v>
@@ -64292,10 +63321,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1140008</t>
-        </is>
+      <c r="A34" t="n">
+        <v>1140008</v>
       </c>
       <c r="B34" t="n">
         <v>229093.95</v>
@@ -64325,10 +63352,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1140009</t>
-        </is>
+      <c r="A35" t="n">
+        <v>1140009</v>
       </c>
       <c r="B35" t="n">
         <v>93820.21000000001</v>
@@ -64358,10 +63383,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1140200</t>
-        </is>
+      <c r="A36" t="n">
+        <v>1140200</v>
       </c>
       <c r="B36" t="n">
         <v>151765.89</v>
@@ -64391,10 +63414,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1140201</t>
-        </is>
+      <c r="A37" t="n">
+        <v>1140201</v>
       </c>
       <c r="B37" t="n">
         <v>171456.84</v>
@@ -64424,10 +63445,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1140202</t>
-        </is>
+      <c r="A38" t="n">
+        <v>1140202</v>
       </c>
       <c r="B38" t="n">
         <v>265969.21</v>
@@ -64457,10 +63476,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1140203</t>
-        </is>
+      <c r="A39" t="n">
+        <v>1140203</v>
       </c>
       <c r="B39" t="n">
         <v>341739.57</v>
@@ -64490,10 +63507,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1140204</t>
-        </is>
+      <c r="A40" t="n">
+        <v>1140204</v>
       </c>
       <c r="B40" t="n">
         <v>129242.02</v>
@@ -64523,10 +63538,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1141101</t>
-        </is>
+      <c r="A41" t="n">
+        <v>1141101</v>
       </c>
       <c r="B41" t="n">
         <v>155469.78</v>
@@ -64556,10 +63569,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1141201</t>
-        </is>
+      <c r="A42" t="n">
+        <v>1141201</v>
       </c>
       <c r="B42" t="n">
         <v>271845.59</v>
@@ -64589,10 +63600,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1141301</t>
-        </is>
+      <c r="A43" t="n">
+        <v>1141301</v>
       </c>
       <c r="B43" t="n">
         <v>259217.34</v>
@@ -64622,10 +63631,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1141401</t>
-        </is>
+      <c r="A44" t="n">
+        <v>1141401</v>
       </c>
       <c r="B44" t="n">
         <v>279542.47</v>
@@ -64655,10 +63662,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1141501</t>
-        </is>
+      <c r="A45" t="n">
+        <v>1141501</v>
       </c>
       <c r="B45" t="n">
         <v>135169.35</v>
@@ -64688,10 +63693,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1150000</t>
-        </is>
+      <c r="A46" t="n">
+        <v>1150000</v>
       </c>
       <c r="B46" t="n">
         <v>129594.34</v>
@@ -64721,10 +63724,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1150100</t>
-        </is>
+      <c r="A47" t="n">
+        <v>1150100</v>
       </c>
       <c r="B47" t="n">
         <v>467705.01</v>
@@ -64754,10 +63755,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1150101</t>
-        </is>
+      <c r="A48" t="n">
+        <v>1150101</v>
       </c>
       <c r="B48" t="n">
         <v>321657.97</v>
@@ -64787,10 +63786,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1150200</t>
-        </is>
+      <c r="A49" t="n">
+        <v>1150200</v>
       </c>
       <c r="B49" t="n">
         <v>118699.8</v>
@@ -64820,10 +63817,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1150201</t>
-        </is>
+      <c r="A50" t="n">
+        <v>1150201</v>
       </c>
       <c r="B50" t="n">
         <v>129030.91</v>
@@ -64853,10 +63848,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1160100</t>
-        </is>
+      <c r="A51" t="n">
+        <v>1160100</v>
       </c>
       <c r="B51" t="n">
         <v>112536.19</v>
@@ -64886,10 +63879,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1160101</t>
-        </is>
+      <c r="A52" t="n">
+        <v>1160101</v>
       </c>
       <c r="B52" t="n">
         <v>233581.87</v>
@@ -64919,10 +63910,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1160201</t>
-        </is>
+      <c r="A53" t="n">
+        <v>1160201</v>
       </c>
       <c r="B53" t="n">
         <v>210030.43</v>
@@ -64952,10 +63941,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1160300</t>
-        </is>
+      <c r="A54" t="n">
+        <v>1160300</v>
       </c>
       <c r="B54" t="n">
         <v>95707.10000000001</v>
@@ -64985,10 +63972,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1160301</t>
-        </is>
+      <c r="A55" t="n">
+        <v>1160301</v>
       </c>
       <c r="B55" t="n">
         <v>315508.03</v>
@@ -65018,10 +64003,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1170000</t>
-        </is>
+      <c r="A56" t="n">
+        <v>1170000</v>
       </c>
       <c r="B56" t="n">
         <v>230197.83</v>
@@ -65051,10 +64034,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>1170100</t>
-        </is>
+      <c r="A57" t="n">
+        <v>1170100</v>
       </c>
       <c r="B57" t="n">
         <v>198019.73</v>
@@ -65084,10 +64065,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1170101</t>
-        </is>
+      <c r="A58" t="n">
+        <v>1170101</v>
       </c>
       <c r="B58" t="n">
         <v>346838.77</v>
@@ -65117,10 +64096,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1190101</t>
-        </is>
+      <c r="A59" t="n">
+        <v>1190101</v>
       </c>
       <c r="B59" t="n">
         <v>178275.19</v>
@@ -65150,10 +64127,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1220200</t>
-        </is>
+      <c r="A60" t="n">
+        <v>1220200</v>
       </c>
       <c r="B60" t="n">
         <v>220119.8</v>
@@ -65239,7 +64214,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
         <v>5136830.92</v>
       </c>

--- a/dados/user/IA.xlsx
+++ b/dados/user/IA.xlsx
@@ -504,7 +504,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>-7215.65</v>
       </c>
@@ -543,7 +542,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>-20517.44</v>
       </c>
@@ -582,7 +580,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>-19466.25</v>
       </c>
@@ -621,7 +618,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>-6996.48</v>
       </c>
@@ -660,7 +656,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>-7959.31</v>
       </c>
@@ -699,7 +694,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>-7719.45</v>
       </c>
@@ -738,7 +732,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>-5553.59</v>
       </c>
@@ -777,7 +770,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>-8061.67</v>
       </c>
@@ -816,7 +808,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>-2388.89</v>
       </c>
@@ -855,7 +846,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>-31446.57</v>
       </c>
@@ -894,7 +884,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>-16048.87</v>
       </c>
@@ -933,7 +922,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>-15774.61</v>
       </c>
@@ -972,7 +960,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>-11702.17</v>
       </c>
@@ -1011,7 +998,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>-4288.94</v>
       </c>
@@ -1050,7 +1036,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>-9428.549999999999</v>
       </c>
@@ -1089,7 +1074,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>-20038.75</v>
       </c>
@@ -1128,7 +1112,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>-2229.42</v>
       </c>
@@ -1167,7 +1150,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>-5077.22</v>
       </c>
@@ -1206,7 +1188,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>-24701.88</v>
       </c>
@@ -1245,7 +1226,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>-5397.7</v>
       </c>
@@ -1284,7 +1264,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>-9205.82</v>
       </c>
@@ -1323,7 +1302,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>-3168.01</v>
       </c>
@@ -1362,7 +1340,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>-1036.31</v>
       </c>
@@ -1401,7 +1378,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>-11950.17</v>
       </c>
@@ -1440,7 +1416,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>-2957.8</v>
       </c>
@@ -1479,7 +1454,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>-8566.360000000001</v>
       </c>
@@ -1518,7 +1492,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>-11824.41</v>
       </c>
@@ -1557,7 +1530,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>-698.8</v>
       </c>
@@ -1596,7 +1568,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>-3353.33</v>
       </c>
@@ -1635,7 +1606,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>-2607.54</v>
       </c>
@@ -1674,7 +1644,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>-4671.35</v>
       </c>
@@ -1713,7 +1682,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>-1259.16</v>
       </c>
@@ -1752,7 +1720,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>-4078.84</v>
       </c>
@@ -1791,7 +1758,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>-5760.54</v>
       </c>
@@ -1830,7 +1796,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>-11844.91</v>
       </c>
@@ -1869,7 +1834,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>-14611.48</v>
       </c>
@@ -1908,7 +1872,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>-1192.98</v>
       </c>
@@ -1947,7 +1910,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>-7985.93</v>
       </c>
@@ -1986,7 +1948,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>-12811.96</v>
       </c>
@@ -2025,7 +1986,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>-18124.1</v>
       </c>
@@ -2064,7 +2024,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>-9183.4</v>
       </c>
@@ -2103,7 +2062,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>-3723.24</v>
       </c>
@@ -2142,7 +2100,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>-3352.09</v>
       </c>
@@ -2181,7 +2138,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>-1990.35</v>
       </c>
@@ -2220,7 +2176,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>-16685.5</v>
       </c>
@@ -2259,7 +2214,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>-1279.78</v>
       </c>
@@ -2298,7 +2252,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>-3389.34</v>
       </c>
@@ -2337,7 +2290,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>-1453.47</v>
       </c>
@@ -2376,7 +2328,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>-10065.85</v>
       </c>
@@ -2415,7 +2366,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>-3341.44</v>
       </c>
@@ -2454,7 +2404,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>-2941.68</v>
       </c>
@@ -2493,7 +2442,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>-3891.15</v>
       </c>
@@ -2532,7 +2480,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>-3428.25</v>
       </c>
@@ -2571,7 +2518,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>-7025.91</v>
       </c>
@@ -2610,7 +2556,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>-9604.43</v>
       </c>
@@ -2649,7 +2594,6 @@
           <t>2821</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>-6304.68</v>
       </c>
@@ -2683,8 +2627,6 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -2723,7 +2665,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>-335.4</v>
       </c>
@@ -2762,7 +2703,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>-1575.93</v>
       </c>
@@ -2796,8 +2736,6 @@
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -2831,8 +2769,6 @@
       <c r="F62" t="n">
         <v>0</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -2866,8 +2802,6 @@
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -2901,8 +2835,6 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -2941,7 +2873,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>-132.97</v>
       </c>
@@ -2980,7 +2911,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>-272.07</v>
       </c>
@@ -3014,8 +2944,6 @@
       <c r="F67" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -3049,8 +2977,6 @@
       <c r="F68" t="n">
         <v>0</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -3084,8 +3010,6 @@
       <c r="F69" t="n">
         <v>0</v>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -3119,8 +3043,6 @@
       <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -3159,7 +3081,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>-432.6</v>
       </c>
@@ -3193,8 +3114,6 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -3228,8 +3147,6 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -3268,7 +3185,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>-237.02</v>
       </c>
@@ -3302,8 +3218,6 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -3342,7 +3256,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>-126.48</v>
       </c>
@@ -3381,7 +3294,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>-340.25</v>
       </c>
@@ -3420,7 +3332,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
         <v>-574.52</v>
       </c>
@@ -3454,8 +3365,6 @@
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -3489,8 +3398,6 @@
       <c r="F80" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -3524,8 +3431,6 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -3559,8 +3464,6 @@
       <c r="F82" t="n">
         <v>0</v>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -3594,8 +3497,6 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -3629,8 +3530,6 @@
       <c r="F84" t="n">
         <v>0</v>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -3664,8 +3563,6 @@
       <c r="F85" t="n">
         <v>0</v>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -3699,8 +3596,6 @@
       <c r="F86" t="n">
         <v>0</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -3739,7 +3634,6 @@
           <t>5590</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>-35.09</v>
       </c>
@@ -3773,8 +3667,6 @@
       <c r="F88" t="n">
         <v>0</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -3808,8 +3700,6 @@
       <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -3843,8 +3733,6 @@
       <c r="F90" t="n">
         <v>0</v>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>978.97</v>
       </c>
@@ -6286,7 +6174,6 @@
       <c r="F147" t="n">
         <v>42281.8</v>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>2621, 2821, 3504, 3529, 5500, 5560, 5580, 5590, 5810, 7621, 9953</t>
@@ -7061,7 +6948,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>-364.03</v>
       </c>
@@ -7100,7 +6986,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>-382.08</v>
       </c>
@@ -7139,7 +7024,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>-733.8099999999999</v>
       </c>
@@ -7221,7 +7105,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>-1090.93</v>
       </c>
@@ -7346,7 +7229,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>-2376.14</v>
       </c>
@@ -7385,7 +7267,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>-485.26</v>
       </c>
@@ -7424,7 +7305,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>-211.92</v>
       </c>
@@ -7463,7 +7343,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>-346.31</v>
       </c>
@@ -7588,7 +7467,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>-140.41</v>
       </c>
@@ -7627,7 +7505,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>-27.39</v>
       </c>
@@ -7666,7 +7543,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>-448.65</v>
       </c>
@@ -7705,7 +7581,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>-1178.12</v>
       </c>
@@ -7830,7 +7705,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>-1342.84</v>
       </c>
@@ -7869,7 +7743,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>-416.62</v>
       </c>
@@ -7908,7 +7781,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
         <v>-1028.57</v>
       </c>
@@ -7947,7 +7819,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
         <v>-709.8</v>
       </c>
@@ -7986,7 +7857,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
         <v>-455.2</v>
       </c>
@@ -8025,7 +7895,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
         <v>-100.27</v>
       </c>
@@ -8064,7 +7933,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
         <v>-3166.21</v>
       </c>
@@ -8103,7 +7971,6 @@
           <t>0240</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>-338.87</v>
       </c>
@@ -8137,7 +8004,6 @@
       <c r="F192" t="n">
         <v>2458.7</v>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -8224,7 +8090,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
         <v>-7594.7</v>
       </c>
@@ -8301,7 +8166,6 @@
       <c r="F196" t="n">
         <v>5763.5</v>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -8340,7 +8204,6 @@
       <c r="F197" t="n">
         <v>3606.41</v>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -8599,7 +8462,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
         <v>-2171.92</v>
       </c>
@@ -8638,7 +8500,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
         <v>-1766.58</v>
       </c>
@@ -8677,7 +8538,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
         <v>-1608.5</v>
       </c>
@@ -8759,7 +8619,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
         <v>-2146.78</v>
       </c>
@@ -8965,7 +8824,6 @@
       <c r="F212" t="n">
         <v>394.1000000000004</v>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -9047,7 +8905,6 @@
       <c r="F214" t="n">
         <v>7733.610000000001</v>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -9177,7 +9034,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
         <v>-2930.4</v>
       </c>
@@ -9259,7 +9115,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
         <v>-250.3</v>
       </c>
@@ -9336,7 +9191,6 @@
       <c r="F221" t="n">
         <v>7229.190000000001</v>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -9380,7 +9234,6 @@
           <t>9953</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
         <v>-5216.25</v>
       </c>
@@ -9414,7 +9267,6 @@
       <c r="F223" t="n">
         <v>1723.2</v>
       </c>
-      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>FERI</t>
@@ -9458,7 +9310,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
         <v>-225.33</v>
       </c>
@@ -9497,7 +9348,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
         <v>-500.72</v>
       </c>
@@ -9536,7 +9386,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
         <v>-497.61</v>
       </c>
@@ -9575,7 +9424,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
         <v>-287.31</v>
       </c>
@@ -9614,7 +9462,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
         <v>-492.32</v>
       </c>
@@ -9653,7 +9500,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
         <v>-162.08</v>
       </c>
@@ -9692,7 +9538,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
         <v>-151</v>
       </c>
@@ -9731,7 +9576,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
         <v>-295</v>
       </c>
@@ -9770,7 +9614,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
         <v>-48.67</v>
       </c>
@@ -9809,7 +9652,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
         <v>-1980.75</v>
       </c>
@@ -9848,7 +9690,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
         <v>-87.58</v>
       </c>
@@ -9887,7 +9728,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
         <v>-500.94</v>
       </c>
@@ -9926,7 +9766,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
         <v>-219.29</v>
       </c>
@@ -9965,7 +9804,6 @@
           <t>3508</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
         <v>-1559.68</v>
       </c>
@@ -10004,7 +9842,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
         <v>-919.34</v>
       </c>
@@ -10043,7 +9880,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
         <v>-4224.11</v>
       </c>
@@ -10082,7 +9918,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
         <v>-3999.26</v>
       </c>
@@ -10121,7 +9956,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
         <v>-708.42</v>
       </c>
@@ -10160,7 +9994,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
         <v>-863.9400000000001</v>
       </c>
@@ -10199,7 +10032,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
         <v>-2655.33</v>
       </c>
@@ -10238,7 +10070,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
         <v>-214.96</v>
       </c>
@@ -10277,7 +10108,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
         <v>-1004.04</v>
       </c>
@@ -10316,7 +10146,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
         <v>-418.91</v>
       </c>
@@ -10398,7 +10227,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
         <v>-3270.48</v>
       </c>
@@ -10437,7 +10265,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
         <v>-2010.51</v>
       </c>
@@ -10476,7 +10303,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
         <v>-1195.23</v>
       </c>
@@ -10515,7 +10341,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
         <v>-330.77</v>
       </c>
@@ -10554,7 +10379,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
         <v>-738.9</v>
       </c>
@@ -10593,7 +10417,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
         <v>-2860.13</v>
       </c>
@@ -10632,7 +10455,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
         <v>-697.12</v>
       </c>
@@ -10671,7 +10493,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
         <v>-206.46</v>
       </c>
@@ -10710,7 +10531,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
         <v>-4183.13</v>
       </c>
@@ -10749,7 +10569,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
         <v>-1170.74</v>
       </c>
@@ -10788,7 +10607,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
         <v>-1302.47</v>
       </c>
@@ -10827,7 +10645,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
         <v>-345.46</v>
       </c>
@@ -10866,7 +10683,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
         <v>-621.29</v>
       </c>
@@ -10948,7 +10764,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
         <v>-1150.06</v>
       </c>
@@ -10987,7 +10802,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
         <v>-1450.05</v>
       </c>
@@ -11026,7 +10840,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
         <v>-2047.56</v>
       </c>
@@ -11065,7 +10878,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
         <v>-458.14</v>
       </c>
@@ -11104,7 +10916,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
         <v>-142.13</v>
       </c>
@@ -11143,7 +10954,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
         <v>-811.14</v>
       </c>
@@ -11182,7 +10992,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
         <v>-817.64</v>
       </c>
@@ -11221,7 +11030,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
         <v>-450.08</v>
       </c>
@@ -11260,7 +11068,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
         <v>-58</v>
       </c>
@@ -11299,7 +11106,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
         <v>-906.9400000000001</v>
       </c>
@@ -11338,7 +11144,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
         <v>-3292.87</v>
       </c>
@@ -11377,7 +11182,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
         <v>-3785.89</v>
       </c>
@@ -11416,7 +11220,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
         <v>-600.65</v>
       </c>
@@ -11455,7 +11258,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
         <v>-1041.5</v>
       </c>
@@ -11494,7 +11296,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
         <v>-2300.74</v>
       </c>
@@ -11533,7 +11334,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
         <v>-3600.88</v>
       </c>
@@ -11572,7 +11372,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
         <v>-2223.07</v>
       </c>
@@ -11611,7 +11410,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
         <v>-97.01000000000001</v>
       </c>
@@ -11650,7 +11448,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
         <v>-995.78</v>
       </c>
@@ -11732,7 +11529,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
         <v>-4157.46</v>
       </c>
@@ -11771,7 +11567,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
         <v>-418.68</v>
       </c>
@@ -11810,7 +11605,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="n">
         <v>-1071.7</v>
       </c>
@@ -11849,7 +11643,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="n">
         <v>-503.26</v>
       </c>
@@ -11888,7 +11681,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="n">
         <v>-1999.94</v>
       </c>
@@ -11927,7 +11719,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="n">
         <v>-502.61</v>
       </c>
@@ -11966,7 +11757,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="n">
         <v>-891.15</v>
       </c>
@@ -12048,7 +11838,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="n">
         <v>-1412.41</v>
       </c>
@@ -12087,7 +11876,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="n">
         <v>-1141.7</v>
       </c>
@@ -12126,7 +11914,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="n">
         <v>-2981.52</v>
       </c>
@@ -12165,7 +11952,6 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="n">
         <v>-529.65</v>
       </c>
@@ -12199,8 +11985,6 @@
       <c r="F294" t="n">
         <v>0</v>
       </c>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="n">
         <v>0</v>
       </c>
@@ -12239,7 +12023,6 @@
           <t>5560, 8100</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="n">
         <v>-834.42</v>
       </c>
@@ -12278,7 +12061,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="n">
         <v>-7900.33</v>
       </c>
@@ -12317,7 +12099,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="n">
         <v>-17039.98</v>
       </c>
@@ -12356,7 +12137,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="n">
         <v>-17919.78</v>
       </c>
@@ -12395,7 +12175,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
         <v>-6892.42</v>
       </c>
@@ -12434,7 +12213,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="n">
         <v>-8074.03</v>
       </c>
@@ -12473,7 +12251,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="n">
         <v>-13599.08</v>
       </c>
@@ -12512,7 +12289,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="n">
         <v>-4847.88</v>
       </c>
@@ -12551,7 +12327,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="n">
         <v>-8290.620000000001</v>
       </c>
@@ -12590,7 +12365,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="n">
         <v>-4707.93</v>
       </c>
@@ -12629,7 +12403,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108, 9960</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="n">
         <v>-15051</v>
       </c>
@@ -12668,7 +12441,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="n">
         <v>-15684.36</v>
       </c>
@@ -12707,7 +12479,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="n">
         <v>-11339.51</v>
       </c>
@@ -12746,7 +12517,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="n">
         <v>-9205.1</v>
       </c>
@@ -12785,7 +12555,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="n">
         <v>-5244.49</v>
       </c>
@@ -12824,7 +12593,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="n">
         <v>-6775.08</v>
       </c>
@@ -12863,7 +12631,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="n">
         <v>-14870.65</v>
       </c>
@@ -12902,7 +12669,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="n">
         <v>-1499.1</v>
       </c>
@@ -12941,7 +12707,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="n">
         <v>-5161.73</v>
       </c>
@@ -12980,7 +12745,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="n">
         <v>-19873.91</v>
       </c>
@@ -13019,7 +12783,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="n">
         <v>-3079.7</v>
       </c>
@@ -13101,7 +12864,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
         <v>-5085.69</v>
       </c>
@@ -13140,7 +12902,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="n">
         <v>-1492.64</v>
       </c>
@@ -13179,7 +12940,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="n">
         <v>-14557.71</v>
       </c>
@@ -13218,7 +12978,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="n">
         <v>-3428.81</v>
       </c>
@@ -13257,7 +13016,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
         <v>-9888.549999999999</v>
       </c>
@@ -13296,7 +13054,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="n">
         <v>-11650.42</v>
       </c>
@@ -13335,7 +13092,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="n">
         <v>-2141.95</v>
       </c>
@@ -13374,7 +13130,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="n">
         <v>-4660.42</v>
       </c>
@@ -13413,7 +13168,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="n">
         <v>-1913.58</v>
       </c>
@@ -13452,7 +13206,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="n">
         <v>-6256.47</v>
       </c>
@@ -13491,7 +13244,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="n">
         <v>-1551.83</v>
       </c>
@@ -13530,7 +13282,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="n">
         <v>-4414.16</v>
       </c>
@@ -13569,7 +13320,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="n">
         <v>-8368.709999999999</v>
       </c>
@@ -13608,7 +13358,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="n">
         <v>-18823.9</v>
       </c>
@@ -13647,7 +13396,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="n">
         <v>-15984.94</v>
       </c>
@@ -13686,7 +13434,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="n">
         <v>-998.75</v>
       </c>
@@ -13811,7 +13558,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
         <v>-16995.05</v>
       </c>
@@ -13850,7 +13596,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
         <v>-13183.58</v>
       </c>
@@ -13889,7 +13634,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
         <v>-4478.09</v>
       </c>
@@ -13928,7 +13672,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">
         <v>-2447.6</v>
       </c>
@@ -13967,7 +13710,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108, 9960</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="n">
         <v>-3948.21</v>
       </c>
@@ -14006,7 +13748,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="n">
         <v>-20558.47</v>
       </c>
@@ -14045,7 +13786,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="n">
         <v>-1939.7</v>
       </c>
@@ -14084,7 +13824,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="n">
         <v>-2820.72</v>
       </c>
@@ -14123,7 +13862,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="n">
         <v>-1807.04</v>
       </c>
@@ -14162,7 +13900,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="n">
         <v>-12912.58</v>
       </c>
@@ -14201,7 +13938,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="n">
         <v>-5051.53</v>
       </c>
@@ -14240,7 +13976,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="n">
         <v>-2081.08</v>
       </c>
@@ -14279,7 +14014,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108, 9960</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="n">
         <v>-2612.03</v>
       </c>
@@ -14318,7 +14052,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="n">
         <v>-8068.55</v>
       </c>
@@ -14357,7 +14090,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="n">
         <v>-9313.99</v>
       </c>
@@ -14396,7 +14128,6 @@
           <t>5560, 5580, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="n">
         <v>-17615.29</v>
       </c>
@@ -14435,7 +14166,6 @@
           <t>5560, 8100, 8101, 8102, 8103, 8104, 8105, 8108</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="n">
         <v>-6221.93</v>
       </c>
@@ -14469,8 +14199,6 @@
       <c r="F352" t="n">
         <v>0</v>
       </c>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="n">
         <v>0</v>
       </c>
@@ -14552,7 +14280,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="n">
         <v>-2880.6</v>
       </c>
@@ -14591,7 +14318,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="n">
         <v>-14821.61</v>
       </c>
@@ -14630,7 +14356,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="n">
         <v>-10776.33</v>
       </c>
@@ -14669,7 +14394,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="n">
         <v>-2199.19</v>
       </c>
@@ -14708,7 +14432,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="n">
         <v>-2831.67</v>
       </c>
@@ -14747,7 +14470,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="n">
         <v>-7610.77</v>
       </c>
@@ -14786,7 +14508,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="n">
         <v>-308.27</v>
       </c>
@@ -14825,7 +14546,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="n">
         <v>-1964.55</v>
       </c>
@@ -14864,7 +14584,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="n">
         <v>-2675.04</v>
       </c>
@@ -14903,7 +14622,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="n">
         <v>-10223.03</v>
       </c>
@@ -14942,7 +14660,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="n">
         <v>-7286.41</v>
       </c>
@@ -14981,7 +14698,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="n">
         <v>-6949.53</v>
       </c>
@@ -15020,7 +14736,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="n">
         <v>-2660.38</v>
       </c>
@@ -15059,7 +14774,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="n">
         <v>-380.08</v>
       </c>
@@ -15098,7 +14812,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="n">
         <v>-3682.17</v>
       </c>
@@ -15137,7 +14850,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="n">
         <v>-8413.139999999999</v>
       </c>
@@ -15176,7 +14888,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="n">
         <v>-591.49</v>
       </c>
@@ -15215,7 +14926,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="n">
         <v>-118.6</v>
       </c>
@@ -15254,7 +14964,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="n">
         <v>-11793.11</v>
       </c>
@@ -15293,7 +15002,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="n">
         <v>-2216.53</v>
       </c>
@@ -15332,7 +15040,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="n">
         <v>-4343.83</v>
       </c>
@@ -15371,7 +15078,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="n">
         <v>-660.38</v>
       </c>
@@ -15410,7 +15116,6 @@
           <t>7621</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="n">
         <v>-59.65</v>
       </c>
@@ -15449,7 +15154,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="n">
         <v>-193.69</v>
       </c>
@@ -15488,7 +15192,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="n">
         <v>-281.56</v>
       </c>
@@ -15527,7 +15230,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="n">
         <v>-4164.94</v>
       </c>
@@ -15566,7 +15268,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="n">
         <v>-6297.4</v>
       </c>
@@ -15605,7 +15306,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="n">
         <v>-470.43</v>
       </c>
@@ -15644,7 +15344,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
       <c r="I382" t="n">
         <v>-94.78</v>
       </c>
@@ -15683,7 +15382,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="n">
         <v>-3030.28</v>
       </c>
@@ -15722,7 +15420,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="n">
         <v>-237.8</v>
       </c>
@@ -15761,7 +15458,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="n">
         <v>-1048.64</v>
       </c>
@@ -15800,7 +15496,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="n">
         <v>-2010.57</v>
       </c>
@@ -15839,7 +15534,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="n">
         <v>-3928.26</v>
       </c>
@@ -15878,7 +15572,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="n">
         <v>-11245.75</v>
       </c>
@@ -15917,7 +15610,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="n">
         <v>-279.59</v>
       </c>
@@ -15956,7 +15648,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="n">
         <v>-2690.1</v>
       </c>
@@ -15995,7 +15686,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="n">
         <v>-5255.89</v>
       </c>
@@ -16034,7 +15724,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="n">
         <v>-9452.59</v>
       </c>
@@ -16073,7 +15762,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="n">
         <v>-2208.76</v>
       </c>
@@ -16112,7 +15800,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="n">
         <v>-522.76</v>
       </c>
@@ -16151,7 +15838,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="n">
         <v>-1437.71</v>
       </c>
@@ -16190,7 +15876,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="n">
         <v>-613.6</v>
       </c>
@@ -16229,7 +15914,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="n">
         <v>-1016</v>
       </c>
@@ -16268,7 +15952,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="n">
         <v>-54.33</v>
       </c>
@@ -16307,7 +15990,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="n">
         <v>-436.85</v>
       </c>
@@ -16346,7 +16028,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="n">
         <v>-175.98</v>
       </c>
@@ -16385,7 +16066,6 @@
           <t>7621</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="n">
         <v>-88.61</v>
       </c>
@@ -16424,7 +16104,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="n">
         <v>-1228.46</v>
       </c>
@@ -16463,7 +16142,6 @@
           <t>7621</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="n">
         <v>-21.44</v>
       </c>
@@ -16502,7 +16180,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="n">
         <v>-5504.01</v>
       </c>
@@ -16541,7 +16218,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="n">
         <v>-3019.28</v>
       </c>
@@ -16580,7 +16256,6 @@
           <t>5500, 7621</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="n">
         <v>-326.56</v>
       </c>
@@ -16619,7 +16294,6 @@
           <t>5500</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="n">
         <v>-126.83</v>
       </c>
@@ -16653,8 +16327,6 @@
       <c r="F408" t="n">
         <v>0</v>
       </c>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="n">
         <v>0</v>
       </c>
@@ -16693,7 +16365,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="n">
         <v>-2828.14</v>
       </c>
@@ -16732,7 +16403,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="n">
         <v>-10660.07</v>
       </c>
@@ -16771,7 +16441,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="n">
         <v>-8188.54</v>
       </c>
@@ -16810,7 +16479,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="n">
         <v>-2357.42</v>
       </c>
@@ -16849,7 +16517,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="n">
         <v>-3038.26</v>
       </c>
@@ -16931,7 +16598,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="n">
         <v>-1859.24</v>
       </c>
@@ -16970,7 +16636,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="n">
         <v>-3556.29</v>
       </c>
@@ -17267,7 +16932,6 @@
           <t>6403, 6404, 6405</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
       <c r="I423" t="n">
         <v>-2014.47</v>
       </c>
@@ -17349,7 +17013,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr"/>
       <c r="I425" t="n">
         <v>-1688.88</v>
       </c>
@@ -17474,7 +17137,6 @@
           <t>6403, 6404, 6405, 6407, 6408</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="n">
         <v>-2195.03</v>
       </c>
@@ -17513,7 +17175,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr"/>
       <c r="I429" t="n">
         <v>-3653.45</v>
       </c>
@@ -17896,7 +17557,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr"/>
       <c r="I438" t="n">
         <v>-1813.47</v>
       </c>
@@ -17978,7 +17638,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr"/>
       <c r="I440" t="n">
         <v>-954.22</v>
       </c>
@@ -18017,7 +17676,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr"/>
       <c r="I441" t="n">
         <v>-983.24</v>
       </c>
@@ -18056,7 +17714,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr"/>
       <c r="I442" t="n">
         <v>-2588.3</v>
       </c>
@@ -18181,7 +17838,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
       <c r="I445" t="n">
         <v>-1544.53</v>
       </c>
@@ -18220,7 +17876,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr"/>
       <c r="I446" t="n">
         <v>-2600.36</v>
       </c>
@@ -18302,7 +17957,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr"/>
       <c r="I448" t="n">
         <v>-7636.53</v>
       </c>
@@ -18384,7 +18038,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr"/>
       <c r="I450" t="n">
         <v>-1776.72</v>
       </c>
@@ -18423,7 +18076,6 @@
           <t>6403, 6404, 6405, 6407</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr"/>
       <c r="I451" t="n">
         <v>-1902.28</v>
       </c>
@@ -18548,7 +18200,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
       <c r="I454" t="n">
         <v>-1049.65</v>
       </c>
@@ -18587,7 +18238,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
       <c r="I455" t="n">
         <v>-2276.45</v>
       </c>
@@ -18626,7 +18276,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr"/>
       <c r="I456" t="n">
         <v>-1074.15</v>
       </c>
@@ -18751,7 +18400,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr"/>
       <c r="I459" t="n">
         <v>-2431.48</v>
       </c>
@@ -18876,7 +18524,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr"/>
       <c r="I462" t="n">
         <v>-3696.66</v>
       </c>
@@ -18958,7 +18605,6 @@
           <t>6403, 6404, 6405, 6406, 6407, 6408</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr"/>
       <c r="I464" t="n">
         <v>-1981.07</v>
       </c>
@@ -18992,7 +18638,6 @@
       <c r="F465" t="n">
         <v>14254.35</v>
       </c>
-      <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr">
         <is>
           <t>0591, 2751, 2762, 6410</t>
@@ -19036,7 +18681,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
       <c r="I466" t="n">
         <v>-2511.26</v>
       </c>
@@ -19075,7 +18719,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr"/>
       <c r="I467" t="n">
         <v>-5725.76</v>
       </c>
@@ -19114,7 +18757,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
       <c r="I468" t="n">
         <v>-5339.75</v>
       </c>
@@ -19153,7 +18795,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr"/>
       <c r="I469" t="n">
         <v>-2768.44</v>
       </c>
@@ -19192,7 +18833,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
       <c r="I470" t="n">
         <v>-1043.4</v>
       </c>
@@ -19231,7 +18871,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
       <c r="I471" t="n">
         <v>-2380.5</v>
       </c>
@@ -19270,7 +18909,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
       <c r="I472" t="n">
         <v>-1994.33</v>
       </c>
@@ -19309,7 +18947,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr"/>
       <c r="I473" t="n">
         <v>-1089.42</v>
       </c>
@@ -19348,7 +18985,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
       <c r="I474" t="n">
         <v>-1845.42</v>
       </c>
@@ -19430,7 +19066,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr"/>
       <c r="I476" t="n">
         <v>-3820.51</v>
       </c>
@@ -19469,7 +19104,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr"/>
       <c r="I477" t="n">
         <v>-2474.44</v>
       </c>
@@ -19508,7 +19142,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr"/>
       <c r="I478" t="n">
         <v>-1330.04</v>
       </c>
@@ -19547,7 +19180,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr"/>
       <c r="I479" t="n">
         <v>-1876.75</v>
       </c>
@@ -19586,7 +19218,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr"/>
       <c r="I480" t="n">
         <v>-2776.11</v>
       </c>
@@ -19625,7 +19256,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr"/>
       <c r="I481" t="n">
         <v>-3669.08</v>
       </c>
@@ -19664,7 +19294,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr"/>
       <c r="I482" t="n">
         <v>-999.28</v>
       </c>
@@ -19703,7 +19332,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr"/>
       <c r="I483" t="n">
         <v>-2146.52</v>
       </c>
@@ -19742,7 +19370,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr"/>
       <c r="I484" t="n">
         <v>-5419.47</v>
       </c>
@@ -19781,7 +19408,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr"/>
       <c r="I485" t="n">
         <v>-1645.51</v>
       </c>
@@ -19820,7 +19446,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
       <c r="I486" t="n">
         <v>-1503.09</v>
       </c>
@@ -19859,7 +19484,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
       <c r="I487" t="n">
         <v>-1907.52</v>
       </c>
@@ -19898,7 +19522,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
       <c r="I488" t="n">
         <v>-755.08</v>
       </c>
@@ -19937,7 +19560,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr"/>
       <c r="I489" t="n">
         <v>-2256.02</v>
       </c>
@@ -19976,7 +19598,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
       <c r="I490" t="n">
         <v>-1455.02</v>
       </c>
@@ -20015,7 +19636,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr"/>
       <c r="I491" t="n">
         <v>-1456.18</v>
       </c>
@@ -20054,7 +19674,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
       <c r="I492" t="n">
         <v>-2475.86</v>
       </c>
@@ -20093,7 +19712,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
       <c r="I493" t="n">
         <v>-523.95</v>
       </c>
@@ -20132,7 +19750,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr"/>
       <c r="I494" t="n">
         <v>-1603.26</v>
       </c>
@@ -20171,7 +19788,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr"/>
       <c r="I495" t="n">
         <v>-1146.36</v>
       </c>
@@ -20210,7 +19826,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr"/>
       <c r="I496" t="n">
         <v>-2548.67</v>
       </c>
@@ -20249,7 +19864,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr"/>
       <c r="I497" t="n">
         <v>-643.97</v>
       </c>
@@ -20288,7 +19902,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
       <c r="I498" t="n">
         <v>-1709.9</v>
       </c>
@@ -20327,7 +19940,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
       <c r="I499" t="n">
         <v>-2452.69</v>
       </c>
@@ -20366,7 +19978,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
       <c r="I500" t="n">
         <v>-2972.03</v>
       </c>
@@ -20405,7 +20016,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
         <v>-4124.67</v>
       </c>
@@ -20444,7 +20054,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
         <v>-641.3</v>
       </c>
@@ -20483,7 +20092,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr"/>
       <c r="I503" t="n">
         <v>-1039.39</v>
       </c>
@@ -20522,7 +20130,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
       <c r="I504" t="n">
         <v>-2821.15</v>
       </c>
@@ -20561,7 +20168,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
         <v>-4815.43</v>
       </c>
@@ -20600,7 +20206,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr"/>
       <c r="I506" t="n">
         <v>-2189.59</v>
       </c>
@@ -20639,7 +20244,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
       <c r="I507" t="n">
         <v>-1596.85</v>
       </c>
@@ -20678,7 +20282,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr"/>
       <c r="I508" t="n">
         <v>-1426.7</v>
       </c>
@@ -20803,7 +20406,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
       <c r="I511" t="n">
         <v>-656.89</v>
       </c>
@@ -20842,7 +20444,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr"/>
       <c r="I512" t="n">
         <v>-1446.93</v>
       </c>
@@ -20881,7 +20482,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
       <c r="I513" t="n">
         <v>-721.63</v>
       </c>
@@ -20920,7 +20520,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr"/>
       <c r="I514" t="n">
         <v>-2090.21</v>
       </c>
@@ -20959,7 +20558,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr"/>
       <c r="I515" t="n">
         <v>-2073.28</v>
       </c>
@@ -20998,7 +20596,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr"/>
       <c r="I516" t="n">
         <v>-1276.97</v>
       </c>
@@ -21080,7 +20677,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr"/>
       <c r="I518" t="n">
         <v>-763.0599999999999</v>
       </c>
@@ -21162,7 +20758,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr"/>
       <c r="I520" t="n">
         <v>-2034.98</v>
       </c>
@@ -21201,7 +20796,6 @@
           <t>6525, 6526, 6527</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr"/>
       <c r="I521" t="n">
         <v>-2581.99</v>
       </c>
@@ -21235,8 +20829,6 @@
       <c r="F522" t="n">
         <v>0</v>
       </c>
-      <c r="G522" t="inlineStr"/>
-      <c r="H522" t="inlineStr"/>
       <c r="I522" t="n">
         <v>0</v>
       </c>
@@ -21270,7 +20862,6 @@
       <c r="F523" t="n">
         <v>13331.12</v>
       </c>
-      <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21309,7 +20900,6 @@
       <c r="F524" t="n">
         <v>46588.11</v>
       </c>
-      <c r="G524" t="inlineStr"/>
       <c r="H524" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21391,7 +20981,6 @@
       <c r="F526" t="n">
         <v>12790.69</v>
       </c>
-      <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21602,7 +21191,6 @@
       <c r="F531" t="n">
         <v>1284.42</v>
       </c>
-      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21641,7 +21229,6 @@
       <c r="F532" t="n">
         <v>44001.42</v>
       </c>
-      <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21766,7 +21353,6 @@
       <c r="F535" t="n">
         <v>24577.43</v>
       </c>
-      <c r="G535" t="inlineStr"/>
       <c r="H535" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21805,7 +21391,6 @@
       <c r="F536" t="n">
         <v>7323.950000000001</v>
       </c>
-      <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21844,7 +21429,6 @@
       <c r="F537" t="n">
         <v>18898.37</v>
       </c>
-      <c r="G537" t="inlineStr"/>
       <c r="H537" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21883,7 +21467,6 @@
       <c r="F538" t="n">
         <v>45426.39</v>
       </c>
-      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
           <t>0010</t>
@@ -21922,7 +21505,6 @@
       <c r="F539" t="n">
         <v>905.5500000000002</v>
       </c>
-      <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
           <t>0010</t>
@@ -22047,7 +21629,6 @@
       <c r="F542" t="n">
         <v>8833.76</v>
       </c>
-      <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr">
         <is>
           <t>0010</t>
@@ -22301,7 +21882,6 @@
       <c r="F548" t="n">
         <v>16770.44</v>
       </c>
-      <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr">
         <is>
           <t>0010</t>
@@ -22512,7 +22092,6 @@
       <c r="F553" t="n">
         <v>7045.200000000001</v>
       </c>
-      <c r="G553" t="inlineStr"/>
       <c r="H553" t="inlineStr">
         <is>
           <t>0010</t>
@@ -22551,7 +22130,6 @@
       <c r="F554" t="n">
         <v>1482.59</v>
       </c>
-      <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr">
         <is>
           <t>0010</t>
@@ -23020,7 +22598,6 @@
       <c r="F565" t="n">
         <v>3777.219999999999</v>
       </c>
-      <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr">
         <is>
           <t>0010</t>
@@ -23360,7 +22937,6 @@
       <c r="F573" t="n">
         <v>2771.190000000001</v>
       </c>
-      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr">
         <is>
           <t>0010</t>
@@ -23442,7 +23018,6 @@
       <c r="F575" t="n">
         <v>3992.639999999999</v>
       </c>
-      <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr">
         <is>
           <t>0010</t>
@@ -23610,7 +23185,6 @@
       <c r="F579" t="n">
         <v>11693.16</v>
       </c>
-      <c r="G579" t="inlineStr"/>
       <c r="H579" t="inlineStr">
         <is>
           <t>0010</t>
@@ -23649,7 +23223,6 @@
       <c r="F580" t="n">
         <v>7388.08</v>
       </c>
-      <c r="G580" t="inlineStr"/>
       <c r="H580" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -23688,7 +23261,6 @@
       <c r="F581" t="n">
         <v>5270.21</v>
       </c>
-      <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23727,7 +23299,6 @@
       <c r="F582" t="n">
         <v>5774.85</v>
       </c>
-      <c r="G582" t="inlineStr"/>
       <c r="H582" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23766,7 +23337,6 @@
       <c r="F583" t="n">
         <v>5732.89</v>
       </c>
-      <c r="G583" t="inlineStr"/>
       <c r="H583" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23805,7 +23375,6 @@
       <c r="F584" t="n">
         <v>15822.16</v>
       </c>
-      <c r="G584" t="inlineStr"/>
       <c r="H584" t="inlineStr">
         <is>
           <t>1606, 1611, 3027</t>
@@ -23844,7 +23413,6 @@
       <c r="F585" t="n">
         <v>5122.63</v>
       </c>
-      <c r="G585" t="inlineStr"/>
       <c r="H585" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23883,7 +23451,6 @@
       <c r="F586" t="n">
         <v>5545.4</v>
       </c>
-      <c r="G586" t="inlineStr"/>
       <c r="H586" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23922,7 +23489,6 @@
       <c r="F587" t="n">
         <v>5576.91</v>
       </c>
-      <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr">
         <is>
           <t>1606</t>
@@ -23961,7 +23527,6 @@
       <c r="F588" t="n">
         <v>5701.82</v>
       </c>
-      <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24000,7 +23565,6 @@
       <c r="F589" t="n">
         <v>5757.21</v>
       </c>
-      <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24039,7 +23603,6 @@
       <c r="F590" t="n">
         <v>5668.78</v>
       </c>
-      <c r="G590" t="inlineStr"/>
       <c r="H590" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24078,7 +23641,6 @@
       <c r="F591" t="n">
         <v>15514.22</v>
       </c>
-      <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr">
         <is>
           <t>1606, 1611, 3027</t>
@@ -24117,7 +23679,6 @@
       <c r="F592" t="n">
         <v>5373.29</v>
       </c>
-      <c r="G592" t="inlineStr"/>
       <c r="H592" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24156,7 +23717,6 @@
       <c r="F593" t="n">
         <v>10115.9</v>
       </c>
-      <c r="G593" t="inlineStr"/>
       <c r="H593" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24195,7 +23755,6 @@
       <c r="F594" t="n">
         <v>5438.74</v>
       </c>
-      <c r="G594" t="inlineStr"/>
       <c r="H594" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24234,7 +23793,6 @@
       <c r="F595" t="n">
         <v>11075.02</v>
       </c>
-      <c r="G595" t="inlineStr"/>
       <c r="H595" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24273,7 +23831,6 @@
       <c r="F596" t="n">
         <v>5340.34</v>
       </c>
-      <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24312,7 +23869,6 @@
       <c r="F597" t="n">
         <v>5650.24</v>
       </c>
-      <c r="G597" t="inlineStr"/>
       <c r="H597" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24351,7 +23907,6 @@
       <c r="F598" t="n">
         <v>5774.16</v>
       </c>
-      <c r="G598" t="inlineStr"/>
       <c r="H598" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24390,7 +23945,6 @@
       <c r="F599" t="n">
         <v>15888.15</v>
       </c>
-      <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr">
         <is>
           <t>1606, 1611, 3027</t>
@@ -24429,7 +23983,6 @@
       <c r="F600" t="n">
         <v>12688.72</v>
       </c>
-      <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr">
         <is>
           <t>1606, 1611, 3067</t>
@@ -24468,7 +24021,6 @@
       <c r="F601" t="n">
         <v>16492.56</v>
       </c>
-      <c r="G601" t="inlineStr"/>
       <c r="H601" t="inlineStr">
         <is>
           <t>1606, 1611, 3027, 3067</t>
@@ -24507,7 +24059,6 @@
       <c r="F602" t="n">
         <v>9001.1</v>
       </c>
-      <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24546,7 +24097,6 @@
       <c r="F603" t="n">
         <v>9762.790000000001</v>
       </c>
-      <c r="G603" t="inlineStr"/>
       <c r="H603" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24585,7 +24135,6 @@
       <c r="F604" t="n">
         <v>5693.75</v>
       </c>
-      <c r="G604" t="inlineStr"/>
       <c r="H604" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24624,7 +24173,6 @@
       <c r="F605" t="n">
         <v>5779.94</v>
       </c>
-      <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24663,7 +24211,6 @@
       <c r="F606" t="n">
         <v>5417.57</v>
       </c>
-      <c r="G606" t="inlineStr"/>
       <c r="H606" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24702,7 +24249,6 @@
       <c r="F607" t="n">
         <v>5651.55</v>
       </c>
-      <c r="G607" t="inlineStr"/>
       <c r="H607" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24741,7 +24287,6 @@
       <c r="F608" t="n">
         <v>8672.23</v>
       </c>
-      <c r="G608" t="inlineStr"/>
       <c r="H608" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24780,7 +24325,6 @@
       <c r="F609" t="n">
         <v>11206.11</v>
       </c>
-      <c r="G609" t="inlineStr"/>
       <c r="H609" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -24819,7 +24363,6 @@
       <c r="F610" t="n">
         <v>10306.22</v>
       </c>
-      <c r="G610" t="inlineStr"/>
       <c r="H610" t="inlineStr">
         <is>
           <t>1606, 3027</t>
@@ -24858,7 +24401,6 @@
       <c r="F611" t="n">
         <v>5774.77</v>
       </c>
-      <c r="G611" t="inlineStr"/>
       <c r="H611" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24897,7 +24439,6 @@
       <c r="F612" t="n">
         <v>5584.62</v>
       </c>
-      <c r="G612" t="inlineStr"/>
       <c r="H612" t="inlineStr">
         <is>
           <t>1606</t>
@@ -24936,7 +24477,6 @@
       <c r="F613" t="n">
         <v>9042.970000000001</v>
       </c>
-      <c r="G613" t="inlineStr"/>
       <c r="H613" t="inlineStr">
         <is>
           <t>1606, 3027</t>
@@ -24975,7 +24515,6 @@
       <c r="F614" t="n">
         <v>4969.15</v>
       </c>
-      <c r="G614" t="inlineStr"/>
       <c r="H614" t="inlineStr">
         <is>
           <t>1606</t>
@@ -25014,7 +24553,6 @@
       <c r="F615" t="n">
         <v>10705.54</v>
       </c>
-      <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -25053,7 +24591,6 @@
       <c r="F616" t="n">
         <v>12431.77</v>
       </c>
-      <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr">
         <is>
           <t>1606, 1611, 3027</t>
@@ -25092,7 +24629,6 @@
       <c r="F617" t="n">
         <v>6515.379999999999</v>
       </c>
-      <c r="G617" t="inlineStr"/>
       <c r="H617" t="inlineStr">
         <is>
           <t>1606, 1611, 3067</t>
@@ -25131,7 +24667,6 @@
       <c r="F618" t="n">
         <v>11271.46</v>
       </c>
-      <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr">
         <is>
           <t>1606, 1611</t>
@@ -25170,7 +24705,6 @@
       <c r="F619" t="n">
         <v>5718.97</v>
       </c>
-      <c r="G619" t="inlineStr"/>
       <c r="H619" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25209,7 +24743,6 @@
       <c r="F620" t="n">
         <v>4870.88</v>
       </c>
-      <c r="G620" t="inlineStr"/>
       <c r="H620" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25248,7 +24781,6 @@
       <c r="F621" t="n">
         <v>4471.91</v>
       </c>
-      <c r="G621" t="inlineStr"/>
       <c r="H621" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25287,7 +24819,6 @@
       <c r="F622" t="n">
         <v>4573.83</v>
       </c>
-      <c r="G622" t="inlineStr"/>
       <c r="H622" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25326,7 +24857,6 @@
       <c r="F623" t="n">
         <v>4167.39</v>
       </c>
-      <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25365,7 +24895,6 @@
       <c r="F624" t="n">
         <v>5786.92</v>
       </c>
-      <c r="G624" t="inlineStr"/>
       <c r="H624" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25404,7 +24933,6 @@
       <c r="F625" t="n">
         <v>4127.2</v>
       </c>
-      <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25443,7 +24971,6 @@
       <c r="F626" t="n">
         <v>2322.97</v>
       </c>
-      <c r="G626" t="inlineStr"/>
       <c r="H626" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25482,7 +25009,6 @@
       <c r="F627" t="n">
         <v>5784.78</v>
       </c>
-      <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25521,7 +25047,6 @@
       <c r="F628" t="n">
         <v>5787.22</v>
       </c>
-      <c r="G628" t="inlineStr"/>
       <c r="H628" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25560,7 +25085,6 @@
       <c r="F629" t="n">
         <v>5786.93</v>
       </c>
-      <c r="G629" t="inlineStr"/>
       <c r="H629" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25599,7 +25123,6 @@
       <c r="F630" t="n">
         <v>4164.74</v>
       </c>
-      <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25638,7 +25161,6 @@
       <c r="F631" t="n">
         <v>5787.31</v>
       </c>
-      <c r="G631" t="inlineStr"/>
       <c r="H631" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25677,7 +25199,6 @@
       <c r="F632" t="n">
         <v>3228.38</v>
       </c>
-      <c r="G632" t="inlineStr"/>
       <c r="H632" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25716,7 +25237,6 @@
       <c r="F633" t="n">
         <v>5563.38</v>
       </c>
-      <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr">
         <is>
           <t>1804</t>
@@ -25755,7 +25275,6 @@
       <c r="F634" t="n">
         <v>4969.36</v>
       </c>
-      <c r="G634" t="inlineStr"/>
       <c r="H634" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25794,7 +25313,6 @@
       <c r="F635" t="n">
         <v>5688.42</v>
       </c>
-      <c r="G635" t="inlineStr"/>
       <c r="H635" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25833,7 +25351,6 @@
       <c r="F636" t="n">
         <v>5785.47</v>
       </c>
-      <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25872,7 +25389,6 @@
       <c r="F637" t="n">
         <v>5777.4</v>
       </c>
-      <c r="G637" t="inlineStr"/>
       <c r="H637" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25911,7 +25427,6 @@
       <c r="F638" t="n">
         <v>5491.49</v>
       </c>
-      <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25950,7 +25465,6 @@
       <c r="F639" t="n">
         <v>5660.04</v>
       </c>
-      <c r="G639" t="inlineStr"/>
       <c r="H639" t="inlineStr">
         <is>
           <t>0502</t>
@@ -25989,7 +25503,6 @@
       <c r="F640" t="n">
         <v>5741.34</v>
       </c>
-      <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26028,7 +25541,6 @@
       <c r="F641" t="n">
         <v>5747.4</v>
       </c>
-      <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26067,7 +25579,6 @@
       <c r="F642" t="n">
         <v>5771.43</v>
       </c>
-      <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26106,7 +25617,6 @@
       <c r="F643" t="n">
         <v>5782.08</v>
       </c>
-      <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26145,7 +25655,6 @@
       <c r="F644" t="n">
         <v>5765.07</v>
       </c>
-      <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26184,7 +25693,6 @@
       <c r="F645" t="n">
         <v>5255.91</v>
       </c>
-      <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26223,7 +25731,6 @@
       <c r="F646" t="n">
         <v>5708.24</v>
       </c>
-      <c r="G646" t="inlineStr"/>
       <c r="H646" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26262,7 +25769,6 @@
       <c r="F647" t="n">
         <v>5507.21</v>
       </c>
-      <c r="G647" t="inlineStr"/>
       <c r="H647" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26301,7 +25807,6 @@
       <c r="F648" t="n">
         <v>5720.83</v>
       </c>
-      <c r="G648" t="inlineStr"/>
       <c r="H648" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26340,7 +25845,6 @@
       <c r="F649" t="n">
         <v>5691.66</v>
       </c>
-      <c r="G649" t="inlineStr"/>
       <c r="H649" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26379,7 +25883,6 @@
       <c r="F650" t="n">
         <v>5448.81</v>
       </c>
-      <c r="G650" t="inlineStr"/>
       <c r="H650" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26418,7 +25921,6 @@
       <c r="F651" t="n">
         <v>5761.51</v>
       </c>
-      <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26457,7 +25959,6 @@
       <c r="F652" t="n">
         <v>5785.34</v>
       </c>
-      <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26496,7 +25997,6 @@
       <c r="F653" t="n">
         <v>5504.18</v>
       </c>
-      <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26535,7 +26035,6 @@
       <c r="F654" t="n">
         <v>4655.41</v>
       </c>
-      <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26574,7 +26073,6 @@
       <c r="F655" t="n">
         <v>4195.67</v>
       </c>
-      <c r="G655" t="inlineStr"/>
       <c r="H655" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26613,7 +26111,6 @@
       <c r="F656" t="n">
         <v>5292.83</v>
       </c>
-      <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26652,7 +26149,6 @@
       <c r="F657" t="n">
         <v>5439.1</v>
       </c>
-      <c r="G657" t="inlineStr"/>
       <c r="H657" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26691,7 +26187,6 @@
       <c r="F658" t="n">
         <v>5769.87</v>
       </c>
-      <c r="G658" t="inlineStr"/>
       <c r="H658" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26730,7 +26225,6 @@
       <c r="F659" t="n">
         <v>5786.45</v>
       </c>
-      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26769,7 +26263,6 @@
       <c r="F660" t="n">
         <v>5716.76</v>
       </c>
-      <c r="G660" t="inlineStr"/>
       <c r="H660" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26808,7 +26301,6 @@
       <c r="F661" t="n">
         <v>5761.76</v>
       </c>
-      <c r="G661" t="inlineStr"/>
       <c r="H661" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26847,7 +26339,6 @@
       <c r="F662" t="n">
         <v>5229.58</v>
       </c>
-      <c r="G662" t="inlineStr"/>
       <c r="H662" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26886,7 +26377,6 @@
       <c r="F663" t="n">
         <v>5397.49</v>
       </c>
-      <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26925,7 +26415,6 @@
       <c r="F664" t="n">
         <v>4877.45</v>
       </c>
-      <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr">
         <is>
           <t>0502</t>
@@ -26964,7 +26453,6 @@
       <c r="F665" t="n">
         <v>5784.84</v>
       </c>
-      <c r="G665" t="inlineStr"/>
       <c r="H665" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27003,7 +26491,6 @@
       <c r="F666" t="n">
         <v>5748.74</v>
       </c>
-      <c r="G666" t="inlineStr"/>
       <c r="H666" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27042,7 +26529,6 @@
       <c r="F667" t="n">
         <v>5300.65</v>
       </c>
-      <c r="G667" t="inlineStr"/>
       <c r="H667" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27081,7 +26567,6 @@
       <c r="F668" t="n">
         <v>5318.35</v>
       </c>
-      <c r="G668" t="inlineStr"/>
       <c r="H668" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27120,7 +26605,6 @@
       <c r="F669" t="n">
         <v>5620.6</v>
       </c>
-      <c r="G669" t="inlineStr"/>
       <c r="H669" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27159,7 +26643,6 @@
       <c r="F670" t="n">
         <v>4839.36</v>
       </c>
-      <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27198,7 +26681,6 @@
       <c r="F671" t="n">
         <v>3209.48</v>
       </c>
-      <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27237,7 +26719,6 @@
       <c r="F672" t="n">
         <v>5686.23</v>
       </c>
-      <c r="G672" t="inlineStr"/>
       <c r="H672" t="inlineStr">
         <is>
           <t>0502</t>
@@ -27276,8 +26757,6 @@
       <c r="F673" t="n">
         <v>0</v>
       </c>
-      <c r="G673" t="inlineStr"/>
-      <c r="H673" t="inlineStr"/>
       <c r="I673" t="n">
         <v>2913.63</v>
       </c>
@@ -27311,8 +26790,6 @@
       <c r="F674" t="n">
         <v>0</v>
       </c>
-      <c r="G674" t="inlineStr"/>
-      <c r="H674" t="inlineStr"/>
       <c r="I674" t="n">
         <v>300.01</v>
       </c>
@@ -27346,8 +26823,6 @@
       <c r="F675" t="n">
         <v>0</v>
       </c>
-      <c r="G675" t="inlineStr"/>
-      <c r="H675" t="inlineStr"/>
       <c r="I675" t="n">
         <v>354.21</v>
       </c>
@@ -27381,8 +26856,6 @@
       <c r="F676" t="n">
         <v>0</v>
       </c>
-      <c r="G676" t="inlineStr"/>
-      <c r="H676" t="inlineStr"/>
       <c r="I676" t="n">
         <v>594.66</v>
       </c>
@@ -27416,8 +26889,6 @@
       <c r="F677" t="n">
         <v>0</v>
       </c>
-      <c r="G677" t="inlineStr"/>
-      <c r="H677" t="inlineStr"/>
       <c r="I677" t="n">
         <v>1998.06</v>
       </c>
@@ -27451,8 +26922,6 @@
       <c r="F678" t="n">
         <v>0</v>
       </c>
-      <c r="G678" t="inlineStr"/>
-      <c r="H678" t="inlineStr"/>
       <c r="I678" t="n">
         <v>1288.26</v>
       </c>
@@ -27486,8 +26955,6 @@
       <c r="F679" t="n">
         <v>0</v>
       </c>
-      <c r="G679" t="inlineStr"/>
-      <c r="H679" t="inlineStr"/>
       <c r="I679" t="n">
         <v>972.9400000000001</v>
       </c>
@@ -27521,8 +26988,6 @@
       <c r="F680" t="n">
         <v>0</v>
       </c>
-      <c r="G680" t="inlineStr"/>
-      <c r="H680" t="inlineStr"/>
       <c r="I680" t="n">
         <v>431.53</v>
       </c>
@@ -27556,8 +27021,6 @@
       <c r="F681" t="n">
         <v>0</v>
       </c>
-      <c r="G681" t="inlineStr"/>
-      <c r="H681" t="inlineStr"/>
       <c r="I681" t="n">
         <v>466.79</v>
       </c>
@@ -27591,8 +27054,6 @@
       <c r="F682" t="n">
         <v>0</v>
       </c>
-      <c r="G682" t="inlineStr"/>
-      <c r="H682" t="inlineStr"/>
       <c r="I682" t="n">
         <v>341.13</v>
       </c>
@@ -27626,7 +27087,6 @@
       <c r="F683" t="n">
         <v>40769.33</v>
       </c>
-      <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr">
         <is>
           <t>0630</t>
@@ -27670,7 +27130,6 @@
           <t>0632</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr"/>
       <c r="I684" t="n">
         <v>-1702.59</v>
       </c>
@@ -27709,7 +27168,6 @@
           <t>0632</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr"/>
       <c r="I685" t="n">
         <v>-789.33</v>
       </c>
@@ -27743,7 +27201,6 @@
       <c r="F686" t="n">
         <v>16809.01</v>
       </c>
-      <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr">
         <is>
           <t>0631</t>
@@ -27782,7 +27239,6 @@
       <c r="F687" t="n">
         <v>8604.620000000001</v>
       </c>
-      <c r="G687" t="inlineStr"/>
       <c r="H687" t="inlineStr">
         <is>
           <t>0631</t>
@@ -27821,7 +27277,6 @@
       <c r="F688" t="n">
         <v>4138</v>
       </c>
-      <c r="G688" t="inlineStr"/>
       <c r="H688" t="inlineStr">
         <is>
           <t>0017</t>
@@ -27860,7 +27315,6 @@
       <c r="F689" t="n">
         <v>4138</v>
       </c>
-      <c r="G689" t="inlineStr"/>
       <c r="H689" t="inlineStr">
         <is>
           <t>0017</t>
@@ -27899,7 +27353,6 @@
       <c r="F690" t="n">
         <v>4138</v>
       </c>
-      <c r="G690" t="inlineStr"/>
       <c r="H690" t="inlineStr">
         <is>
           <t>0017</t>
@@ -27938,7 +27391,6 @@
       <c r="F691" t="n">
         <v>2454.08</v>
       </c>
-      <c r="G691" t="inlineStr"/>
       <c r="H691" t="inlineStr">
         <is>
           <t>6403</t>
@@ -27977,7 +27429,6 @@
       <c r="F692" t="n">
         <v>4639.35</v>
       </c>
-      <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28016,7 +27467,6 @@
       <c r="F693" t="n">
         <v>2807.360000000001</v>
       </c>
-      <c r="G693" t="inlineStr"/>
       <c r="H693" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28055,7 +27505,6 @@
       <c r="F694" t="n">
         <v>2801.04</v>
       </c>
-      <c r="G694" t="inlineStr"/>
       <c r="H694" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28094,7 +27543,6 @@
       <c r="F695" t="n">
         <v>2284.44</v>
       </c>
-      <c r="G695" t="inlineStr"/>
       <c r="H695" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28133,7 +27581,6 @@
       <c r="F696" t="n">
         <v>49.22000000000025</v>
       </c>
-      <c r="G696" t="inlineStr"/>
       <c r="H696" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28172,7 +27619,6 @@
       <c r="F697" t="n">
         <v>3168.38</v>
       </c>
-      <c r="G697" t="inlineStr"/>
       <c r="H697" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28211,7 +27657,6 @@
       <c r="F698" t="n">
         <v>1908.71</v>
       </c>
-      <c r="G698" t="inlineStr"/>
       <c r="H698" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28250,7 +27695,6 @@
       <c r="F699" t="n">
         <v>2986.6</v>
       </c>
-      <c r="G699" t="inlineStr"/>
       <c r="H699" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28375,7 +27819,6 @@
       <c r="F702" t="n">
         <v>1283.11</v>
       </c>
-      <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28457,7 +27900,6 @@
       <c r="F704" t="n">
         <v>3934.64</v>
       </c>
-      <c r="G704" t="inlineStr"/>
       <c r="H704" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28496,7 +27938,6 @@
       <c r="F705" t="n">
         <v>3045.07</v>
       </c>
-      <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28578,7 +28019,6 @@
       <c r="F707" t="n">
         <v>4539.57</v>
       </c>
-      <c r="G707" t="inlineStr"/>
       <c r="H707" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28617,7 +28057,6 @@
       <c r="F708" t="n">
         <v>3292.26</v>
       </c>
-      <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28656,7 +28095,6 @@
       <c r="F709" t="n">
         <v>1794.7</v>
       </c>
-      <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28695,7 +28133,6 @@
       <c r="F710" t="n">
         <v>4163.36</v>
       </c>
-      <c r="G710" t="inlineStr"/>
       <c r="H710" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28734,7 +28171,6 @@
       <c r="F711" t="n">
         <v>1826.98</v>
       </c>
-      <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr">
         <is>
           <t>6406</t>
@@ -28816,7 +28252,6 @@
       <c r="F713" t="n">
         <v>4846.3</v>
       </c>
-      <c r="G713" t="inlineStr"/>
       <c r="H713" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28898,7 +28333,6 @@
       <c r="F715" t="n">
         <v>3853.14</v>
       </c>
-      <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28937,7 +28371,6 @@
       <c r="F716" t="n">
         <v>1388.44</v>
       </c>
-      <c r="G716" t="inlineStr"/>
       <c r="H716" t="inlineStr">
         <is>
           <t>6403</t>
@@ -28976,7 +28409,6 @@
       <c r="F717" t="n">
         <v>814.8199999999997</v>
       </c>
-      <c r="G717" t="inlineStr"/>
       <c r="H717" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29015,7 +28447,6 @@
       <c r="F718" t="n">
         <v>4419.25</v>
       </c>
-      <c r="G718" t="inlineStr"/>
       <c r="H718" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29054,7 +28485,6 @@
       <c r="F719" t="n">
         <v>3572.54</v>
       </c>
-      <c r="G719" t="inlineStr"/>
       <c r="H719" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29093,7 +28523,6 @@
       <c r="F720" t="n">
         <v>4447.14</v>
       </c>
-      <c r="G720" t="inlineStr"/>
       <c r="H720" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29132,7 +28561,6 @@
       <c r="F721" t="n">
         <v>2871.92</v>
       </c>
-      <c r="G721" t="inlineStr"/>
       <c r="H721" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29171,7 +28599,6 @@
       <c r="F722" t="n">
         <v>5084.57</v>
       </c>
-      <c r="G722" t="inlineStr"/>
       <c r="H722" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29210,7 +28637,6 @@
       <c r="F723" t="n">
         <v>3798.95</v>
       </c>
-      <c r="G723" t="inlineStr"/>
       <c r="H723" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29249,7 +28675,6 @@
       <c r="F724" t="n">
         <v>2607.52</v>
       </c>
-      <c r="G724" t="inlineStr"/>
       <c r="H724" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29331,7 +28756,6 @@
       <c r="F726" t="n">
         <v>2244.7</v>
       </c>
-      <c r="G726" t="inlineStr"/>
       <c r="H726" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29370,7 +28794,6 @@
       <c r="F727" t="n">
         <v>4646.66</v>
       </c>
-      <c r="G727" t="inlineStr"/>
       <c r="H727" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29409,7 +28832,6 @@
       <c r="F728" t="n">
         <v>2595.6</v>
       </c>
-      <c r="G728" t="inlineStr"/>
       <c r="H728" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29448,7 +28870,6 @@
       <c r="F729" t="n">
         <v>775.4899999999998</v>
       </c>
-      <c r="G729" t="inlineStr"/>
       <c r="H729" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29487,7 +28908,6 @@
       <c r="F730" t="n">
         <v>2452.75</v>
       </c>
-      <c r="G730" t="inlineStr"/>
       <c r="H730" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29526,7 +28946,6 @@
       <c r="F731" t="n">
         <v>887.5799999999999</v>
       </c>
-      <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29565,7 +28984,6 @@
       <c r="F732" t="n">
         <v>3203.63</v>
       </c>
-      <c r="G732" t="inlineStr"/>
       <c r="H732" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29604,7 +29022,6 @@
       <c r="F733" t="n">
         <v>4379.79</v>
       </c>
-      <c r="G733" t="inlineStr"/>
       <c r="H733" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29643,7 +29060,6 @@
       <c r="F734" t="n">
         <v>2408.37</v>
       </c>
-      <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29682,7 +29098,6 @@
       <c r="F735" t="n">
         <v>2855.01</v>
       </c>
-      <c r="G735" t="inlineStr"/>
       <c r="H735" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29721,7 +29136,6 @@
       <c r="F736" t="n">
         <v>5013.78</v>
       </c>
-      <c r="G736" t="inlineStr"/>
       <c r="H736" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29760,7 +29174,6 @@
       <c r="F737" t="n">
         <v>4103.690000000001</v>
       </c>
-      <c r="G737" t="inlineStr"/>
       <c r="H737" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29799,7 +29212,6 @@
       <c r="F738" t="n">
         <v>4995.6</v>
       </c>
-      <c r="G738" t="inlineStr"/>
       <c r="H738" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29838,7 +29250,6 @@
       <c r="F739" t="n">
         <v>516.1499999999996</v>
       </c>
-      <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29877,7 +29288,6 @@
       <c r="F740" t="n">
         <v>2738.24</v>
       </c>
-      <c r="G740" t="inlineStr"/>
       <c r="H740" t="inlineStr">
         <is>
           <t>6403</t>
@@ -29916,7 +29326,6 @@
       <c r="F741" t="n">
         <v>3988.68</v>
       </c>
-      <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr">
         <is>
           <t>6406</t>
@@ -29998,7 +29407,6 @@
       <c r="F743" t="n">
         <v>2690.79</v>
       </c>
-      <c r="G743" t="inlineStr"/>
       <c r="H743" t="inlineStr">
         <is>
           <t>6406</t>
@@ -30037,7 +29445,6 @@
       <c r="F744" t="n">
         <v>1770.45</v>
       </c>
-      <c r="G744" t="inlineStr"/>
       <c r="H744" t="inlineStr">
         <is>
           <t>6403</t>
@@ -30076,7 +29483,6 @@
       <c r="F745" t="n">
         <v>236.7399999999998</v>
       </c>
-      <c r="G745" t="inlineStr"/>
       <c r="H745" t="inlineStr">
         <is>
           <t>6406</t>
@@ -30115,7 +29521,6 @@
       <c r="F746" t="n">
         <v>3041.65</v>
       </c>
-      <c r="G746" t="inlineStr"/>
       <c r="H746" t="inlineStr">
         <is>
           <t>6403</t>
@@ -30154,7 +29559,6 @@
       <c r="F747" t="n">
         <v>1935.47</v>
       </c>
-      <c r="G747" t="inlineStr"/>
       <c r="H747" t="inlineStr">
         <is>
           <t>6403</t>
@@ -30193,7 +29597,6 @@
       <c r="F748" t="n">
         <v>3927.28</v>
       </c>
-      <c r="G748" t="inlineStr"/>
       <c r="H748" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30232,7 +29635,6 @@
       <c r="F749" t="n">
         <v>4.800000000000182</v>
       </c>
-      <c r="G749" t="inlineStr"/>
       <c r="H749" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30271,7 +29673,6 @@
       <c r="F750" t="n">
         <v>290.3999999999996</v>
       </c>
-      <c r="G750" t="inlineStr"/>
       <c r="H750" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30310,7 +29711,6 @@
       <c r="F751" t="n">
         <v>3736.49</v>
       </c>
-      <c r="G751" t="inlineStr"/>
       <c r="H751" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30349,7 +29749,6 @@
       <c r="F752" t="n">
         <v>3470.09</v>
       </c>
-      <c r="G752" t="inlineStr"/>
       <c r="H752" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30388,7 +29787,6 @@
       <c r="F753" t="n">
         <v>2483.47</v>
       </c>
-      <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30427,7 +29825,6 @@
       <c r="F754" t="n">
         <v>4310.75</v>
       </c>
-      <c r="G754" t="inlineStr"/>
       <c r="H754" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30466,7 +29863,6 @@
       <c r="F755" t="n">
         <v>3439.77</v>
       </c>
-      <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30505,7 +29901,6 @@
       <c r="F756" t="n">
         <v>4421.22</v>
       </c>
-      <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30544,7 +29939,6 @@
       <c r="F757" t="n">
         <v>4812.209999999999</v>
       </c>
-      <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr">
         <is>
           <t>6525, 6533</t>
@@ -30583,7 +29977,6 @@
       <c r="F758" t="n">
         <v>1411.5</v>
       </c>
-      <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30622,7 +30015,6 @@
       <c r="F759" t="n">
         <v>2409.33</v>
       </c>
-      <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30661,7 +30053,6 @@
       <c r="F760" t="n">
         <v>3257.55</v>
       </c>
-      <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30700,7 +30091,6 @@
       <c r="F761" t="n">
         <v>4397.98</v>
       </c>
-      <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30739,7 +30129,6 @@
       <c r="F762" t="n">
         <v>3730.8</v>
       </c>
-      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30778,7 +30167,6 @@
       <c r="F763" t="n">
         <v>1520.14</v>
       </c>
-      <c r="G763" t="inlineStr"/>
       <c r="H763" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30817,7 +30205,6 @@
       <c r="F764" t="n">
         <v>5048.92</v>
       </c>
-      <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30856,7 +30243,6 @@
       <c r="F765" t="n">
         <v>4191.82</v>
       </c>
-      <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30895,7 +30281,6 @@
       <c r="F766" t="n">
         <v>219.3900000000003</v>
       </c>
-      <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30934,7 +30319,6 @@
       <c r="F767" t="n">
         <v>4569.52</v>
       </c>
-      <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr">
         <is>
           <t>6525</t>
@@ -30973,7 +30357,6 @@
       <c r="F768" t="n">
         <v>3123.25</v>
       </c>
-      <c r="G768" t="inlineStr"/>
       <c r="H768" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31012,7 +30395,6 @@
       <c r="F769" t="n">
         <v>4375.15</v>
       </c>
-      <c r="G769" t="inlineStr"/>
       <c r="H769" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31051,7 +30433,6 @@
       <c r="F770" t="n">
         <v>5230.08</v>
       </c>
-      <c r="G770" t="inlineStr"/>
       <c r="H770" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31090,7 +30471,6 @@
       <c r="F771" t="n">
         <v>2562.48</v>
       </c>
-      <c r="G771" t="inlineStr"/>
       <c r="H771" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31129,7 +30509,6 @@
       <c r="F772" t="n">
         <v>4710.83</v>
       </c>
-      <c r="G772" t="inlineStr"/>
       <c r="H772" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31168,7 +30547,6 @@
       <c r="F773" t="n">
         <v>3154.33</v>
       </c>
-      <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31207,7 +30585,6 @@
       <c r="F774" t="n">
         <v>2397.16</v>
       </c>
-      <c r="G774" t="inlineStr"/>
       <c r="H774" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31246,7 +30623,6 @@
       <c r="F775" t="n">
         <v>5401.54</v>
       </c>
-      <c r="G775" t="inlineStr"/>
       <c r="H775" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31285,7 +30661,6 @@
       <c r="F776" t="n">
         <v>4600.86</v>
       </c>
-      <c r="G776" t="inlineStr"/>
       <c r="H776" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31324,7 +30699,6 @@
       <c r="F777" t="n">
         <v>4939.809999999999</v>
       </c>
-      <c r="G777" t="inlineStr"/>
       <c r="H777" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31363,7 +30737,6 @@
       <c r="F778" t="n">
         <v>3899.52</v>
       </c>
-      <c r="G778" t="inlineStr"/>
       <c r="H778" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31402,7 +30775,6 @@
       <c r="F779" t="n">
         <v>5312.5</v>
       </c>
-      <c r="G779" t="inlineStr"/>
       <c r="H779" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31441,7 +30813,6 @@
       <c r="F780" t="n">
         <v>4521.76</v>
       </c>
-      <c r="G780" t="inlineStr"/>
       <c r="H780" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31480,7 +30851,6 @@
       <c r="F781" t="n">
         <v>3970.72</v>
       </c>
-      <c r="G781" t="inlineStr"/>
       <c r="H781" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31519,7 +30889,6 @@
       <c r="F782" t="n">
         <v>2023.14</v>
       </c>
-      <c r="G782" t="inlineStr"/>
       <c r="H782" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31558,7 +30927,6 @@
       <c r="F783" t="n">
         <v>1167.32</v>
       </c>
-      <c r="G783" t="inlineStr"/>
       <c r="H783" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31597,7 +30965,6 @@
       <c r="F784" t="n">
         <v>5314.48</v>
       </c>
-      <c r="G784" t="inlineStr"/>
       <c r="H784" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31636,7 +31003,6 @@
       <c r="F785" t="n">
         <v>3454.62</v>
       </c>
-      <c r="G785" t="inlineStr"/>
       <c r="H785" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31675,7 +31041,6 @@
       <c r="F786" t="n">
         <v>2132.09</v>
       </c>
-      <c r="G786" t="inlineStr"/>
       <c r="H786" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31714,7 +31079,6 @@
       <c r="F787" t="n">
         <v>651.9200000000001</v>
       </c>
-      <c r="G787" t="inlineStr"/>
       <c r="H787" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31753,7 +31117,6 @@
       <c r="F788" t="n">
         <v>2599.15</v>
       </c>
-      <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31792,7 +31155,6 @@
       <c r="F789" t="n">
         <v>4605.62</v>
       </c>
-      <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31831,7 +31193,6 @@
       <c r="F790" t="n">
         <v>4731.84</v>
       </c>
-      <c r="G790" t="inlineStr"/>
       <c r="H790" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31870,7 +31231,6 @@
       <c r="F791" t="n">
         <v>9381.4</v>
       </c>
-      <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr">
         <is>
           <t>6525, 6533</t>
@@ -31909,7 +31269,6 @@
       <c r="F792" t="n">
         <v>670.3199999999997</v>
       </c>
-      <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31948,7 +31307,6 @@
       <c r="F793" t="n">
         <v>5302.92</v>
       </c>
-      <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr">
         <is>
           <t>6525</t>
@@ -31987,7 +31345,6 @@
       <c r="F794" t="n">
         <v>4716.84</v>
       </c>
-      <c r="G794" t="inlineStr"/>
       <c r="H794" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32026,7 +31383,6 @@
       <c r="F795" t="n">
         <v>5254.89</v>
       </c>
-      <c r="G795" t="inlineStr"/>
       <c r="H795" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32065,7 +31421,6 @@
       <c r="F796" t="n">
         <v>2666.92</v>
       </c>
-      <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32104,7 +31459,6 @@
       <c r="F797" t="n">
         <v>4252.17</v>
       </c>
-      <c r="G797" t="inlineStr"/>
       <c r="H797" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32143,7 +31497,6 @@
       <c r="F798" t="n">
         <v>4842.92</v>
       </c>
-      <c r="G798" t="inlineStr"/>
       <c r="H798" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32182,7 +31535,6 @@
       <c r="F799" t="n">
         <v>9856.49</v>
       </c>
-      <c r="G799" t="inlineStr"/>
       <c r="H799" t="inlineStr">
         <is>
           <t>6525, 6533</t>
@@ -32221,7 +31573,6 @@
       <c r="F800" t="n">
         <v>3648.49</v>
       </c>
-      <c r="G800" t="inlineStr"/>
       <c r="H800" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32260,7 +31611,6 @@
       <c r="F801" t="n">
         <v>3674</v>
       </c>
-      <c r="G801" t="inlineStr"/>
       <c r="H801" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32299,7 +31649,6 @@
       <c r="F802" t="n">
         <v>2703.43</v>
       </c>
-      <c r="G802" t="inlineStr"/>
       <c r="H802" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32338,7 +31687,6 @@
       <c r="F803" t="n">
         <v>3874.82</v>
       </c>
-      <c r="G803" t="inlineStr"/>
       <c r="H803" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32377,7 +31725,6 @@
       <c r="F804" t="n">
         <v>3734.51</v>
       </c>
-      <c r="G804" t="inlineStr"/>
       <c r="H804" t="inlineStr">
         <is>
           <t>6525</t>
@@ -32416,7 +31763,6 @@
       <c r="F805" t="n">
         <v>2687.549999999999</v>
       </c>
-      <c r="G805" t="inlineStr"/>
       <c r="H805" t="inlineStr">
         <is>
           <t>0019</t>
@@ -32455,7 +31801,6 @@
       <c r="F806" t="n">
         <v>3215.69</v>
       </c>
-      <c r="G806" t="inlineStr"/>
       <c r="H806" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32494,7 +31839,6 @@
       <c r="F807" t="n">
         <v>9924.83</v>
       </c>
-      <c r="G807" t="inlineStr"/>
       <c r="H807" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32533,7 +31877,6 @@
       <c r="F808" t="n">
         <v>9137.18</v>
       </c>
-      <c r="G808" t="inlineStr"/>
       <c r="H808" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32572,7 +31915,6 @@
       <c r="F809" t="n">
         <v>214.3900000000003</v>
       </c>
-      <c r="G809" t="inlineStr"/>
       <c r="H809" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32611,7 +31953,6 @@
       <c r="F810" t="n">
         <v>508.4799999999996</v>
       </c>
-      <c r="G810" t="inlineStr"/>
       <c r="H810" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32650,7 +31991,6 @@
       <c r="F811" t="n">
         <v>329.2600000000002</v>
       </c>
-      <c r="G811" t="inlineStr"/>
       <c r="H811" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32689,7 +32029,6 @@
       <c r="F812" t="n">
         <v>1789.31</v>
       </c>
-      <c r="G812" t="inlineStr"/>
       <c r="H812" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32728,7 +32067,6 @@
       <c r="F813" t="n">
         <v>542.9300000000003</v>
       </c>
-      <c r="G813" t="inlineStr"/>
       <c r="H813" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32767,7 +32105,6 @@
       <c r="F814" t="n">
         <v>3666.27</v>
       </c>
-      <c r="G814" t="inlineStr"/>
       <c r="H814" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32806,7 +32143,6 @@
       <c r="F815" t="n">
         <v>5005.25</v>
       </c>
-      <c r="G815" t="inlineStr"/>
       <c r="H815" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32845,7 +32181,6 @@
       <c r="F816" t="n">
         <v>3779.94</v>
       </c>
-      <c r="G816" t="inlineStr"/>
       <c r="H816" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32884,7 +32219,6 @@
       <c r="F817" t="n">
         <v>1710.91</v>
       </c>
-      <c r="G817" t="inlineStr"/>
       <c r="H817" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32923,7 +32257,6 @@
       <c r="F818" t="n">
         <v>4117.92</v>
       </c>
-      <c r="G818" t="inlineStr"/>
       <c r="H818" t="inlineStr">
         <is>
           <t>1801</t>
@@ -32962,7 +32295,6 @@
       <c r="F819" t="n">
         <v>947.6499999999996</v>
       </c>
-      <c r="G819" t="inlineStr"/>
       <c r="H819" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33001,7 +32333,6 @@
       <c r="F820" t="n">
         <v>3072.25</v>
       </c>
-      <c r="G820" t="inlineStr"/>
       <c r="H820" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33040,7 +32371,6 @@
       <c r="F821" t="n">
         <v>4670.25</v>
       </c>
-      <c r="G821" t="inlineStr"/>
       <c r="H821" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33079,7 +32409,6 @@
       <c r="F822" t="n">
         <v>4144.58</v>
       </c>
-      <c r="G822" t="inlineStr"/>
       <c r="H822" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33118,7 +32447,6 @@
       <c r="F823" t="n">
         <v>3227.64</v>
       </c>
-      <c r="G823" t="inlineStr"/>
       <c r="H823" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33157,7 +32485,6 @@
       <c r="F824" t="n">
         <v>979.5299999999997</v>
       </c>
-      <c r="G824" t="inlineStr"/>
       <c r="H824" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33196,7 +32523,6 @@
       <c r="F825" t="n">
         <v>3668.26</v>
       </c>
-      <c r="G825" t="inlineStr"/>
       <c r="H825" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33235,7 +32561,6 @@
       <c r="F826" t="n">
         <v>4919.66</v>
       </c>
-      <c r="G826" t="inlineStr"/>
       <c r="H826" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33274,7 +32599,6 @@
       <c r="F827" t="n">
         <v>2928.01</v>
       </c>
-      <c r="G827" t="inlineStr"/>
       <c r="H827" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33313,7 +32637,6 @@
       <c r="F828" t="n">
         <v>3486.6</v>
       </c>
-      <c r="G828" t="inlineStr"/>
       <c r="H828" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33352,7 +32675,6 @@
       <c r="F829" t="n">
         <v>1938.04</v>
       </c>
-      <c r="G829" t="inlineStr"/>
       <c r="H829" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33391,7 +32713,6 @@
       <c r="F830" t="n">
         <v>4496.38</v>
       </c>
-      <c r="G830" t="inlineStr"/>
       <c r="H830" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33430,7 +32751,6 @@
       <c r="F831" t="n">
         <v>2380.86</v>
       </c>
-      <c r="G831" t="inlineStr"/>
       <c r="H831" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33469,7 +32789,6 @@
       <c r="F832" t="n">
         <v>1118.83</v>
       </c>
-      <c r="G832" t="inlineStr"/>
       <c r="H832" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33508,7 +32827,6 @@
       <c r="F833" t="n">
         <v>3445.17</v>
       </c>
-      <c r="G833" t="inlineStr"/>
       <c r="H833" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33547,7 +32865,6 @@
       <c r="F834" t="n">
         <v>5520.83</v>
       </c>
-      <c r="G834" t="inlineStr"/>
       <c r="H834" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33586,7 +32903,6 @@
       <c r="F835" t="n">
         <v>4542.26</v>
       </c>
-      <c r="G835" t="inlineStr"/>
       <c r="H835" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33625,7 +32941,6 @@
       <c r="F836" t="n">
         <v>837.0600000000004</v>
       </c>
-      <c r="G836" t="inlineStr"/>
       <c r="H836" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33664,7 +32979,6 @@
       <c r="F837" t="n">
         <v>3054.360000000001</v>
       </c>
-      <c r="G837" t="inlineStr"/>
       <c r="H837" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33703,7 +33017,6 @@
       <c r="F838" t="n">
         <v>8158.32</v>
       </c>
-      <c r="G838" t="inlineStr"/>
       <c r="H838" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33742,7 +33055,6 @@
       <c r="F839" t="n">
         <v>817.1800000000003</v>
       </c>
-      <c r="G839" t="inlineStr"/>
       <c r="H839" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33781,7 +33093,6 @@
       <c r="F840" t="n">
         <v>2640.82</v>
       </c>
-      <c r="G840" t="inlineStr"/>
       <c r="H840" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33820,7 +33131,6 @@
       <c r="F841" t="n">
         <v>2918.43</v>
       </c>
-      <c r="G841" t="inlineStr"/>
       <c r="H841" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33859,7 +33169,6 @@
       <c r="F842" t="n">
         <v>4553.91</v>
       </c>
-      <c r="G842" t="inlineStr"/>
       <c r="H842" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33898,7 +33207,6 @@
       <c r="F843" t="n">
         <v>7342.139999999999</v>
       </c>
-      <c r="G843" t="inlineStr"/>
       <c r="H843" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33937,7 +33245,6 @@
       <c r="F844" t="n">
         <v>4470.42</v>
       </c>
-      <c r="G844" t="inlineStr"/>
       <c r="H844" t="inlineStr">
         <is>
           <t>1801</t>
@@ -33976,7 +33283,6 @@
       <c r="F845" t="n">
         <v>2646.3</v>
       </c>
-      <c r="G845" t="inlineStr"/>
       <c r="H845" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34015,7 +33321,6 @@
       <c r="F846" t="n">
         <v>4386.940000000001</v>
       </c>
-      <c r="G846" t="inlineStr"/>
       <c r="H846" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34054,7 +33359,6 @@
       <c r="F847" t="n">
         <v>2065.43</v>
       </c>
-      <c r="G847" t="inlineStr"/>
       <c r="H847" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34093,7 +33397,6 @@
       <c r="F848" t="n">
         <v>3052.33</v>
       </c>
-      <c r="G848" t="inlineStr"/>
       <c r="H848" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34132,7 +33435,6 @@
       <c r="F849" t="n">
         <v>3220.24</v>
       </c>
-      <c r="G849" t="inlineStr"/>
       <c r="H849" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34171,7 +33473,6 @@
       <c r="F850" t="n">
         <v>3432.19</v>
       </c>
-      <c r="G850" t="inlineStr"/>
       <c r="H850" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34210,7 +33511,6 @@
       <c r="F851" t="n">
         <v>2853.81</v>
       </c>
-      <c r="G851" t="inlineStr"/>
       <c r="H851" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34249,7 +33549,6 @@
       <c r="F852" t="n">
         <v>178.7700000000004</v>
       </c>
-      <c r="G852" t="inlineStr"/>
       <c r="H852" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34288,7 +33587,6 @@
       <c r="F853" t="n">
         <v>2428.39</v>
       </c>
-      <c r="G853" t="inlineStr"/>
       <c r="H853" t="inlineStr">
         <is>
           <t>1801, 3535</t>
@@ -34327,7 +33625,6 @@
       <c r="F854" t="n">
         <v>694.25</v>
       </c>
-      <c r="G854" t="inlineStr"/>
       <c r="H854" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34366,7 +33663,6 @@
       <c r="F855" t="n">
         <v>3367.99</v>
       </c>
-      <c r="G855" t="inlineStr"/>
       <c r="H855" t="inlineStr">
         <is>
           <t>1801</t>
@@ -34405,7 +33701,6 @@
       <c r="F856" t="n">
         <v>5594.87</v>
       </c>
-      <c r="G856" t="inlineStr"/>
       <c r="H856" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34444,7 +33739,6 @@
       <c r="F857" t="n">
         <v>3194.35</v>
       </c>
-      <c r="G857" t="inlineStr"/>
       <c r="H857" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34483,7 +33777,6 @@
       <c r="F858" t="n">
         <v>5495.15</v>
       </c>
-      <c r="G858" t="inlineStr"/>
       <c r="H858" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34522,7 +33815,6 @@
       <c r="F859" t="n">
         <v>5129.93</v>
       </c>
-      <c r="G859" t="inlineStr"/>
       <c r="H859" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34561,7 +33853,6 @@
       <c r="F860" t="n">
         <v>5618.83</v>
       </c>
-      <c r="G860" t="inlineStr"/>
       <c r="H860" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34600,7 +33891,6 @@
       <c r="F861" t="n">
         <v>5464.26</v>
       </c>
-      <c r="G861" t="inlineStr"/>
       <c r="H861" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34639,7 +33929,6 @@
       <c r="F862" t="n">
         <v>4757.67</v>
       </c>
-      <c r="G862" t="inlineStr"/>
       <c r="H862" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34678,7 +33967,6 @@
       <c r="F863" t="n">
         <v>5686</v>
       </c>
-      <c r="G863" t="inlineStr"/>
       <c r="H863" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34717,7 +34005,6 @@
       <c r="F864" t="n">
         <v>5578.74</v>
       </c>
-      <c r="G864" t="inlineStr"/>
       <c r="H864" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34756,7 +34043,6 @@
       <c r="F865" t="n">
         <v>5545.61</v>
       </c>
-      <c r="G865" t="inlineStr"/>
       <c r="H865" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34795,7 +34081,6 @@
       <c r="F866" t="n">
         <v>5219.77</v>
       </c>
-      <c r="G866" t="inlineStr"/>
       <c r="H866" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34834,7 +34119,6 @@
       <c r="F867" t="n">
         <v>5684.26</v>
       </c>
-      <c r="G867" t="inlineStr"/>
       <c r="H867" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34873,7 +34157,6 @@
       <c r="F868" t="n">
         <v>5583.86</v>
       </c>
-      <c r="G868" t="inlineStr"/>
       <c r="H868" t="inlineStr">
         <is>
           <t>0842</t>
@@ -34912,7 +34195,6 @@
       <c r="F869" t="n">
         <v>4092.89</v>
       </c>
-      <c r="G869" t="inlineStr"/>
       <c r="H869" t="inlineStr">
         <is>
           <t>8100</t>
@@ -34951,7 +34233,6 @@
       <c r="F870" t="n">
         <v>4402.440000000001</v>
       </c>
-      <c r="G870" t="inlineStr"/>
       <c r="H870" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -34990,7 +34271,6 @@
       <c r="F871" t="n">
         <v>6671.840000000001</v>
       </c>
-      <c r="G871" t="inlineStr"/>
       <c r="H871" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -35029,7 +34309,6 @@
       <c r="F872" t="n">
         <v>5922.02</v>
       </c>
-      <c r="G872" t="inlineStr"/>
       <c r="H872" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -35068,7 +34347,6 @@
       <c r="F873" t="n">
         <v>5099</v>
       </c>
-      <c r="G873" t="inlineStr"/>
       <c r="H873" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -35107,7 +34385,6 @@
       <c r="F874" t="n">
         <v>4253.25</v>
       </c>
-      <c r="G874" t="inlineStr"/>
       <c r="H874" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -35146,7 +34423,6 @@
       <c r="F875" t="n">
         <v>1429.87</v>
       </c>
-      <c r="G875" t="inlineStr"/>
       <c r="H875" t="inlineStr">
         <is>
           <t>8103, 8105</t>
@@ -35185,7 +34461,6 @@
       <c r="F876" t="n">
         <v>6742.01</v>
       </c>
-      <c r="G876" t="inlineStr"/>
       <c r="H876" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -35224,7 +34499,6 @@
       <c r="F877" t="n">
         <v>4095.219999999999</v>
       </c>
-      <c r="G877" t="inlineStr"/>
       <c r="H877" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -35263,7 +34537,6 @@
       <c r="F878" t="n">
         <v>6052.139999999999</v>
       </c>
-      <c r="G878" t="inlineStr"/>
       <c r="H878" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -35302,7 +34575,6 @@
       <c r="F879" t="n">
         <v>3712.22</v>
       </c>
-      <c r="G879" t="inlineStr"/>
       <c r="H879" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -35341,7 +34613,6 @@
       <c r="F880" t="n">
         <v>3507.42</v>
       </c>
-      <c r="G880" t="inlineStr"/>
       <c r="H880" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -35380,7 +34651,6 @@
       <c r="F881" t="n">
         <v>710.2099999999991</v>
       </c>
-      <c r="G881" t="inlineStr"/>
       <c r="H881" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -35419,7 +34689,6 @@
       <c r="F882" t="n">
         <v>3438.04</v>
       </c>
-      <c r="G882" t="inlineStr"/>
       <c r="H882" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -35458,7 +34727,6 @@
       <c r="F883" t="n">
         <v>6330.58</v>
       </c>
-      <c r="G883" t="inlineStr"/>
       <c r="H883" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -35497,7 +34765,6 @@
       <c r="F884" t="n">
         <v>4960.06</v>
       </c>
-      <c r="G884" t="inlineStr"/>
       <c r="H884" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -35536,7 +34803,6 @@
       <c r="F885" t="n">
         <v>2149.440000000001</v>
       </c>
-      <c r="G885" t="inlineStr"/>
       <c r="H885" t="inlineStr">
         <is>
           <t>8104, 8105</t>
@@ -35575,7 +34841,6 @@
       <c r="F886" t="n">
         <v>9243.970000000001</v>
       </c>
-      <c r="G886" t="inlineStr"/>
       <c r="H886" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -35614,7 +34879,6 @@
       <c r="F887" t="n">
         <v>6413.68</v>
       </c>
-      <c r="G887" t="inlineStr"/>
       <c r="H887" t="inlineStr">
         <is>
           <t>8103, 8105</t>
@@ -35653,7 +34917,6 @@
       <c r="F888" t="n">
         <v>6591.559999999999</v>
       </c>
-      <c r="G888" t="inlineStr"/>
       <c r="H888" t="inlineStr">
         <is>
           <t>8104, 8105</t>
@@ -35692,7 +34955,6 @@
       <c r="F889" t="n">
         <v>7657.369999999999</v>
       </c>
-      <c r="G889" t="inlineStr"/>
       <c r="H889" t="inlineStr">
         <is>
           <t>8104, 8105</t>
@@ -35731,7 +34993,6 @@
       <c r="F890" t="n">
         <v>3715.33</v>
       </c>
-      <c r="G890" t="inlineStr"/>
       <c r="H890" t="inlineStr">
         <is>
           <t>8103, 8105</t>
@@ -35770,7 +35031,6 @@
       <c r="F891" t="n">
         <v>6254.6</v>
       </c>
-      <c r="G891" t="inlineStr"/>
       <c r="H891" t="inlineStr">
         <is>
           <t>8103, 8105</t>
@@ -35809,7 +35069,6 @@
       <c r="F892" t="n">
         <v>9497.98</v>
       </c>
-      <c r="G892" t="inlineStr"/>
       <c r="H892" t="inlineStr">
         <is>
           <t>8104, 8105</t>
@@ -35848,7 +35107,6 @@
       <c r="F893" t="n">
         <v>605.2599999999993</v>
       </c>
-      <c r="G893" t="inlineStr"/>
       <c r="H893" t="inlineStr">
         <is>
           <t>8103, 8105</t>
@@ -35887,7 +35145,6 @@
       <c r="F894" t="n">
         <v>7726.57</v>
       </c>
-      <c r="G894" t="inlineStr"/>
       <c r="H894" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -35926,7 +35183,6 @@
       <c r="F895" t="n">
         <v>2540.810000000001</v>
       </c>
-      <c r="G895" t="inlineStr"/>
       <c r="H895" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -35965,7 +35221,6 @@
       <c r="F896" t="n">
         <v>535.8299999999999</v>
       </c>
-      <c r="G896" t="inlineStr"/>
       <c r="H896" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36004,7 +35259,6 @@
       <c r="F897" t="n">
         <v>10044.55</v>
       </c>
-      <c r="G897" t="inlineStr"/>
       <c r="H897" t="inlineStr">
         <is>
           <t>8101, 8108</t>
@@ -36043,7 +35297,6 @@
       <c r="F898" t="n">
         <v>6912.320000000001</v>
       </c>
-      <c r="G898" t="inlineStr"/>
       <c r="H898" t="inlineStr">
         <is>
           <t>8102, 8105</t>
@@ -36082,7 +35335,6 @@
       <c r="F899" t="n">
         <v>8862.030000000001</v>
       </c>
-      <c r="G899" t="inlineStr"/>
       <c r="H899" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -36121,7 +35373,6 @@
       <c r="F900" t="n">
         <v>4642.68</v>
       </c>
-      <c r="G900" t="inlineStr"/>
       <c r="H900" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -36160,7 +35411,6 @@
       <c r="F901" t="n">
         <v>10071.56</v>
       </c>
-      <c r="G901" t="inlineStr"/>
       <c r="H901" t="inlineStr">
         <is>
           <t>8102, 8105</t>
@@ -36199,7 +35449,6 @@
       <c r="F902" t="n">
         <v>7180.77</v>
       </c>
-      <c r="G902" t="inlineStr"/>
       <c r="H902" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -36238,7 +35487,6 @@
       <c r="F903" t="n">
         <v>4333.429999999999</v>
       </c>
-      <c r="G903" t="inlineStr"/>
       <c r="H903" t="inlineStr">
         <is>
           <t>8104, 8108</t>
@@ -36277,7 +35525,6 @@
       <c r="F904" t="n">
         <v>3662.84</v>
       </c>
-      <c r="G904" t="inlineStr"/>
       <c r="H904" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -36316,7 +35563,6 @@
       <c r="F905" t="n">
         <v>5317.73</v>
       </c>
-      <c r="G905" t="inlineStr"/>
       <c r="H905" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -36355,7 +35601,6 @@
       <c r="F906" t="n">
         <v>9567.15</v>
       </c>
-      <c r="G906" t="inlineStr"/>
       <c r="H906" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -36394,7 +35639,6 @@
       <c r="F907" t="n">
         <v>5805.88</v>
       </c>
-      <c r="G907" t="inlineStr"/>
       <c r="H907" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -36433,7 +35677,6 @@
       <c r="F908" t="n">
         <v>187.2100000000009</v>
       </c>
-      <c r="G908" t="inlineStr"/>
       <c r="H908" t="inlineStr">
         <is>
           <t>8100, 8108</t>
@@ -36472,7 +35715,6 @@
       <c r="F909" t="n">
         <v>4711.41</v>
       </c>
-      <c r="G909" t="inlineStr"/>
       <c r="H909" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36511,7 +35753,6 @@
       <c r="F910" t="n">
         <v>99.09000000000015</v>
       </c>
-      <c r="G910" t="inlineStr"/>
       <c r="H910" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36550,7 +35791,6 @@
       <c r="F911" t="n">
         <v>7019.96</v>
       </c>
-      <c r="G911" t="inlineStr"/>
       <c r="H911" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36589,7 +35829,6 @@
       <c r="F912" t="n">
         <v>8243.469999999999</v>
       </c>
-      <c r="G912" t="inlineStr"/>
       <c r="H912" t="inlineStr">
         <is>
           <t>8102, 8105</t>
@@ -36628,7 +35867,6 @@
       <c r="F913" t="n">
         <v>6813.87</v>
       </c>
-      <c r="G913" t="inlineStr"/>
       <c r="H913" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -36667,7 +35905,6 @@
       <c r="F914" t="n">
         <v>6592.969999999998</v>
       </c>
-      <c r="G914" t="inlineStr"/>
       <c r="H914" t="inlineStr">
         <is>
           <t>8103, 8108</t>
@@ -36706,7 +35943,6 @@
       <c r="F915" t="n">
         <v>10176.75</v>
       </c>
-      <c r="G915" t="inlineStr"/>
       <c r="H915" t="inlineStr">
         <is>
           <t>8102, 8105</t>
@@ -36745,7 +35981,6 @@
       <c r="F916" t="n">
         <v>7989.09</v>
       </c>
-      <c r="G916" t="inlineStr"/>
       <c r="H916" t="inlineStr">
         <is>
           <t>8100, 8105</t>
@@ -36784,7 +36019,6 @@
       <c r="F917" t="n">
         <v>9893.42</v>
       </c>
-      <c r="G917" t="inlineStr"/>
       <c r="H917" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36823,7 +36057,6 @@
       <c r="F918" t="n">
         <v>621.5299999999997</v>
       </c>
-      <c r="G918" t="inlineStr"/>
       <c r="H918" t="inlineStr">
         <is>
           <t>8102, 8105</t>
@@ -36862,7 +36095,6 @@
       <c r="F919" t="n">
         <v>6091.13</v>
       </c>
-      <c r="G919" t="inlineStr"/>
       <c r="H919" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36901,7 +36133,6 @@
       <c r="F920" t="n">
         <v>8593.99</v>
       </c>
-      <c r="G920" t="inlineStr"/>
       <c r="H920" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36940,7 +36171,6 @@
       <c r="F921" t="n">
         <v>8219.969999999999</v>
       </c>
-      <c r="G921" t="inlineStr"/>
       <c r="H921" t="inlineStr">
         <is>
           <t>8101, 8105</t>
@@ -36979,7 +36209,6 @@
       <c r="F922" t="n">
         <v>2576.52</v>
       </c>
-      <c r="G922" t="inlineStr"/>
       <c r="H922" t="inlineStr">
         <is>
           <t>8100, 8104</t>
@@ -37018,7 +36247,6 @@
       <c r="F923" t="n">
         <v>3480.04</v>
       </c>
-      <c r="G923" t="inlineStr"/>
       <c r="H923" t="inlineStr">
         <is>
           <t>8102, 8108</t>
@@ -37057,7 +36285,6 @@
       <c r="F924" t="n">
         <v>2686.909999999999</v>
       </c>
-      <c r="G924" t="inlineStr"/>
       <c r="H924" t="inlineStr">
         <is>
           <t>8100, 8104</t>
@@ -37096,7 +36323,6 @@
       <c r="F925" t="n">
         <v>5523.61</v>
       </c>
-      <c r="G925" t="inlineStr"/>
       <c r="H925" t="inlineStr">
         <is>
           <t>8100, 8104</t>
@@ -37135,7 +36361,6 @@
       <c r="F926" t="n">
         <v>2213.589999999999</v>
       </c>
-      <c r="G926" t="inlineStr"/>
       <c r="H926" t="inlineStr">
         <is>
           <t>8102, 8104</t>
@@ -37174,7 +36399,6 @@
       <c r="F927" t="n">
         <v>3646.66</v>
       </c>
-      <c r="G927" t="inlineStr"/>
       <c r="H927" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37213,7 +36437,6 @@
       <c r="F928" t="n">
         <v>340.8900000000003</v>
       </c>
-      <c r="G928" t="inlineStr"/>
       <c r="H928" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37252,7 +36475,6 @@
       <c r="F929" t="n">
         <v>564.7399999999998</v>
       </c>
-      <c r="G929" t="inlineStr"/>
       <c r="H929" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37291,7 +36513,6 @@
       <c r="F930" t="n">
         <v>3854.58</v>
       </c>
-      <c r="G930" t="inlineStr"/>
       <c r="H930" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37330,7 +36551,6 @@
       <c r="F931" t="n">
         <v>3698.06</v>
       </c>
-      <c r="G931" t="inlineStr"/>
       <c r="H931" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37369,7 +36589,6 @@
       <c r="F932" t="n">
         <v>1905.67</v>
       </c>
-      <c r="G932" t="inlineStr"/>
       <c r="H932" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37408,7 +36627,6 @@
       <c r="F933" t="n">
         <v>4345.04</v>
       </c>
-      <c r="G933" t="inlineStr"/>
       <c r="H933" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37447,7 +36665,6 @@
       <c r="F934" t="n">
         <v>3554.96</v>
       </c>
-      <c r="G934" t="inlineStr"/>
       <c r="H934" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37486,7 +36703,6 @@
       <c r="F935" t="n">
         <v>4139.09</v>
       </c>
-      <c r="G935" t="inlineStr"/>
       <c r="H935" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37525,7 +36741,6 @@
       <c r="F936" t="n">
         <v>3024.58</v>
       </c>
-      <c r="G936" t="inlineStr"/>
       <c r="H936" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37564,7 +36779,6 @@
       <c r="F937" t="n">
         <v>1285.52</v>
       </c>
-      <c r="G937" t="inlineStr"/>
       <c r="H937" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37603,7 +36817,6 @@
       <c r="F938" t="n">
         <v>2544.49</v>
       </c>
-      <c r="G938" t="inlineStr"/>
       <c r="H938" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37642,7 +36855,6 @@
       <c r="F939" t="n">
         <v>3358.77</v>
       </c>
-      <c r="G939" t="inlineStr"/>
       <c r="H939" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37681,7 +36893,6 @@
       <c r="F940" t="n">
         <v>4222.23</v>
       </c>
-      <c r="G940" t="inlineStr"/>
       <c r="H940" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37720,7 +36931,6 @@
       <c r="F941" t="n">
         <v>3813.1</v>
       </c>
-      <c r="G941" t="inlineStr"/>
       <c r="H941" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37759,7 +36969,6 @@
       <c r="F942" t="n">
         <v>1690.87</v>
       </c>
-      <c r="G942" t="inlineStr"/>
       <c r="H942" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37798,7 +37007,6 @@
       <c r="F943" t="n">
         <v>5091.88</v>
       </c>
-      <c r="G943" t="inlineStr"/>
       <c r="H943" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37837,7 +37045,6 @@
       <c r="F944" t="n">
         <v>4342.54</v>
       </c>
-      <c r="G944" t="inlineStr"/>
       <c r="H944" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37876,7 +37083,6 @@
       <c r="F945" t="n">
         <v>364.8699999999999</v>
       </c>
-      <c r="G945" t="inlineStr"/>
       <c r="H945" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37915,7 +37121,6 @@
       <c r="F946" t="n">
         <v>4618.26</v>
       </c>
-      <c r="G946" t="inlineStr"/>
       <c r="H946" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37954,7 +37159,6 @@
       <c r="F947" t="n">
         <v>3243.53</v>
       </c>
-      <c r="G947" t="inlineStr"/>
       <c r="H947" t="inlineStr">
         <is>
           <t>1330</t>
@@ -37993,7 +37197,6 @@
       <c r="F948" t="n">
         <v>4199.54</v>
       </c>
-      <c r="G948" t="inlineStr"/>
       <c r="H948" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38032,7 +37235,6 @@
       <c r="F949" t="n">
         <v>5167.71</v>
       </c>
-      <c r="G949" t="inlineStr"/>
       <c r="H949" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38071,7 +37273,6 @@
       <c r="F950" t="n">
         <v>2162.1</v>
       </c>
-      <c r="G950" t="inlineStr"/>
       <c r="H950" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38110,7 +37311,6 @@
       <c r="F951" t="n">
         <v>4638.940000000001</v>
       </c>
-      <c r="G951" t="inlineStr"/>
       <c r="H951" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38149,7 +37349,6 @@
       <c r="F952" t="n">
         <v>3090.95</v>
       </c>
-      <c r="G952" t="inlineStr"/>
       <c r="H952" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38188,7 +37387,6 @@
       <c r="F953" t="n">
         <v>2492.44</v>
       </c>
-      <c r="G953" t="inlineStr"/>
       <c r="H953" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38227,7 +37425,6 @@
       <c r="F954" t="n">
         <v>5330.86</v>
       </c>
-      <c r="G954" t="inlineStr"/>
       <c r="H954" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38266,7 +37463,6 @@
       <c r="F955" t="n">
         <v>4395.87</v>
       </c>
-      <c r="G955" t="inlineStr"/>
       <c r="H955" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38305,7 +37501,6 @@
       <c r="F956" t="n">
         <v>4977.86</v>
       </c>
-      <c r="G956" t="inlineStr"/>
       <c r="H956" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38344,7 +37539,6 @@
       <c r="F957" t="n">
         <v>3718.36</v>
       </c>
-      <c r="G957" t="inlineStr"/>
       <c r="H957" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38383,7 +37577,6 @@
       <c r="F958" t="n">
         <v>5338.92</v>
       </c>
-      <c r="G958" t="inlineStr"/>
       <c r="H958" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38422,7 +37615,6 @@
       <c r="F959" t="n">
         <v>4476</v>
       </c>
-      <c r="G959" t="inlineStr"/>
       <c r="H959" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38461,7 +37653,6 @@
       <c r="F960" t="n">
         <v>3626.06</v>
       </c>
-      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38500,7 +37691,6 @@
       <c r="F961" t="n">
         <v>1239.13</v>
       </c>
-      <c r="G961" t="inlineStr"/>
       <c r="H961" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38539,7 +37729,6 @@
       <c r="F962" t="n">
         <v>745.1099999999997</v>
       </c>
-      <c r="G962" t="inlineStr"/>
       <c r="H962" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38578,7 +37767,6 @@
       <c r="F963" t="n">
         <v>5188.35</v>
       </c>
-      <c r="G963" t="inlineStr"/>
       <c r="H963" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38617,7 +37805,6 @@
       <c r="F964" t="n">
         <v>3487.5</v>
       </c>
-      <c r="G964" t="inlineStr"/>
       <c r="H964" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38656,7 +37843,6 @@
       <c r="F965" t="n">
         <v>2227.26</v>
       </c>
-      <c r="G965" t="inlineStr"/>
       <c r="H965" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38695,7 +37881,6 @@
       <c r="F966" t="n">
         <v>926.1199999999999</v>
       </c>
-      <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38734,7 +37919,6 @@
       <c r="F967" t="n">
         <v>2302.93</v>
       </c>
-      <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38773,7 +37957,6 @@
       <c r="F968" t="n">
         <v>4427.99</v>
       </c>
-      <c r="G968" t="inlineStr"/>
       <c r="H968" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38812,7 +37995,6 @@
       <c r="F969" t="n">
         <v>4793.22</v>
       </c>
-      <c r="G969" t="inlineStr"/>
       <c r="H969" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38851,7 +38033,6 @@
       <c r="F970" t="n">
         <v>4918.14</v>
       </c>
-      <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38890,7 +38071,6 @@
       <c r="F971" t="n">
         <v>364.54</v>
       </c>
-      <c r="G971" t="inlineStr"/>
       <c r="H971" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38929,7 +38109,6 @@
       <c r="F972" t="n">
         <v>5370.32</v>
       </c>
-      <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr">
         <is>
           <t>1330</t>
@@ -38968,7 +38147,6 @@
       <c r="F973" t="n">
         <v>4717.3</v>
       </c>
-      <c r="G973" t="inlineStr"/>
       <c r="H973" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39007,7 +38185,6 @@
       <c r="F974" t="n">
         <v>5285.74</v>
       </c>
-      <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39046,7 +38223,6 @@
       <c r="F975" t="n">
         <v>2518.06</v>
       </c>
-      <c r="G975" t="inlineStr"/>
       <c r="H975" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39085,7 +38261,6 @@
       <c r="F976" t="n">
         <v>4014.39</v>
       </c>
-      <c r="G976" t="inlineStr"/>
       <c r="H976" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39124,7 +38299,6 @@
       <c r="F977" t="n">
         <v>4897.85</v>
       </c>
-      <c r="G977" t="inlineStr"/>
       <c r="H977" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39163,7 +38337,6 @@
       <c r="F978" t="n">
         <v>5070.22</v>
       </c>
-      <c r="G978" t="inlineStr"/>
       <c r="H978" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39202,7 +38375,6 @@
       <c r="F979" t="n">
         <v>3101.59</v>
       </c>
-      <c r="G979" t="inlineStr"/>
       <c r="H979" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39241,7 +38413,6 @@
       <c r="F980" t="n">
         <v>3371.3</v>
       </c>
-      <c r="G980" t="inlineStr"/>
       <c r="H980" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39280,7 +38451,6 @@
       <c r="F981" t="n">
         <v>1530.48</v>
       </c>
-      <c r="G981" t="inlineStr"/>
       <c r="H981" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39319,7 +38489,6 @@
       <c r="F982" t="n">
         <v>3981.35</v>
       </c>
-      <c r="G982" t="inlineStr"/>
       <c r="H982" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39358,7 +38527,6 @@
       <c r="F983" t="n">
         <v>2993.27</v>
       </c>
-      <c r="G983" t="inlineStr"/>
       <c r="H983" t="inlineStr">
         <is>
           <t>1330</t>
@@ -39397,7 +38565,6 @@
       <c r="F984" t="n">
         <v>5289.32</v>
       </c>
-      <c r="G984" t="inlineStr"/>
       <c r="H984" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39436,7 +38603,6 @@
       <c r="F985" t="n">
         <v>4238.1</v>
       </c>
-      <c r="G985" t="inlineStr"/>
       <c r="H985" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39475,7 +38641,6 @@
       <c r="F986" t="n">
         <v>4314.65</v>
       </c>
-      <c r="G986" t="inlineStr"/>
       <c r="H986" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39514,7 +38679,6 @@
       <c r="F987" t="n">
         <v>5238.190000000001</v>
       </c>
-      <c r="G987" t="inlineStr"/>
       <c r="H987" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39553,7 +38717,6 @@
       <c r="F988" t="n">
         <v>5166.79</v>
       </c>
-      <c r="G988" t="inlineStr"/>
       <c r="H988" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39592,7 +38755,6 @@
       <c r="F989" t="n">
         <v>4902.39</v>
       </c>
-      <c r="G989" t="inlineStr"/>
       <c r="H989" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39631,7 +38793,6 @@
       <c r="F990" t="n">
         <v>5392.1</v>
       </c>
-      <c r="G990" t="inlineStr"/>
       <c r="H990" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39670,7 +38831,6 @@
       <c r="F991" t="n">
         <v>5158.67</v>
       </c>
-      <c r="G991" t="inlineStr"/>
       <c r="H991" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39709,7 +38869,6 @@
       <c r="F992" t="n">
         <v>5421.7</v>
       </c>
-      <c r="G992" t="inlineStr"/>
       <c r="H992" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39791,7 +38950,6 @@
       <c r="F994" t="n">
         <v>4615.1</v>
       </c>
-      <c r="G994" t="inlineStr"/>
       <c r="H994" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39830,7 +38988,6 @@
       <c r="F995" t="n">
         <v>4882.52</v>
       </c>
-      <c r="G995" t="inlineStr"/>
       <c r="H995" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39869,7 +39026,6 @@
       <c r="F996" t="n">
         <v>5109.84</v>
       </c>
-      <c r="G996" t="inlineStr"/>
       <c r="H996" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39908,7 +39064,6 @@
       <c r="F997" t="n">
         <v>5415.47</v>
       </c>
-      <c r="G997" t="inlineStr"/>
       <c r="H997" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39947,7 +39102,6 @@
       <c r="F998" t="n">
         <v>5236.67</v>
       </c>
-      <c r="G998" t="inlineStr"/>
       <c r="H998" t="inlineStr">
         <is>
           <t>6526</t>
@@ -39986,7 +39140,6 @@
       <c r="F999" t="n">
         <v>4644.21</v>
       </c>
-      <c r="G999" t="inlineStr"/>
       <c r="H999" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40025,7 +39178,6 @@
       <c r="F1000" t="n">
         <v>5589.93</v>
       </c>
-      <c r="G1000" t="inlineStr"/>
       <c r="H1000" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40064,7 +39216,6 @@
       <c r="F1001" t="n">
         <v>5360.22</v>
       </c>
-      <c r="G1001" t="inlineStr"/>
       <c r="H1001" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40103,7 +39254,6 @@
       <c r="F1002" t="n">
         <v>4295.63</v>
       </c>
-      <c r="G1002" t="inlineStr"/>
       <c r="H1002" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40142,7 +39292,6 @@
       <c r="F1003" t="n">
         <v>5461.45</v>
       </c>
-      <c r="G1003" t="inlineStr"/>
       <c r="H1003" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40181,7 +39330,6 @@
       <c r="F1004" t="n">
         <v>5073.84</v>
       </c>
-      <c r="G1004" t="inlineStr"/>
       <c r="H1004" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40220,7 +39368,6 @@
       <c r="F1005" t="n">
         <v>5409.36</v>
       </c>
-      <c r="G1005" t="inlineStr"/>
       <c r="H1005" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40259,7 +39406,6 @@
       <c r="F1006" t="n">
         <v>5638.47</v>
       </c>
-      <c r="G1006" t="inlineStr"/>
       <c r="H1006" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40298,7 +39444,6 @@
       <c r="F1007" t="n">
         <v>4923.55</v>
       </c>
-      <c r="G1007" t="inlineStr"/>
       <c r="H1007" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40337,7 +39482,6 @@
       <c r="F1008" t="n">
         <v>5499.32</v>
       </c>
-      <c r="G1008" t="inlineStr"/>
       <c r="H1008" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40376,7 +39520,6 @@
       <c r="F1009" t="n">
         <v>5082.18</v>
       </c>
-      <c r="G1009" t="inlineStr"/>
       <c r="H1009" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40415,7 +39558,6 @@
       <c r="F1010" t="n">
         <v>4879.25</v>
       </c>
-      <c r="G1010" t="inlineStr"/>
       <c r="H1010" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40454,7 +39596,6 @@
       <c r="F1011" t="n">
         <v>5684.43</v>
       </c>
-      <c r="G1011" t="inlineStr"/>
       <c r="H1011" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40493,7 +39634,6 @@
       <c r="F1012" t="n">
         <v>5469.85</v>
       </c>
-      <c r="G1012" t="inlineStr"/>
       <c r="H1012" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40532,7 +39672,6 @@
       <c r="F1013" t="n">
         <v>5560.68</v>
       </c>
-      <c r="G1013" t="inlineStr"/>
       <c r="H1013" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40571,7 +39710,6 @@
       <c r="F1014" t="n">
         <v>5281.89</v>
       </c>
-      <c r="G1014" t="inlineStr"/>
       <c r="H1014" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40610,7 +39748,6 @@
       <c r="F1015" t="n">
         <v>5660.57</v>
       </c>
-      <c r="G1015" t="inlineStr"/>
       <c r="H1015" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40649,7 +39786,6 @@
       <c r="F1016" t="n">
         <v>5448.64</v>
       </c>
-      <c r="G1016" t="inlineStr"/>
       <c r="H1016" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40688,7 +39824,6 @@
       <c r="F1017" t="n">
         <v>5300.97</v>
       </c>
-      <c r="G1017" t="inlineStr"/>
       <c r="H1017" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40727,7 +39862,6 @@
       <c r="F1018" t="n">
         <v>4779.02</v>
       </c>
-      <c r="G1018" t="inlineStr"/>
       <c r="H1018" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40766,7 +39900,6 @@
       <c r="F1019" t="n">
         <v>4549.66</v>
       </c>
-      <c r="G1019" t="inlineStr"/>
       <c r="H1019" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40805,7 +39938,6 @@
       <c r="F1020" t="n">
         <v>5661.1</v>
       </c>
-      <c r="G1020" t="inlineStr"/>
       <c r="H1020" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40844,7 +39976,6 @@
       <c r="F1021" t="n">
         <v>5162.66</v>
       </c>
-      <c r="G1021" t="inlineStr"/>
       <c r="H1021" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40883,7 +40014,6 @@
       <c r="F1022" t="n">
         <v>4808.22</v>
       </c>
-      <c r="G1022" t="inlineStr"/>
       <c r="H1022" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40922,7 +40052,6 @@
       <c r="F1023" t="n">
         <v>4411.54</v>
       </c>
-      <c r="G1023" t="inlineStr"/>
       <c r="H1023" t="inlineStr">
         <is>
           <t>6526</t>
@@ -40961,7 +40090,6 @@
       <c r="F1024" t="n">
         <v>4933.37</v>
       </c>
-      <c r="G1024" t="inlineStr"/>
       <c r="H1024" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41000,7 +40128,6 @@
       <c r="F1025" t="n">
         <v>5471.13</v>
       </c>
-      <c r="G1025" t="inlineStr"/>
       <c r="H1025" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41039,7 +40166,6 @@
       <c r="F1026" t="n">
         <v>5504.95</v>
       </c>
-      <c r="G1026" t="inlineStr"/>
       <c r="H1026" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41164,7 +40290,6 @@
       <c r="F1029" t="n">
         <v>5658</v>
       </c>
-      <c r="G1029" t="inlineStr"/>
       <c r="H1029" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41203,7 +40328,6 @@
       <c r="F1030" t="n">
         <v>5500.92</v>
       </c>
-      <c r="G1030" t="inlineStr"/>
       <c r="H1030" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41242,7 +40366,6 @@
       <c r="F1031" t="n">
         <v>5645.13</v>
       </c>
-      <c r="G1031" t="inlineStr"/>
       <c r="H1031" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41281,7 +40404,6 @@
       <c r="F1032" t="n">
         <v>4951.55</v>
       </c>
-      <c r="G1032" t="inlineStr"/>
       <c r="H1032" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41320,7 +40442,6 @@
       <c r="F1033" t="n">
         <v>5376.41</v>
       </c>
-      <c r="G1033" t="inlineStr"/>
       <c r="H1033" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41359,7 +40480,6 @@
       <c r="F1034" t="n">
         <v>5534.72</v>
       </c>
-      <c r="G1034" t="inlineStr"/>
       <c r="H1034" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41441,7 +40561,6 @@
       <c r="F1036" t="n">
         <v>5214.61</v>
       </c>
-      <c r="G1036" t="inlineStr"/>
       <c r="H1036" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41523,7 +40642,6 @@
       <c r="F1038" t="n">
         <v>4961.34</v>
       </c>
-      <c r="G1038" t="inlineStr"/>
       <c r="H1038" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41562,7 +40680,6 @@
       <c r="F1039" t="n">
         <v>5275.25</v>
       </c>
-      <c r="G1039" t="inlineStr"/>
       <c r="H1039" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41601,7 +40718,6 @@
       <c r="F1040" t="n">
         <v>5237.66</v>
       </c>
-      <c r="G1040" t="inlineStr"/>
       <c r="H1040" t="inlineStr">
         <is>
           <t>6526</t>
@@ -41640,7 +40756,6 @@
       <c r="F1041" t="n">
         <v>5639.14</v>
       </c>
-      <c r="G1041" t="inlineStr"/>
       <c r="H1041" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41679,7 +40794,6 @@
       <c r="F1042" t="n">
         <v>5325.34</v>
       </c>
-      <c r="G1042" t="inlineStr"/>
       <c r="H1042" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41718,7 +40832,6 @@
       <c r="F1043" t="n">
         <v>5348.2</v>
       </c>
-      <c r="G1043" t="inlineStr"/>
       <c r="H1043" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41757,7 +40870,6 @@
       <c r="F1044" t="n">
         <v>5623.88</v>
       </c>
-      <c r="G1044" t="inlineStr"/>
       <c r="H1044" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41796,7 +40908,6 @@
       <c r="F1045" t="n">
         <v>5610.72</v>
       </c>
-      <c r="G1045" t="inlineStr"/>
       <c r="H1045" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41835,7 +40946,6 @@
       <c r="F1046" t="n">
         <v>5523.64</v>
       </c>
-      <c r="G1046" t="inlineStr"/>
       <c r="H1046" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41874,7 +40984,6 @@
       <c r="F1047" t="n">
         <v>5669.82</v>
       </c>
-      <c r="G1047" t="inlineStr"/>
       <c r="H1047" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41913,7 +41022,6 @@
       <c r="F1048" t="n">
         <v>5600.14</v>
       </c>
-      <c r="G1048" t="inlineStr"/>
       <c r="H1048" t="inlineStr">
         <is>
           <t>6527</t>
@@ -41952,7 +41060,6 @@
       <c r="F1049" t="n">
         <v>5678.66</v>
       </c>
-      <c r="G1049" t="inlineStr"/>
       <c r="H1049" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42034,7 +41141,6 @@
       <c r="F1051" t="n">
         <v>5437.89</v>
       </c>
-      <c r="G1051" t="inlineStr"/>
       <c r="H1051" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42073,7 +41179,6 @@
       <c r="F1052" t="n">
         <v>5517.71</v>
       </c>
-      <c r="G1052" t="inlineStr"/>
       <c r="H1052" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42112,7 +41217,6 @@
       <c r="F1053" t="n">
         <v>5585.57</v>
       </c>
-      <c r="G1053" t="inlineStr"/>
       <c r="H1053" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42151,7 +41255,6 @@
       <c r="F1054" t="n">
         <v>5676.8</v>
       </c>
-      <c r="G1054" t="inlineStr"/>
       <c r="H1054" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42190,7 +41293,6 @@
       <c r="F1055" t="n">
         <v>5623.42</v>
       </c>
-      <c r="G1055" t="inlineStr"/>
       <c r="H1055" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42229,7 +41331,6 @@
       <c r="F1056" t="n">
         <v>5446.57</v>
       </c>
-      <c r="G1056" t="inlineStr"/>
       <c r="H1056" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42268,7 +41369,6 @@
       <c r="F1057" t="n">
         <v>5728.87</v>
       </c>
-      <c r="G1057" t="inlineStr"/>
       <c r="H1057" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42307,7 +41407,6 @@
       <c r="F1058" t="n">
         <v>5668.44</v>
       </c>
-      <c r="G1058" t="inlineStr"/>
       <c r="H1058" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42346,7 +41445,6 @@
       <c r="F1059" t="n">
         <v>5342.51</v>
       </c>
-      <c r="G1059" t="inlineStr"/>
       <c r="H1059" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42385,7 +41483,6 @@
       <c r="F1060" t="n">
         <v>5690.52</v>
       </c>
-      <c r="G1060" t="inlineStr"/>
       <c r="H1060" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42424,7 +41521,6 @@
       <c r="F1061" t="n">
         <v>5574.82</v>
       </c>
-      <c r="G1061" t="inlineStr"/>
       <c r="H1061" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42463,7 +41559,6 @@
       <c r="F1062" t="n">
         <v>5674.97</v>
       </c>
-      <c r="G1062" t="inlineStr"/>
       <c r="H1062" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42502,7 +41597,6 @@
       <c r="F1063" t="n">
         <v>5743.37</v>
       </c>
-      <c r="G1063" t="inlineStr"/>
       <c r="H1063" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42541,7 +41635,6 @@
       <c r="F1064" t="n">
         <v>5529.95</v>
       </c>
-      <c r="G1064" t="inlineStr"/>
       <c r="H1064" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42580,7 +41673,6 @@
       <c r="F1065" t="n">
         <v>5701.83</v>
       </c>
-      <c r="G1065" t="inlineStr"/>
       <c r="H1065" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42619,7 +41711,6 @@
       <c r="F1066" t="n">
         <v>5577.31</v>
       </c>
-      <c r="G1066" t="inlineStr"/>
       <c r="H1066" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42658,7 +41749,6 @@
       <c r="F1067" t="n">
         <v>5516.73</v>
       </c>
-      <c r="G1067" t="inlineStr"/>
       <c r="H1067" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42697,7 +41787,6 @@
       <c r="F1068" t="n">
         <v>5757.08</v>
       </c>
-      <c r="G1068" t="inlineStr"/>
       <c r="H1068" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42736,7 +41825,6 @@
       <c r="F1069" t="n">
         <v>5693.03</v>
       </c>
-      <c r="G1069" t="inlineStr"/>
       <c r="H1069" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42775,7 +41863,6 @@
       <c r="F1070" t="n">
         <v>5720.15</v>
       </c>
-      <c r="G1070" t="inlineStr"/>
       <c r="H1070" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42814,7 +41901,6 @@
       <c r="F1071" t="n">
         <v>5636.92</v>
       </c>
-      <c r="G1071" t="inlineStr"/>
       <c r="H1071" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42853,7 +41939,6 @@
       <c r="F1072" t="n">
         <v>5749.96</v>
       </c>
-      <c r="G1072" t="inlineStr"/>
       <c r="H1072" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42892,7 +41977,6 @@
       <c r="F1073" t="n">
         <v>5686.7</v>
       </c>
-      <c r="G1073" t="inlineStr"/>
       <c r="H1073" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42931,7 +42015,6 @@
       <c r="F1074" t="n">
         <v>5642.62</v>
       </c>
-      <c r="G1074" t="inlineStr"/>
       <c r="H1074" t="inlineStr">
         <is>
           <t>6527</t>
@@ -42970,7 +42053,6 @@
       <c r="F1075" t="n">
         <v>5486.81</v>
       </c>
-      <c r="G1075" t="inlineStr"/>
       <c r="H1075" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43009,7 +42091,6 @@
       <c r="F1076" t="n">
         <v>5418.35</v>
       </c>
-      <c r="G1076" t="inlineStr"/>
       <c r="H1076" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43048,7 +42129,6 @@
       <c r="F1077" t="n">
         <v>5750.12</v>
       </c>
-      <c r="G1077" t="inlineStr"/>
       <c r="H1077" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43087,7 +42167,6 @@
       <c r="F1078" t="n">
         <v>5601.33</v>
       </c>
-      <c r="G1078" t="inlineStr"/>
       <c r="H1078" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43126,7 +42205,6 @@
       <c r="F1079" t="n">
         <v>5495.54</v>
       </c>
-      <c r="G1079" t="inlineStr"/>
       <c r="H1079" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43165,7 +42243,6 @@
       <c r="F1080" t="n">
         <v>5377.11</v>
       </c>
-      <c r="G1080" t="inlineStr"/>
       <c r="H1080" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43204,7 +42281,6 @@
       <c r="F1081" t="n">
         <v>5532.89</v>
       </c>
-      <c r="G1081" t="inlineStr"/>
       <c r="H1081" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43243,7 +42319,6 @@
       <c r="F1082" t="n">
         <v>5693.4</v>
       </c>
-      <c r="G1082" t="inlineStr"/>
       <c r="H1082" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43282,7 +42357,6 @@
       <c r="F1083" t="n">
         <v>5703.51</v>
       </c>
-      <c r="G1083" t="inlineStr"/>
       <c r="H1083" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43364,7 +42438,6 @@
       <c r="F1085" t="n">
         <v>5378.59</v>
       </c>
-      <c r="G1085" t="inlineStr"/>
       <c r="H1085" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43403,7 +42476,6 @@
       <c r="F1086" t="n">
         <v>5749.19</v>
       </c>
-      <c r="G1086" t="inlineStr"/>
       <c r="H1086" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43442,7 +42514,6 @@
       <c r="F1087" t="n">
         <v>5702.31</v>
       </c>
-      <c r="G1087" t="inlineStr"/>
       <c r="H1087" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43481,7 +42552,6 @@
       <c r="F1088" t="n">
         <v>5745.35</v>
       </c>
-      <c r="G1088" t="inlineStr"/>
       <c r="H1088" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43520,7 +42590,6 @@
       <c r="F1089" t="n">
         <v>5538.32</v>
       </c>
-      <c r="G1089" t="inlineStr"/>
       <c r="H1089" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43559,7 +42628,6 @@
       <c r="F1090" t="n">
         <v>5665.14</v>
       </c>
-      <c r="G1090" t="inlineStr"/>
       <c r="H1090" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43598,7 +42666,6 @@
       <c r="F1091" t="n">
         <v>5712.39</v>
       </c>
-      <c r="G1091" t="inlineStr"/>
       <c r="H1091" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43680,7 +42747,6 @@
       <c r="F1093" t="n">
         <v>5616.84</v>
       </c>
-      <c r="G1093" t="inlineStr"/>
       <c r="H1093" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43719,7 +42785,6 @@
       <c r="F1094" t="n">
         <v>5618.88</v>
       </c>
-      <c r="G1094" t="inlineStr"/>
       <c r="H1094" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43758,7 +42823,6 @@
       <c r="F1095" t="n">
         <v>5541.25</v>
       </c>
-      <c r="G1095" t="inlineStr"/>
       <c r="H1095" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43797,7 +42861,6 @@
       <c r="F1096" t="n">
         <v>5634.94</v>
       </c>
-      <c r="G1096" t="inlineStr"/>
       <c r="H1096" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43836,7 +42899,6 @@
       <c r="F1097" t="n">
         <v>5623.72</v>
       </c>
-      <c r="G1097" t="inlineStr"/>
       <c r="H1097" t="inlineStr">
         <is>
           <t>6527</t>
@@ -43875,7 +42937,6 @@
       <c r="F1098" t="n">
         <v>4894.51</v>
       </c>
-      <c r="G1098" t="inlineStr"/>
       <c r="H1098" t="inlineStr">
         <is>
           <t>6407</t>
@@ -43914,7 +42975,6 @@
       <c r="F1099" t="n">
         <v>2993.47</v>
       </c>
-      <c r="G1099" t="inlineStr"/>
       <c r="H1099" t="inlineStr">
         <is>
           <t>6407</t>
@@ -43953,7 +43013,6 @@
       <c r="F1100" t="n">
         <v>3484.46</v>
       </c>
-      <c r="G1100" t="inlineStr"/>
       <c r="H1100" t="inlineStr">
         <is>
           <t>6404</t>
@@ -43992,7 +43051,6 @@
       <c r="F1101" t="n">
         <v>4987.49</v>
       </c>
-      <c r="G1101" t="inlineStr"/>
       <c r="H1101" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44031,7 +43089,6 @@
       <c r="F1102" t="n">
         <v>4849.03</v>
       </c>
-      <c r="G1102" t="inlineStr"/>
       <c r="H1102" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44113,7 +43170,6 @@
       <c r="F1104" t="n">
         <v>5085.940000000001</v>
       </c>
-      <c r="G1104" t="inlineStr"/>
       <c r="H1104" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44152,7 +43208,6 @@
       <c r="F1105" t="n">
         <v>4748.35</v>
       </c>
-      <c r="G1105" t="inlineStr"/>
       <c r="H1105" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44320,7 +43375,6 @@
       <c r="F1109" t="n">
         <v>4580.68</v>
       </c>
-      <c r="G1109" t="inlineStr"/>
       <c r="H1109" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44359,7 +43413,6 @@
       <c r="F1110" t="n">
         <v>4883.77</v>
       </c>
-      <c r="G1110" t="inlineStr"/>
       <c r="H1110" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44441,7 +43494,6 @@
       <c r="F1112" t="n">
         <v>5052.9</v>
       </c>
-      <c r="G1112" t="inlineStr"/>
       <c r="H1112" t="inlineStr">
         <is>
           <t>6404</t>
@@ -44523,7 +43575,6 @@
       <c r="F1114" t="n">
         <v>5453.42</v>
       </c>
-      <c r="G1114" t="inlineStr"/>
       <c r="H1114" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44648,7 +43699,6 @@
       <c r="F1117" t="n">
         <v>5352.59</v>
       </c>
-      <c r="G1117" t="inlineStr"/>
       <c r="H1117" t="inlineStr">
         <is>
           <t>6407</t>
@@ -44687,7 +43737,6 @@
       <c r="F1118" t="n">
         <v>10514.45</v>
       </c>
-      <c r="G1118" t="inlineStr"/>
       <c r="H1118" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45070,7 +44119,6 @@
       <c r="F1127" t="n">
         <v>11216.66</v>
       </c>
-      <c r="G1127" t="inlineStr"/>
       <c r="H1127" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45152,7 +44200,6 @@
       <c r="F1129" t="n">
         <v>11387.48</v>
       </c>
-      <c r="G1129" t="inlineStr"/>
       <c r="H1129" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45191,7 +44238,6 @@
       <c r="F1130" t="n">
         <v>11042.93</v>
       </c>
-      <c r="G1130" t="inlineStr"/>
       <c r="H1130" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45230,7 +44276,6 @@
       <c r="F1131" t="n">
         <v>10723.63</v>
       </c>
-      <c r="G1131" t="inlineStr"/>
       <c r="H1131" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45355,7 +44400,6 @@
       <c r="F1134" t="n">
         <v>11270.12</v>
       </c>
-      <c r="G1134" t="inlineStr"/>
       <c r="H1134" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45394,7 +44438,6 @@
       <c r="F1135" t="n">
         <v>10720.43</v>
       </c>
-      <c r="G1135" t="inlineStr"/>
       <c r="H1135" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45476,7 +44519,6 @@
       <c r="F1137" t="n">
         <v>9367.470000000001</v>
       </c>
-      <c r="G1137" t="inlineStr"/>
       <c r="H1137" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45558,7 +44600,6 @@
       <c r="F1139" t="n">
         <v>10883.39</v>
       </c>
-      <c r="G1139" t="inlineStr"/>
       <c r="H1139" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45597,7 +44638,6 @@
       <c r="F1140" t="n">
         <v>11198.59</v>
       </c>
-      <c r="G1140" t="inlineStr"/>
       <c r="H1140" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45722,7 +44762,6 @@
       <c r="F1143" t="n">
         <v>11368.51</v>
       </c>
-      <c r="G1143" t="inlineStr"/>
       <c r="H1143" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45761,7 +44800,6 @@
       <c r="F1144" t="n">
         <v>11124.6</v>
       </c>
-      <c r="G1144" t="inlineStr"/>
       <c r="H1144" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45800,7 +44838,6 @@
       <c r="F1145" t="n">
         <v>11363.64</v>
       </c>
-      <c r="G1145" t="inlineStr"/>
       <c r="H1145" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -45925,7 +44962,6 @@
       <c r="F1148" t="n">
         <v>11093.79</v>
       </c>
-      <c r="G1148" t="inlineStr"/>
       <c r="H1148" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -46050,7 +45086,6 @@
       <c r="F1151" t="n">
         <v>10499.3</v>
       </c>
-      <c r="G1151" t="inlineStr"/>
       <c r="H1151" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -46132,7 +45167,6 @@
       <c r="F1153" t="n">
         <v>10839.98</v>
       </c>
-      <c r="G1153" t="inlineStr"/>
       <c r="H1153" t="inlineStr">
         <is>
           <t>6404, 6407</t>
@@ -46171,7 +45205,6 @@
       <c r="F1154" t="n">
         <v>14660.84</v>
       </c>
-      <c r="G1154" t="inlineStr"/>
       <c r="H1154" t="inlineStr">
         <is>
           <t>6404, 6407, RECL</t>
@@ -46210,7 +45243,6 @@
       <c r="F1155" t="n">
         <v>11309.27</v>
       </c>
-      <c r="G1155" t="inlineStr"/>
       <c r="H1155" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46249,7 +45281,6 @@
       <c r="F1156" t="n">
         <v>10741.81</v>
       </c>
-      <c r="G1156" t="inlineStr"/>
       <c r="H1156" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46288,7 +45319,6 @@
       <c r="F1157" t="n">
         <v>10888.36</v>
       </c>
-      <c r="G1157" t="inlineStr"/>
       <c r="H1157" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46327,7 +45357,6 @@
       <c r="F1158" t="n">
         <v>11337.05</v>
       </c>
-      <c r="G1158" t="inlineStr"/>
       <c r="H1158" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46366,7 +45395,6 @@
       <c r="F1159" t="n">
         <v>11310.27</v>
       </c>
-      <c r="G1159" t="inlineStr"/>
       <c r="H1159" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46448,7 +45476,6 @@
       <c r="F1161" t="n">
         <v>11366.44</v>
       </c>
-      <c r="G1161" t="inlineStr"/>
       <c r="H1161" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46487,7 +45514,6 @@
       <c r="F1162" t="n">
         <v>11265.65</v>
       </c>
-      <c r="G1162" t="inlineStr"/>
       <c r="H1162" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46698,7 +45724,6 @@
       <c r="F1167" t="n">
         <v>11306.08</v>
       </c>
-      <c r="G1167" t="inlineStr"/>
       <c r="H1167" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46780,7 +45805,6 @@
       <c r="F1169" t="n">
         <v>5568.56</v>
       </c>
-      <c r="G1169" t="inlineStr"/>
       <c r="H1169" t="inlineStr">
         <is>
           <t>6405</t>
@@ -46819,7 +45843,6 @@
       <c r="F1170" t="n">
         <v>5332.76</v>
       </c>
-      <c r="G1170" t="inlineStr"/>
       <c r="H1170" t="inlineStr">
         <is>
           <t>6405</t>
@@ -46858,7 +45881,6 @@
       <c r="F1171" t="n">
         <v>11476.13</v>
       </c>
-      <c r="G1171" t="inlineStr"/>
       <c r="H1171" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -46983,7 +46005,6 @@
       <c r="F1174" t="n">
         <v>11446.02</v>
       </c>
-      <c r="G1174" t="inlineStr"/>
       <c r="H1174" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47022,7 +46043,6 @@
       <c r="F1175" t="n">
         <v>11259.12</v>
       </c>
-      <c r="G1175" t="inlineStr"/>
       <c r="H1175" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47405,7 +46425,6 @@
       <c r="F1184" t="n">
         <v>11468.73</v>
       </c>
-      <c r="G1184" t="inlineStr"/>
       <c r="H1184" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47487,7 +46506,6 @@
       <c r="F1186" t="n">
         <v>11519.73</v>
       </c>
-      <c r="G1186" t="inlineStr"/>
       <c r="H1186" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47526,7 +46544,6 @@
       <c r="F1187" t="n">
         <v>11416.88</v>
       </c>
-      <c r="G1187" t="inlineStr"/>
       <c r="H1187" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47565,7 +46582,6 @@
       <c r="F1188" t="n">
         <v>11321.55</v>
       </c>
-      <c r="G1188" t="inlineStr"/>
       <c r="H1188" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47690,7 +46706,6 @@
       <c r="F1191" t="n">
         <v>11484.69</v>
       </c>
-      <c r="G1191" t="inlineStr"/>
       <c r="H1191" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47729,7 +46744,6 @@
       <c r="F1192" t="n">
         <v>11320.61</v>
       </c>
-      <c r="G1192" t="inlineStr"/>
       <c r="H1192" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47811,7 +46825,6 @@
       <c r="F1194" t="n">
         <v>10916.75</v>
       </c>
-      <c r="G1194" t="inlineStr"/>
       <c r="H1194" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47893,7 +46906,6 @@
       <c r="F1196" t="n">
         <v>11369.26</v>
       </c>
-      <c r="G1196" t="inlineStr"/>
       <c r="H1196" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -47932,7 +46944,6 @@
       <c r="F1197" t="n">
         <v>5675.34</v>
       </c>
-      <c r="G1197" t="inlineStr"/>
       <c r="H1197" t="inlineStr">
         <is>
           <t>6405</t>
@@ -48057,7 +47068,6 @@
       <c r="F1200" t="n">
         <v>11514.06</v>
       </c>
-      <c r="G1200" t="inlineStr"/>
       <c r="H1200" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48096,7 +47106,6 @@
       <c r="F1201" t="n">
         <v>11441.26</v>
       </c>
-      <c r="G1201" t="inlineStr"/>
       <c r="H1201" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48135,7 +47144,6 @@
       <c r="F1202" t="n">
         <v>11512.61</v>
       </c>
-      <c r="G1202" t="inlineStr"/>
       <c r="H1202" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48260,7 +47268,6 @@
       <c r="F1205" t="n">
         <v>11432.05</v>
       </c>
-      <c r="G1205" t="inlineStr"/>
       <c r="H1205" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48385,7 +47392,6 @@
       <c r="F1208" t="n">
         <v>11254.59</v>
       </c>
-      <c r="G1208" t="inlineStr"/>
       <c r="H1208" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48467,7 +47473,6 @@
       <c r="F1210" t="n">
         <v>11356.3</v>
       </c>
-      <c r="G1210" t="inlineStr"/>
       <c r="H1210" t="inlineStr">
         <is>
           <t>6405, 6408</t>
@@ -48506,7 +47511,6 @@
       <c r="F1211" t="n">
         <v>16557.09</v>
       </c>
-      <c r="G1211" t="inlineStr"/>
       <c r="H1211" t="inlineStr">
         <is>
           <t>6405, 6408, RECL</t>
@@ -48545,7 +47549,6 @@
       <c r="F1212" t="n">
         <v>12062.11</v>
       </c>
-      <c r="G1212" t="inlineStr"/>
       <c r="H1212" t="inlineStr">
         <is>
           <t>1335</t>
@@ -48584,7 +47587,6 @@
       <c r="F1213" t="n">
         <v>5777.76</v>
       </c>
-      <c r="G1213" t="inlineStr"/>
       <c r="H1213" t="inlineStr">
         <is>
           <t>1332</t>
@@ -48623,7 +47625,6 @@
       <c r="F1214" t="n">
         <v>32269.23</v>
       </c>
-      <c r="G1214" t="inlineStr"/>
       <c r="H1214" t="inlineStr">
         <is>
           <t>1335</t>
@@ -48662,7 +47663,6 @@
       <c r="F1215" t="n">
         <v>23428.29</v>
       </c>
-      <c r="G1215" t="inlineStr"/>
       <c r="H1215" t="inlineStr">
         <is>
           <t>1335</t>
@@ -48701,7 +47701,6 @@
       <c r="F1216" t="n">
         <v>5584.02</v>
       </c>
-      <c r="G1216" t="inlineStr"/>
       <c r="H1216" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -49127,8 +48126,6 @@
       <c r="F1226" t="n">
         <v>0</v>
       </c>
-      <c r="G1226" t="inlineStr"/>
-      <c r="H1226" t="inlineStr"/>
       <c r="I1226" t="n">
         <v>0</v>
       </c>
@@ -51183,7 +50180,6 @@
       <c r="F1274" t="n">
         <v>5175.99</v>
       </c>
-      <c r="G1274" t="inlineStr"/>
       <c r="H1274" t="inlineStr">
         <is>
           <t>CT_B</t>
@@ -51222,8 +50218,6 @@
       <c r="F1275" t="n">
         <v>0</v>
       </c>
-      <c r="G1275" t="inlineStr"/>
-      <c r="H1275" t="inlineStr"/>
       <c r="I1275" t="n">
         <v>1078.27</v>
       </c>
@@ -51262,7 +50256,6 @@
           <t>0809</t>
         </is>
       </c>
-      <c r="H1276" t="inlineStr"/>
       <c r="I1276" t="n">
         <v>-2474.12</v>
       </c>
@@ -51301,7 +50294,6 @@
           <t>0809</t>
         </is>
       </c>
-      <c r="H1277" t="inlineStr"/>
       <c r="I1277" t="n">
         <v>-7224.19</v>
       </c>
@@ -51340,7 +50332,6 @@
           <t>0809</t>
         </is>
       </c>
-      <c r="H1278" t="inlineStr"/>
       <c r="I1278" t="n">
         <v>-2010.99</v>
       </c>
@@ -51374,7 +50365,6 @@
       <c r="F1279" t="n">
         <v>44413.78999999999</v>
       </c>
-      <c r="G1279" t="inlineStr"/>
       <c r="H1279" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -51585,7 +50575,6 @@
       <c r="F1284" t="n">
         <v>10692.34</v>
       </c>
-      <c r="G1284" t="inlineStr"/>
       <c r="H1284" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -51796,7 +50785,6 @@
       <c r="F1289" t="n">
         <v>89655.63</v>
       </c>
-      <c r="G1289" t="inlineStr"/>
       <c r="H1289" t="inlineStr">
         <is>
           <t>CONV</t>
@@ -52781,7 +51769,6 @@
       <c r="F1312" t="n">
         <v>11305.99</v>
       </c>
-      <c r="G1312" t="inlineStr"/>
       <c r="H1312" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -53035,7 +52022,6 @@
       <c r="F1318" t="n">
         <v>11011.44</v>
       </c>
-      <c r="G1318" t="inlineStr"/>
       <c r="H1318" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -53203,7 +52189,6 @@
       <c r="F1322" t="n">
         <v>10741.43</v>
       </c>
-      <c r="G1322" t="inlineStr"/>
       <c r="H1322" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -53844,7 +52829,6 @@
       <c r="F1337" t="n">
         <v>7967.74</v>
       </c>
-      <c r="G1337" t="inlineStr"/>
       <c r="H1337" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -53883,7 +52867,6 @@
       <c r="F1338" t="n">
         <v>4065.77</v>
       </c>
-      <c r="G1338" t="inlineStr"/>
       <c r="H1338" t="inlineStr">
         <is>
           <t>ASSI</t>
@@ -54309,7 +53292,6 @@
       <c r="F1348" t="n">
         <v>14545.35</v>
       </c>
-      <c r="G1348" t="inlineStr"/>
       <c r="H1348" t="inlineStr">
         <is>
           <t>PLAN</t>
@@ -56369,7 +55351,6 @@
       <c r="F1396" t="n">
         <v>5234.77</v>
       </c>
-      <c r="G1396" t="inlineStr"/>
       <c r="H1396" t="inlineStr">
         <is>
           <t>PLAN</t>
@@ -56537,7 +55518,6 @@
       <c r="F1400" t="n">
         <v>9300.59</v>
       </c>
-      <c r="G1400" t="inlineStr"/>
       <c r="H1400" t="inlineStr">
         <is>
           <t xml:space="preserve">VT  </t>
@@ -56576,7 +55556,6 @@
       <c r="F1401" t="n">
         <v>12207.77</v>
       </c>
-      <c r="G1401" t="inlineStr"/>
       <c r="H1401" t="inlineStr">
         <is>
           <t>VT F</t>
@@ -59544,7 +58523,6 @@
           <t>5593, 5595</t>
         </is>
       </c>
-      <c r="H1470" t="inlineStr"/>
       <c r="I1470" t="n">
         <v>-389.12</v>
       </c>
@@ -59583,7 +58561,6 @@
           <t>5593</t>
         </is>
       </c>
-      <c r="H1471" t="inlineStr"/>
       <c r="I1471" t="n">
         <v>-1143.93</v>
       </c>
@@ -59622,7 +58599,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1472" t="inlineStr"/>
       <c r="I1472" t="n">
         <v>-260.86</v>
       </c>
@@ -59661,7 +58637,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1473" t="inlineStr"/>
       <c r="I1473" t="n">
         <v>-812.23</v>
       </c>
@@ -59700,7 +58675,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1474" t="inlineStr"/>
       <c r="I1474" t="n">
         <v>-719.6</v>
       </c>
@@ -59739,7 +58713,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1475" t="inlineStr"/>
       <c r="I1475" t="n">
         <v>-797.72</v>
       </c>
@@ -59778,7 +58751,6 @@
           <t>5593</t>
         </is>
       </c>
-      <c r="H1476" t="inlineStr"/>
       <c r="I1476" t="n">
         <v>-132.97</v>
       </c>
@@ -59817,7 +58789,6 @@
           <t>5593</t>
         </is>
       </c>
-      <c r="H1477" t="inlineStr"/>
       <c r="I1477" t="n">
         <v>-272.07</v>
       </c>
@@ -59856,7 +58827,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1478" t="inlineStr"/>
       <c r="I1478" t="n">
         <v>-56.9</v>
       </c>
@@ -59895,7 +58865,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1479" t="inlineStr"/>
       <c r="I1479" t="n">
         <v>-297.07</v>
       </c>
@@ -59934,7 +58903,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1480" t="inlineStr"/>
       <c r="I1480" t="n">
         <v>-297.43</v>
       </c>
@@ -59973,7 +58941,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1481" t="inlineStr"/>
       <c r="I1481" t="n">
         <v>-115.83</v>
       </c>
@@ -60012,7 +58979,6 @@
           <t>5593, 5595</t>
         </is>
       </c>
-      <c r="H1482" t="inlineStr"/>
       <c r="I1482" t="n">
         <v>-42.29</v>
       </c>
@@ -60051,7 +59017,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1483" t="inlineStr"/>
       <c r="I1483" t="n">
         <v>-56.45</v>
       </c>
@@ -60090,7 +59055,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1484" t="inlineStr"/>
       <c r="I1484" t="n">
         <v>-291.81</v>
       </c>
@@ -60129,7 +59093,6 @@
           <t>5593</t>
         </is>
       </c>
-      <c r="H1485" t="inlineStr"/>
       <c r="I1485" t="n">
         <v>-237.02</v>
       </c>
@@ -60168,7 +59131,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1486" t="inlineStr"/>
       <c r="I1486" t="n">
         <v>-54.98</v>
       </c>
@@ -60207,7 +59169,6 @@
           <t>5593, 5595, 5596</t>
         </is>
       </c>
-      <c r="H1487" t="inlineStr"/>
       <c r="I1487" t="n">
         <v>-1877.12</v>
       </c>
@@ -60246,7 +59207,6 @@
           <t>5593</t>
         </is>
       </c>
-      <c r="H1488" t="inlineStr"/>
       <c r="I1488" t="n">
         <v>-1037.25</v>
       </c>
@@ -60285,7 +59245,6 @@
           <t>5593, 5595</t>
         </is>
       </c>
-      <c r="H1489" t="inlineStr"/>
       <c r="I1489" t="n">
         <v>-253.63</v>
       </c>
@@ -60324,7 +59283,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1490" t="inlineStr"/>
       <c r="I1490" t="n">
         <v>-540.62</v>
       </c>
@@ -60363,7 +59321,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1491" t="inlineStr"/>
       <c r="I1491" t="n">
         <v>-57.06</v>
       </c>
@@ -60402,7 +59359,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1492" t="inlineStr"/>
       <c r="I1492" t="n">
         <v>-374.04</v>
       </c>
@@ -60441,7 +59397,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1493" t="inlineStr"/>
       <c r="I1493" t="n">
         <v>-310.46</v>
       </c>
@@ -60480,7 +59435,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1494" t="inlineStr"/>
       <c r="I1494" t="n">
         <v>-90.09</v>
       </c>
@@ -60519,7 +59473,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1495" t="inlineStr"/>
       <c r="I1495" t="n">
         <v>-43.14</v>
       </c>
@@ -60558,7 +59511,6 @@
           <t>5595</t>
         </is>
       </c>
-      <c r="H1496" t="inlineStr"/>
       <c r="I1496" t="n">
         <v>-43.14</v>
       </c>
@@ -60597,7 +59549,6 @@
           <t>5595, 5597</t>
         </is>
       </c>
-      <c r="H1497" t="inlineStr"/>
       <c r="I1497" t="n">
         <v>-355.95</v>
       </c>
@@ -60636,7 +59587,6 @@
           <t>5593, 5595, 5596</t>
         </is>
       </c>
-      <c r="H1498" t="inlineStr"/>
       <c r="I1498" t="n">
         <v>-101.79</v>
       </c>
@@ -60675,7 +59625,6 @@
           <t>5595, 5597</t>
         </is>
       </c>
-      <c r="H1499" t="inlineStr"/>
       <c r="I1499" t="n">
         <v>-203.8</v>
       </c>
@@ -60709,7 +59658,6 @@
       <c r="F1500" t="n">
         <v>11188.88</v>
       </c>
-      <c r="G1500" t="inlineStr"/>
       <c r="H1500" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60748,7 +59696,6 @@
       <c r="F1501" t="n">
         <v>3522.07</v>
       </c>
-      <c r="G1501" t="inlineStr"/>
       <c r="H1501" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60787,7 +59734,6 @@
       <c r="F1502" t="n">
         <v>5528.14</v>
       </c>
-      <c r="G1502" t="inlineStr"/>
       <c r="H1502" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60826,7 +59772,6 @@
       <c r="F1503" t="n">
         <v>4976.77</v>
       </c>
-      <c r="G1503" t="inlineStr"/>
       <c r="H1503" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60865,7 +59810,6 @@
       <c r="F1504" t="n">
         <v>5069.4</v>
       </c>
-      <c r="G1504" t="inlineStr"/>
       <c r="H1504" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60904,7 +59848,6 @@
       <c r="F1505" t="n">
         <v>4991.28</v>
       </c>
-      <c r="G1505" t="inlineStr"/>
       <c r="H1505" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60943,7 +59886,6 @@
       <c r="F1506" t="n">
         <v>5656.03</v>
       </c>
-      <c r="G1506" t="inlineStr"/>
       <c r="H1506" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -60982,7 +59924,6 @@
       <c r="F1507" t="n">
         <v>5516.93</v>
       </c>
-      <c r="G1507" t="inlineStr"/>
       <c r="H1507" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61021,7 +59962,6 @@
       <c r="F1508" t="n">
         <v>5732.1</v>
       </c>
-      <c r="G1508" t="inlineStr"/>
       <c r="H1508" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61060,7 +60000,6 @@
       <c r="F1509" t="n">
         <v>5491.93</v>
       </c>
-      <c r="G1509" t="inlineStr"/>
       <c r="H1509" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61099,7 +60038,6 @@
       <c r="F1510" t="n">
         <v>5491.57</v>
       </c>
-      <c r="G1510" t="inlineStr"/>
       <c r="H1510" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61138,7 +60076,6 @@
       <c r="F1511" t="n">
         <v>5673.17</v>
       </c>
-      <c r="G1511" t="inlineStr"/>
       <c r="H1511" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61177,7 +60114,6 @@
       <c r="F1512" t="n">
         <v>10409.71</v>
       </c>
-      <c r="G1512" t="inlineStr"/>
       <c r="H1512" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61216,7 +60152,6 @@
       <c r="F1513" t="n">
         <v>5732.55</v>
       </c>
-      <c r="G1513" t="inlineStr"/>
       <c r="H1513" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61255,7 +60190,6 @@
       <c r="F1514" t="n">
         <v>5497.19</v>
       </c>
-      <c r="G1514" t="inlineStr"/>
       <c r="H1514" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61294,7 +60228,6 @@
       <c r="F1515" t="n">
         <v>5551.98</v>
       </c>
-      <c r="G1515" t="inlineStr"/>
       <c r="H1515" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61333,7 +60266,6 @@
       <c r="F1516" t="n">
         <v>5734.02</v>
       </c>
-      <c r="G1516" t="inlineStr"/>
       <c r="H1516" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61372,7 +60304,6 @@
       <c r="F1517" t="n">
         <v>10694.44</v>
       </c>
-      <c r="G1517" t="inlineStr"/>
       <c r="H1517" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61411,7 +60342,6 @@
       <c r="F1518" t="n">
         <v>4751.75</v>
       </c>
-      <c r="G1518" t="inlineStr"/>
       <c r="H1518" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61450,7 +60380,6 @@
       <c r="F1519" t="n">
         <v>10194.38</v>
       </c>
-      <c r="G1519" t="inlineStr"/>
       <c r="H1519" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61489,7 +60418,6 @@
       <c r="F1520" t="n">
         <v>5248.38</v>
       </c>
-      <c r="G1520" t="inlineStr"/>
       <c r="H1520" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61528,7 +60456,6 @@
       <c r="F1521" t="n">
         <v>5731.94</v>
       </c>
-      <c r="G1521" t="inlineStr"/>
       <c r="H1521" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61567,7 +60494,6 @@
       <c r="F1522" t="n">
         <v>5414.96</v>
       </c>
-      <c r="G1522" t="inlineStr"/>
       <c r="H1522" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61606,7 +60532,6 @@
       <c r="F1523" t="n">
         <v>5478.54</v>
       </c>
-      <c r="G1523" t="inlineStr"/>
       <c r="H1523" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61645,7 +60570,6 @@
       <c r="F1524" t="n">
         <v>5698.91</v>
       </c>
-      <c r="G1524" t="inlineStr"/>
       <c r="H1524" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61684,7 +60608,6 @@
       <c r="F1525" t="n">
         <v>5745.86</v>
       </c>
-      <c r="G1525" t="inlineStr"/>
       <c r="H1525" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61723,7 +60646,6 @@
       <c r="F1526" t="n">
         <v>5745.86</v>
       </c>
-      <c r="G1526" t="inlineStr"/>
       <c r="H1526" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61762,7 +60684,6 @@
       <c r="F1527" t="n">
         <v>5465.19</v>
       </c>
-      <c r="G1527" t="inlineStr"/>
       <c r="H1527" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61801,7 +60722,6 @@
       <c r="F1528" t="n">
         <v>11511.3</v>
       </c>
-      <c r="G1528" t="inlineStr"/>
       <c r="H1528" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61840,7 +60760,6 @@
       <c r="F1529" t="n">
         <v>5693.49</v>
       </c>
-      <c r="G1529" t="inlineStr"/>
       <c r="H1529" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61879,7 +60798,6 @@
       <c r="F1530" t="n">
         <v>5710.73</v>
       </c>
-      <c r="G1530" t="inlineStr"/>
       <c r="H1530" t="inlineStr">
         <is>
           <t>RECL</t>
@@ -61918,7 +60836,6 @@
       <c r="F1531" t="n">
         <v>147636</v>
       </c>
-      <c r="G1531" t="inlineStr"/>
       <c r="H1531" t="inlineStr">
         <is>
           <t>ACOR, PROV</t>
@@ -61957,8 +60874,6 @@
       <c r="F1532" t="n">
         <v>0</v>
       </c>
-      <c r="G1532" t="inlineStr"/>
-      <c r="H1532" t="inlineStr"/>
       <c r="I1532" t="n">
         <v>705.53</v>
       </c>
@@ -61992,8 +60907,6 @@
       <c r="F1533" t="n">
         <v>0</v>
       </c>
-      <c r="G1533" t="inlineStr"/>
-      <c r="H1533" t="inlineStr"/>
       <c r="I1533" t="n">
         <v>217.05</v>
       </c>
@@ -62032,7 +60945,6 @@
           <t>0532</t>
         </is>
       </c>
-      <c r="H1534" t="inlineStr"/>
       <c r="I1534" t="n">
         <v>-329.99</v>
       </c>
@@ -62071,7 +60983,6 @@
           <t>3504</t>
         </is>
       </c>
-      <c r="H1535" t="inlineStr"/>
       <c r="I1535" t="n">
         <v>-130.13</v>
       </c>
@@ -62110,7 +61021,6 @@
           <t>3504</t>
         </is>
       </c>
-      <c r="H1536" t="inlineStr"/>
       <c r="I1536" t="n">
         <v>-137.67</v>
       </c>
@@ -62149,7 +61059,6 @@
           <t>3504</t>
         </is>
       </c>
-      <c r="H1537" t="inlineStr"/>
       <c r="I1537" t="n">
         <v>-130.13</v>
       </c>
@@ -62188,7 +61097,6 @@
           <t>3504</t>
         </is>
       </c>
-      <c r="H1538" t="inlineStr"/>
       <c r="I1538" t="n">
         <v>-1053.9</v>
       </c>
@@ -62222,8 +61130,6 @@
       <c r="F1539" t="n">
         <v>0</v>
       </c>
-      <c r="G1539" t="inlineStr"/>
-      <c r="H1539" t="inlineStr"/>
       <c r="I1539" t="n">
         <v>0</v>
       </c>
@@ -62918,7 +61824,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t>2 -  Diferença somente na folha RH</t>
         </is>
       </c>
     </row>
@@ -62951,7 +61857,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t>2 -  Diferença somente na folha RH</t>
         </is>
       </c>
     </row>
@@ -63479,7 +62385,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t>2 -  Diferença somente na folha RH</t>
         </is>
       </c>
     </row>
@@ -63512,7 +62418,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t xml:space="preserve">1 - OK! </t>
         </is>
       </c>
     </row>
@@ -63677,7 +62583,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2 - Apenas ADP</t>
+          <t xml:space="preserve">1 - OK! </t>
         </is>
       </c>
     </row>
@@ -63870,7 +62776,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -63893,7 +62799,7 @@
         <v>145115.56</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>22230.32</v>
@@ -63903,7 +62809,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -63936,7 +62842,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -63969,7 +62875,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -63992,7 +62898,7 @@
         <v>135652.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>28195.48</v>
@@ -64002,7 +62908,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64025,7 +62931,7 @@
         <v>119652.36</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>26169.45</v>
@@ -64035,7 +62941,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64068,7 +62974,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64101,7 +63007,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64134,7 +63040,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64157,7 +63063,7 @@
         <v>133609.55</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>69218.78</v>
@@ -64167,7 +63073,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64200,7 +63106,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>3 - Diferença somente no SAP</t>
         </is>
       </c>
     </row>
@@ -64223,7 +63129,7 @@
         <v>411517.21</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>118212.02</v>
@@ -64233,7 +63139,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64256,7 +63162,7 @@
         <v>122217.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>220879.74</v>
@@ -64266,7 +63172,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64289,7 +63195,7 @@
         <v>113652.76</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>60908.05</v>
@@ -64299,7 +63205,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64332,7 +63238,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64365,7 +63271,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64388,7 +63294,7 @@
         <v>98549.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>27902.23</v>
@@ -64398,7 +63304,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64431,7 +63337,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64464,7 +63370,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64497,7 +63403,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64530,7 +63436,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64563,7 +63469,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64596,7 +63502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64629,7 +63535,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64652,7 +63558,7 @@
         <v>218956.26</v>
       </c>
       <c r="F26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>-25166</v>
@@ -64662,7 +63568,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64685,7 +63591,7 @@
         <v>258621.54</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>108337.78</v>
@@ -64695,7 +63601,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64728,7 +63634,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64751,7 +63657,7 @@
         <v>182313.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>74697.42</v>
@@ -64761,7 +63667,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64784,7 +63690,7 @@
         <v>157615.87</v>
       </c>
       <c r="F30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>123047.55</v>
@@ -64794,7 +63700,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64827,7 +63733,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64860,7 +63766,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64883,7 +63789,7 @@
         <v>130725.21</v>
       </c>
       <c r="F33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>-10675.51</v>
@@ -64893,7 +63799,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64926,7 +63832,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64949,7 +63855,7 @@
         <v>126704.95</v>
       </c>
       <c r="F35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>-33969.36</v>
@@ -64959,7 +63865,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -64982,7 +63888,7 @@
         <v>159839.67</v>
       </c>
       <c r="F36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>11291.68</v>
@@ -64992,7 +63898,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65015,7 +63921,7 @@
         <v>146170.71</v>
       </c>
       <c r="F37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>31472.89</v>
@@ -65025,7 +63931,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65048,7 +63954,7 @@
         <v>214792.32</v>
       </c>
       <c r="F38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>135455.48</v>
@@ -65058,7 +63964,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65081,7 +63987,7 @@
         <v>190826.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>202192.28</v>
@@ -65091,7 +63997,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65114,7 +64020,7 @@
         <v>161821.35</v>
       </c>
       <c r="F40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>-29331.23</v>
@@ -65124,7 +64030,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65157,7 +64063,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65190,7 +64096,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65223,7 +64129,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65256,7 +64162,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65279,7 +64185,7 @@
         <v>155981.41</v>
       </c>
       <c r="F45" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>-10348.2</v>
@@ -65289,7 +64195,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65322,7 +64228,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65355,7 +64261,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65388,7 +64294,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65421,7 +64327,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65454,7 +64360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65477,7 +64383,7 @@
         <v>135269.96</v>
       </c>
       <c r="F51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>-22778.84</v>
@@ -65487,7 +64393,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65520,7 +64426,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65543,7 +64449,7 @@
         <v>186709.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>44646.99</v>
@@ -65553,7 +64459,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65586,7 +64492,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65619,7 +64525,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65652,7 +64558,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65685,7 +64591,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65708,7 +64614,7 @@
         <v>251715.87</v>
       </c>
       <c r="F58" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>147428.71</v>
@@ -65718,7 +64624,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65741,7 +64647,7 @@
         <v>171768.53</v>
       </c>
       <c r="F59" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>9176.459999999999</v>
@@ -65751,7 +64657,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>4 - Diferença em ambos</t>
         </is>
       </c>
     </row>
@@ -65784,7 +64690,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3 - Apenas SAP</t>
+          <t>3 - Diferença somente no SAP</t>
         </is>
       </c>
     </row>
@@ -65845,7 +64751,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
         <v>1559926.65</v>
       </c>
